--- a/sheets/NBFC.xlsx
+++ b/sheets/NBFC.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="10"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="Business" sheetId="1" state="visible" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="563">
   <si>
     <t>NBFC</t>
   </si>
@@ -228,6 +228,24 @@
     <t xml:space="preserve">Total No. of shares </t>
   </si>
   <si>
+    <t xml:space="preserve">Market cap </t>
+  </si>
+  <si>
+    <t>EV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Earnings </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Book value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PB </t>
+  </si>
+  <si>
     <t xml:space="preserve">Jio Financials</t>
   </si>
   <si>
@@ -1192,9 +1210,6 @@
   </si>
   <si>
     <t xml:space="preserve">EPS YoY</t>
-  </si>
-  <si>
-    <t>EV</t>
   </si>
   <si>
     <t xml:space="preserve">OCI YoY</t>
@@ -1898,7 +1913,7 @@
     <xf fontId="0" fillId="2" borderId="0" numFmtId="43" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0"/>
     <xf fontId="0" fillId="2" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="122">
+  <cellXfs count="110">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
@@ -2002,23 +2017,15 @@
     </xf>
     <xf fontId="3" fillId="0" borderId="0" numFmtId="171" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf fontId="4" fillId="0" borderId="0" numFmtId="171" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="0" fillId="0" borderId="2" numFmtId="0" xfId="0" applyBorder="1">
       <protection hidden="0" locked="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="165" xfId="1" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="172" xfId="1" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="172" xfId="1" applyNumberFormat="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="165" xfId="1" applyNumberFormat="1" applyFont="1">
       <protection hidden="0" locked="1"/>
     </xf>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="172" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="165" xfId="1" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="165" xfId="1" applyNumberFormat="1">
-      <protection hidden="0" locked="1"/>
-    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="165" xfId="1" applyNumberFormat="1">
       <protection hidden="0" locked="1"/>
     </xf>
@@ -2042,18 +2049,12 @@
       <protection hidden="0" locked="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="2" numFmtId="165" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="172" xfId="1" applyNumberFormat="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="165" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf fontId="1" fillId="0" borderId="2" numFmtId="165" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="10" xfId="2" applyNumberFormat="1"/>
-    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="171" xfId="1" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="172" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="172" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="2" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="2" xfId="2" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="2" xfId="2" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="9" xfId="2" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="9" xfId="2" applyNumberFormat="1">
       <protection hidden="0" locked="1"/>
     </xf>
@@ -2684,6 +2685,7 @@
   <cols>
     <col customWidth="1" min="2" max="2" width="29.421875"/>
     <col customWidth="1" min="3" max="3" width="19.57421875"/>
+    <col customWidth="1" min="10" max="10" width="12.421875"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -2993,50 +2995,75 @@
         <v>65</v>
       </c>
       <c r="E49" s="1"/>
-      <c r="F49" s="5"/>
-      <c r="G49" s="5"/>
-      <c r="H49" s="5"/>
-      <c r="I49" s="5"/>
-      <c r="J49" s="5"/>
+      <c r="F49" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="H49" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="I49" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="J49" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="L49" s="1"/>
+      <c r="M49" s="1"/>
+      <c r="N49" s="1"/>
+      <c r="O49" s="1"/>
+      <c r="P49" s="1"/>
+      <c r="Q49" s="1"/>
+      <c r="R49" s="1"/>
+      <c r="S49" s="1"/>
+      <c r="T49" s="1"/>
+      <c r="U49" s="1"/>
+      <c r="V49" s="1"/>
+      <c r="W49" s="1"/>
     </row>
     <row r="50" ht="14.25">
       <c r="B50" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="1" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="52" ht="14.25">
       <c r="B52" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
     <row r="53" ht="14.25">
       <c r="B53" s="1" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="1" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="55" ht="14.25">
       <c r="B55" s="1" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="56" ht="14.25">
       <c r="B56" s="1" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
     <row r="57" ht="14.25">
       <c r="B57" s="1" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -3059,7 +3086,7 @@
   <sheetData>
     <row r="2" ht="14.25">
       <c r="B2" s="23" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
     </row>
     <row r="3" ht="14.25">
@@ -3067,18 +3094,18 @@
     </row>
     <row r="5" ht="16.5">
       <c r="A5" s="21" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
     </row>
     <row r="7" ht="16.5">
       <c r="A7" s="21" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="C7" s="45">
         <v>0.39000000000000001</v>
@@ -3086,10 +3113,10 @@
     </row>
     <row r="8" ht="16.5">
       <c r="A8" s="21" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="C8" s="24">
         <v>0.34000000000000002</v>
@@ -3097,10 +3124,10 @@
     </row>
     <row r="9" ht="16.5">
       <c r="A9" s="21" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="C9" s="24">
         <v>0.51000000000000001</v>
@@ -3124,10 +3151,10 @@
     </row>
     <row r="14" ht="16.5">
       <c r="A14" s="21" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="C14" s="24">
         <v>0.51390000000000002</v>
@@ -3136,7 +3163,7 @@
     <row r="15" ht="16.5">
       <c r="A15" s="21"/>
       <c r="B15" s="21" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="C15" s="24">
         <v>0.73999999999999999</v>
@@ -3144,7 +3171,7 @@
     </row>
     <row r="16" ht="16.5">
       <c r="B16" s="21" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="C16" s="24">
         <v>0.73999999999999999</v>
@@ -3152,7 +3179,7 @@
     </row>
     <row r="17" ht="16.5">
       <c r="B17" s="21" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="C17" s="24">
         <v>0.80100000000000005</v>
@@ -3160,7 +3187,7 @@
     </row>
     <row r="18" ht="16.5">
       <c r="B18" s="21" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="C18" s="24">
         <v>1</v>
@@ -3181,10 +3208,10 @@
     </row>
     <row r="22" ht="16.5">
       <c r="A22" s="21" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="B22" s="21" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="C22" s="24">
         <v>0.88749999999999996</v>
@@ -3192,7 +3219,7 @@
     </row>
     <row r="23" ht="16.5">
       <c r="B23" s="21" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="C23" s="24">
         <v>1</v>
@@ -3203,12 +3230,12 @@
     </row>
     <row r="27" ht="16.5">
       <c r="B27" s="22" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
     </row>
     <row r="29" ht="16.5">
       <c r="B29" s="21" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="C29" s="75">
         <v>49500</v>
@@ -3216,10 +3243,10 @@
     </row>
     <row r="30" ht="16.5">
       <c r="A30" s="21" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="B30" s="21" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="C30" s="75">
         <v>62700</v>
@@ -3227,7 +3254,7 @@
     </row>
     <row r="31" ht="16.5">
       <c r="B31" s="21" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="C31" s="75">
         <v>46250</v>
@@ -3235,7 +3262,7 @@
     </row>
     <row r="32" ht="16.5">
       <c r="B32" s="21" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="C32" s="75">
         <v>21250</v>
@@ -3243,7 +3270,7 @@
     </row>
     <row r="33" ht="16.5">
       <c r="B33" s="21" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="C33" s="75">
         <v>30700</v>
@@ -3251,7 +3278,7 @@
     </row>
     <row r="34" ht="16.5">
       <c r="B34" s="21" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="C34" s="75">
         <v>550</v>
@@ -3259,7 +3286,7 @@
     </row>
     <row r="35" ht="16.5">
       <c r="B35" s="21" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="C35" s="75">
         <v>8900</v>
@@ -3267,7 +3294,7 @@
     </row>
     <row r="36" ht="16.5">
       <c r="B36" s="21" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="C36" s="75">
         <v>2300</v>
@@ -3275,7 +3302,7 @@
     </row>
     <row r="37" ht="16.5">
       <c r="B37" s="21" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="C37" s="75">
         <v>100</v>
@@ -3283,7 +3310,7 @@
     </row>
     <row r="38" ht="16.5">
       <c r="B38" s="21" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="C38" s="75">
         <v>850</v>
@@ -3291,7 +3318,7 @@
     </row>
     <row r="39" ht="16.5">
       <c r="B39" s="21" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="C39" s="75">
         <v>9200</v>
@@ -3299,7 +3326,7 @@
     </row>
     <row r="40" ht="16.5">
       <c r="B40" s="21" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C40" s="75">
         <v>232200</v>
@@ -3307,7 +3334,7 @@
     </row>
     <row r="41" ht="16.5">
       <c r="B41" s="21" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C41" s="75">
         <v>7500</v>
@@ -3315,12 +3342,12 @@
     </row>
     <row r="44" ht="16.5">
       <c r="B44" s="22" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
     </row>
     <row r="45" ht="16.5">
       <c r="B45" s="21" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="C45" s="75">
         <v>17319</v>
@@ -3328,7 +3355,7 @@
     </row>
     <row r="46" ht="16.5">
       <c r="B46" s="21" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="C46" s="75">
         <v>29109</v>
@@ -3336,7 +3363,7 @@
     </row>
     <row r="47" ht="16.5">
       <c r="B47" s="21" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="C47" s="75">
         <v>87696</v>
@@ -3344,7 +3371,7 @@
     </row>
     <row r="48" ht="16.5">
       <c r="B48" s="21" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="C48" s="75">
         <v>7944</v>
@@ -3353,7 +3380,7 @@
     <row r="49" ht="16.5">
       <c r="A49" s="21"/>
       <c r="B49" s="21" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="C49" s="75">
         <v>21467</v>
@@ -3361,7 +3388,7 @@
     </row>
     <row r="50" ht="16.5">
       <c r="B50" s="21" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="C50" s="75">
         <v>8307</v>
@@ -3369,7 +3396,7 @@
     </row>
     <row r="51" ht="16.5">
       <c r="B51" s="21" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="C51" s="75">
         <v>50345</v>
@@ -3377,7 +3404,7 @@
     </row>
     <row r="52" ht="16.5">
       <c r="B52" s="21" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="C52" s="75">
         <v>11876</v>
@@ -3385,7 +3412,7 @@
     </row>
     <row r="53" ht="16.5">
       <c r="B53" s="21" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="C53" s="75">
         <v>27760</v>
@@ -3393,7 +3420,7 @@
     </row>
     <row r="54" ht="16.5">
       <c r="B54" s="21" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="C54" s="75">
         <v>25377</v>
@@ -3401,7 +3428,7 @@
     </row>
     <row r="55" ht="16.5">
       <c r="B55" s="21" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="C55" s="75">
         <v>129461</v>
@@ -3409,7 +3436,7 @@
     </row>
     <row r="56" ht="16.5">
       <c r="B56" s="22" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="C56" s="76">
         <f>SUM(C45:C55)</f>
@@ -3437,62 +3464,60 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="14.140625"/>
     <col customWidth="1" min="2" max="3" width="22.28125"/>
-    <col customWidth="1" min="4" max="11" width="17.7109375"/>
-    <col customWidth="1" min="12" max="15" width="17.7109375"/>
-    <col customWidth="1" min="16" max="16384" width="17.7109375"/>
+    <col customWidth="1" min="4" max="16384" width="17.7109375"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B1" t="s">
-        <v>476</v>
-      </c>
-      <c r="C1" s="77"/>
+        <v>481</v>
+      </c>
+      <c r="C1" s="2"/>
       <c r="J1" s="23" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="K1" s="23" t="s">
-        <v>478</v>
-      </c>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
+        <v>483</v>
+      </c>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="23"/>
+      <c r="O1" s="23"/>
     </row>
     <row r="2">
       <c r="C2" s="1" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="K2" s="1">
         <v>2025</v>
       </c>
-      <c r="L2" s="79"/>
-      <c r="M2" s="79"/>
-      <c r="N2" s="79"/>
-      <c r="O2" s="79"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
       <c r="P2">
         <v>2025</v>
       </c>
@@ -3532,630 +3557,628 @@
         <f>X2+1</f>
         <v>2034</v>
       </c>
-      <c r="Z2" s="80">
+      <c r="Z2" s="77">
         <f>Y2+1</f>
         <v>2035</v>
       </c>
-      <c r="AA2" s="80">
+      <c r="AA2" s="77">
         <f>Z2+1</f>
         <v>2036</v>
       </c>
-      <c r="AB2" s="80">
+      <c r="AB2" s="77">
         <f>AA2+1</f>
         <v>2037</v>
       </c>
-      <c r="AC2" s="80">
+      <c r="AC2" s="77">
         <f>AB2+1</f>
         <v>2038</v>
       </c>
-      <c r="AD2" s="80">
+      <c r="AD2" s="77">
         <f>AC2+1</f>
         <v>2039</v>
       </c>
-      <c r="AE2" s="80">
+      <c r="AE2" s="77">
         <f>AD2+1</f>
         <v>2040</v>
       </c>
-      <c r="AF2" s="80">
+      <c r="AF2" s="77">
         <f>AE2+1</f>
         <v>2041</v>
       </c>
-      <c r="AG2" s="80">
+      <c r="AG2" s="77">
         <f>AF2+1</f>
         <v>2042</v>
       </c>
-      <c r="AH2" s="80">
+      <c r="AH2" s="77">
         <f>AG2+1</f>
         <v>2043</v>
       </c>
-      <c r="AI2" s="80">
+      <c r="AI2" s="77">
         <f>AH2+1</f>
         <v>2044</v>
       </c>
-      <c r="AJ2" s="80">
+      <c r="AJ2" s="77">
         <f>AI2+1</f>
         <v>2045</v>
       </c>
-      <c r="AK2" s="80">
+      <c r="AK2" s="77">
         <f>AJ2+1</f>
         <v>2046</v>
       </c>
-      <c r="AL2" s="80">
+      <c r="AL2" s="77">
         <f>AK2+1</f>
         <v>2047</v>
       </c>
-      <c r="AM2" s="80">
+      <c r="AM2" s="77">
         <f>AL2+1</f>
         <v>2048</v>
       </c>
-      <c r="AN2" s="80">
+      <c r="AN2" s="77">
         <f>AM2+1</f>
         <v>2049</v>
       </c>
-      <c r="AO2" s="80">
+      <c r="AO2" s="77">
         <f>AN2+1</f>
         <v>2050</v>
       </c>
-      <c r="AP2" s="80">
+      <c r="AP2" s="77">
         <f>AO2+1</f>
         <v>2051</v>
       </c>
-      <c r="AQ2" s="80">
+      <c r="AQ2" s="77">
         <f>AP2+1</f>
         <v>2052</v>
       </c>
-      <c r="AR2" s="80">
+      <c r="AR2" s="77">
         <f>AQ2+1</f>
         <v>2053</v>
       </c>
-      <c r="AS2" s="80">
+      <c r="AS2" s="77">
         <f>AR2+1</f>
         <v>2054</v>
       </c>
-      <c r="AT2" s="80">
+      <c r="AT2" s="77">
         <f>AS2+1</f>
         <v>2055</v>
       </c>
-      <c r="AU2" s="80">
+      <c r="AU2" s="77">
         <f>AT2+1</f>
         <v>2056</v>
       </c>
-      <c r="AV2" s="80">
+      <c r="AV2" s="77">
         <f>AU2+1</f>
         <v>2057</v>
       </c>
-      <c r="AW2" s="80">
+      <c r="AW2" s="77">
         <f>AV2+1</f>
         <v>2058</v>
       </c>
-      <c r="AX2" s="80">
+      <c r="AX2" s="77">
         <f>AW2+1</f>
         <v>2059</v>
       </c>
-      <c r="AY2" s="80">
+      <c r="AY2" s="77">
         <f>AX2+1</f>
         <v>2060</v>
       </c>
-      <c r="AZ2" s="80">
+      <c r="AZ2" s="77">
         <f>AY2+1</f>
         <v>2061</v>
       </c>
-      <c r="BA2" s="80">
+      <c r="BA2" s="77">
         <f>AZ2+1</f>
         <v>2062</v>
       </c>
-      <c r="BB2" s="80">
+      <c r="BB2" s="77">
         <f>BA2+1</f>
         <v>2063</v>
       </c>
-      <c r="BC2" s="80">
+      <c r="BC2" s="77">
         <f>BB2+1</f>
         <v>2064</v>
       </c>
-      <c r="BD2" s="80">
+      <c r="BD2" s="77">
         <f>BC2+1</f>
         <v>2065</v>
       </c>
-      <c r="BE2" s="80">
+      <c r="BE2" s="77">
         <f>BD2+1</f>
         <v>2066</v>
       </c>
-      <c r="BF2" s="80">
+      <c r="BF2" s="77">
         <f>BE2+1</f>
         <v>2067</v>
       </c>
-      <c r="BG2" s="80">
+      <c r="BG2" s="77">
         <f>BF2+1</f>
         <v>2068</v>
       </c>
-      <c r="BH2" s="80">
+      <c r="BH2" s="77">
         <f>BG2+1</f>
         <v>2069</v>
       </c>
-      <c r="BI2" s="80">
+      <c r="BI2" s="77">
         <f>BH2+1</f>
         <v>2070</v>
       </c>
-      <c r="BJ2" s="80">
+      <c r="BJ2" s="77">
         <f>BI2+1</f>
         <v>2071</v>
       </c>
-      <c r="BK2" s="80">
+      <c r="BK2" s="77">
         <f>BJ2+1</f>
         <v>2072</v>
       </c>
-      <c r="BL2" s="80">
+      <c r="BL2" s="77">
         <f>BK2+1</f>
         <v>2073</v>
       </c>
-      <c r="BM2" s="80">
+      <c r="BM2" s="77">
         <f>BL2+1</f>
         <v>2074</v>
       </c>
-      <c r="BN2" s="80">
+      <c r="BN2" s="77">
         <f>BM2+1</f>
         <v>2075</v>
       </c>
-      <c r="BO2" s="80">
+      <c r="BO2" s="77">
         <f>BN2+1</f>
         <v>2076</v>
       </c>
-      <c r="BP2" s="80">
+      <c r="BP2" s="77">
         <f>BO2+1</f>
         <v>2077</v>
       </c>
-      <c r="BQ2" s="80">
+      <c r="BQ2" s="77">
         <f>BP2+1</f>
         <v>2078</v>
       </c>
-      <c r="BR2" s="80">
+      <c r="BR2" s="77">
         <f>BQ2+1</f>
         <v>2079</v>
       </c>
-      <c r="BS2" s="80">
+      <c r="BS2" s="77">
         <f>BR2+1</f>
         <v>2080</v>
       </c>
-      <c r="BT2" s="80">
+      <c r="BT2" s="77">
         <f>BS2+1</f>
         <v>2081</v>
       </c>
-      <c r="BU2" s="80">
+      <c r="BU2" s="77">
         <f>BT2+1</f>
         <v>2082</v>
       </c>
-      <c r="BV2" s="80">
+      <c r="BV2" s="77">
         <f>BU2+1</f>
         <v>2083</v>
       </c>
-      <c r="BW2" s="80">
+      <c r="BW2" s="77">
         <f>BV2+1</f>
         <v>2084</v>
       </c>
-      <c r="BX2" s="80">
+      <c r="BX2" s="77">
         <f>BW2+1</f>
         <v>2085</v>
       </c>
-      <c r="BY2" s="80">
+      <c r="BY2" s="77">
         <f>BX2+1</f>
         <v>2086</v>
       </c>
-      <c r="BZ2" s="80">
+      <c r="BZ2" s="77">
         <f>BY2+1</f>
         <v>2087</v>
       </c>
-      <c r="CA2" s="80">
+      <c r="CA2" s="77">
         <f>BZ2+1</f>
         <v>2088</v>
       </c>
-      <c r="CB2" s="80">
+      <c r="CB2" s="77">
         <f>CA2+1</f>
         <v>2089</v>
       </c>
-      <c r="CC2" s="80">
+      <c r="CC2" s="77">
         <f>CB2+1</f>
         <v>2090</v>
       </c>
-      <c r="CD2" s="80">
+      <c r="CD2" s="77">
         <f>CC2+1</f>
         <v>2091</v>
       </c>
-      <c r="CE2" s="80">
+      <c r="CE2" s="77">
         <f>CD2+1</f>
         <v>2092</v>
       </c>
-      <c r="CF2" s="80">
+      <c r="CF2" s="77">
         <f>CE2+1</f>
         <v>2093</v>
       </c>
-      <c r="CG2" s="80">
+      <c r="CG2" s="77">
         <f>CF2+1</f>
         <v>2094</v>
       </c>
-      <c r="CH2" s="80">
+      <c r="CH2" s="77">
         <f>CG2+1</f>
         <v>2095</v>
       </c>
-      <c r="CI2" s="80">
+      <c r="CI2" s="77">
         <f>CH2+1</f>
         <v>2096</v>
       </c>
-      <c r="CJ2" s="80">
+      <c r="CJ2" s="77">
         <f>CI2+1</f>
         <v>2097</v>
       </c>
-      <c r="CK2" s="80">
+      <c r="CK2" s="77">
         <f>CJ2+1</f>
         <v>2098</v>
       </c>
-      <c r="CL2" s="80">
+      <c r="CL2" s="77">
         <f>CK2+1</f>
         <v>2099</v>
       </c>
-      <c r="CM2" s="80">
+      <c r="CM2" s="77">
         <f>CL2+1</f>
         <v>2100</v>
       </c>
-      <c r="CN2" s="80">
+      <c r="CN2" s="77">
         <f>CM2+1</f>
         <v>2101</v>
       </c>
-      <c r="CO2" s="80">
+      <c r="CO2" s="77">
         <f>CN2+1</f>
         <v>2102</v>
       </c>
-      <c r="CP2" s="80">
+      <c r="CP2" s="77">
         <f>CO2+1</f>
         <v>2103</v>
       </c>
-      <c r="CQ2" s="80">
+      <c r="CQ2" s="77">
         <f>CP2+1</f>
         <v>2104</v>
       </c>
-      <c r="CR2" s="80">
+      <c r="CR2" s="77">
         <f>CQ2+1</f>
         <v>2105</v>
       </c>
-      <c r="CS2" s="80">
+      <c r="CS2" s="77">
         <f>CR2+1</f>
         <v>2106</v>
       </c>
-      <c r="CT2" s="80">
+      <c r="CT2" s="77">
         <f>CS2+1</f>
         <v>2107</v>
       </c>
-      <c r="CU2" s="80">
+      <c r="CU2" s="77">
         <f>CT2+1</f>
         <v>2108</v>
       </c>
-      <c r="CV2" s="80">
+      <c r="CV2" s="77">
         <f>CU2+1</f>
         <v>2109</v>
       </c>
-      <c r="CW2" s="80">
+      <c r="CW2" s="77">
         <f>CV2+1</f>
         <v>2110</v>
       </c>
-      <c r="CX2" s="80">
+      <c r="CX2" s="77">
         <f>CW2+1</f>
         <v>2111</v>
       </c>
-      <c r="CY2" s="80">
+      <c r="CY2" s="77">
         <f>CX2+1</f>
         <v>2112</v>
       </c>
-      <c r="CZ2" s="80">
+      <c r="CZ2" s="77">
         <f>CY2+1</f>
         <v>2113</v>
       </c>
-      <c r="DA2" s="80">
+      <c r="DA2" s="77">
         <f>CZ2+1</f>
         <v>2114</v>
       </c>
-      <c r="DB2" s="80">
+      <c r="DB2" s="77">
         <f>DA2+1</f>
         <v>2115</v>
       </c>
-      <c r="DC2" s="80">
+      <c r="DC2" s="77">
         <f>DB2+1</f>
         <v>2116</v>
       </c>
-      <c r="DD2" s="80">
+      <c r="DD2" s="77">
         <f>DC2+1</f>
         <v>2117</v>
       </c>
-      <c r="DE2" s="80">
+      <c r="DE2" s="77">
         <f>DD2+1</f>
         <v>2118</v>
       </c>
-      <c r="DF2" s="80">
+      <c r="DF2" s="77">
         <f>DE2+1</f>
         <v>2119</v>
       </c>
-      <c r="DG2" s="80">
+      <c r="DG2" s="77">
         <f>DF2+1</f>
         <v>2120</v>
       </c>
-      <c r="DH2" s="80">
+      <c r="DH2" s="77">
         <f>DG2+1</f>
         <v>2121</v>
       </c>
-      <c r="DI2" s="80">
+      <c r="DI2" s="77">
         <f>DH2+1</f>
         <v>2122</v>
       </c>
-      <c r="DJ2" s="80">
+      <c r="DJ2" s="77">
         <f>DI2+1</f>
         <v>2123</v>
       </c>
-      <c r="DK2" s="80">
+      <c r="DK2" s="77">
         <f>DJ2+1</f>
         <v>2124</v>
       </c>
-      <c r="DL2" s="80">
+      <c r="DL2" s="77">
         <f>DK2+1</f>
         <v>2125</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" t="s">
-        <v>479</v>
-      </c>
-      <c r="C3" s="77"/>
-      <c r="D3" s="81">
+        <v>484</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="78">
         <v>22970.389999999999</v>
       </c>
-      <c r="E3" s="81">
+      <c r="E3" s="78">
         <v>16348.75</v>
       </c>
-      <c r="F3" s="81">
+      <c r="F3" s="78">
         <v>22970.389999999999</v>
       </c>
-      <c r="G3" s="81">
+      <c r="G3" s="78">
         <v>23303.380000000001</v>
       </c>
-      <c r="H3" s="81">
+      <c r="H3" s="78">
         <v>27269.759999999998</v>
       </c>
-      <c r="I3" s="81">
+      <c r="I3" s="78">
         <v>35548.57</v>
       </c>
-      <c r="J3" s="81">
+      <c r="J3" s="78">
         <v>48306.599999999999</v>
       </c>
-      <c r="K3" s="82">
+      <c r="K3" s="79">
         <v>61163</v>
       </c>
-      <c r="L3" s="83"/>
-      <c r="M3" s="83"/>
-      <c r="N3" s="83"/>
-      <c r="O3" s="83"/>
+      <c r="L3" s="79"/>
+      <c r="M3" s="79"/>
+      <c r="N3" s="79"/>
+      <c r="O3" s="79"/>
       <c r="U3" s="8"/>
       <c r="Z3" s="8"/>
     </row>
     <row r="4">
       <c r="B4" t="s">
-        <v>480</v>
-      </c>
-      <c r="C4" s="77"/>
-      <c r="D4" s="81">
+        <v>485</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="78">
         <v>2590.9499999999998</v>
       </c>
-      <c r="E4" s="81">
+      <c r="E4" s="78">
         <v>1681.8699999999999</v>
       </c>
-      <c r="F4" s="81">
+      <c r="F4" s="78">
         <v>2590.9499999999998</v>
       </c>
-      <c r="G4" s="81">
+      <c r="G4" s="78">
         <v>2452.3899999999999</v>
       </c>
-      <c r="H4" s="81">
+      <c r="H4" s="78">
         <v>3066.6900000000001</v>
       </c>
-      <c r="I4" s="81">
+      <c r="I4" s="78">
         <v>4355.6300000000001</v>
       </c>
-      <c r="J4" s="81">
+      <c r="J4" s="78">
         <v>5267.1700000000001</v>
       </c>
-      <c r="K4" s="82">
+      <c r="K4" s="79">
         <v>5982.8400000000001</v>
       </c>
-      <c r="L4" s="83"/>
-      <c r="M4" s="83"/>
-      <c r="N4" s="83"/>
-      <c r="O4" s="83"/>
+      <c r="L4" s="79"/>
+      <c r="M4" s="79"/>
+      <c r="N4" s="79"/>
+      <c r="O4" s="79"/>
       <c r="U4" s="8"/>
       <c r="Z4" s="8"/>
     </row>
     <row r="5" s="1" customFormat="1">
       <c r="B5" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C5"/>
-      <c r="D5" s="81">
+        <v>85</v>
+      </c>
+      <c r="D5" s="78">
         <v>537.49000000000001</v>
       </c>
-      <c r="E5" s="81">
+      <c r="E5" s="78">
         <v>297.89999999999998</v>
       </c>
-      <c r="F5" s="81">
+      <c r="F5" s="78">
         <v>537.49000000000001</v>
       </c>
-      <c r="G5" s="81">
+      <c r="G5" s="78">
         <v>591.20000000000005</v>
       </c>
-      <c r="H5" s="81">
+      <c r="H5" s="78">
         <v>327.74000000000001</v>
       </c>
-      <c r="I5" s="81">
+      <c r="I5" s="78">
         <v>334.31999999999999</v>
       </c>
-      <c r="J5" s="81">
+      <c r="J5" s="78">
         <v>308.29000000000002</v>
       </c>
-      <c r="K5" s="82">
+      <c r="K5" s="79">
         <v>539.02999999999997</v>
       </c>
-      <c r="L5" s="83"/>
-      <c r="M5" s="83"/>
-      <c r="N5" s="83"/>
-      <c r="O5" s="83"/>
+      <c r="L5" s="79"/>
+      <c r="M5" s="79"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
       <c r="U5" s="6"/>
       <c r="Z5" s="6"/>
     </row>
     <row r="6">
       <c r="B6" t="s">
-        <v>352</v>
-      </c>
-      <c r="C6" s="77"/>
-      <c r="D6" s="81">
+        <v>358</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="78">
         <v>124.27</v>
       </c>
-      <c r="E6" s="81">
+      <c r="E6" s="78">
         <v>68.769999999999996</v>
       </c>
-      <c r="F6" s="81">
+      <c r="F6" s="78">
         <v>124.27</v>
       </c>
-      <c r="G6" s="81">
+      <c r="G6" s="78">
         <v>157.53</v>
       </c>
-      <c r="H6" s="81">
+      <c r="H6" s="78">
         <v>74.959999999999994</v>
       </c>
-      <c r="I6" s="81">
+      <c r="I6" s="78">
         <v>38.18</v>
       </c>
-      <c r="J6" s="81">
+      <c r="J6" s="78">
         <v>49.969999999999999</v>
       </c>
-      <c r="K6" s="82">
+      <c r="K6" s="79">
         <v>27.129999999999999</v>
       </c>
-      <c r="L6" s="83"/>
-      <c r="M6" s="83"/>
-      <c r="N6" s="83"/>
-      <c r="O6" s="83"/>
+      <c r="L6" s="79"/>
+      <c r="M6" s="79"/>
+      <c r="N6" s="79"/>
+      <c r="O6" s="79"/>
       <c r="U6" s="8"/>
       <c r="Z6" s="8"/>
     </row>
     <row r="7" s="1" customFormat="1">
       <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="C7"/>
-      <c r="D7" s="81">
+        <v>486</v>
+      </c>
+      <c r="D7" s="78">
         <v>150.69999999999999</v>
       </c>
-      <c r="E7" s="81">
+      <c r="E7" s="78">
         <v>89.849999999999994</v>
       </c>
-      <c r="F7" s="81">
+      <c r="F7" s="78">
         <v>150.69999999999999</v>
       </c>
-      <c r="G7" s="81">
+      <c r="G7" s="78">
         <v>0</v>
       </c>
-      <c r="H7" s="81">
+      <c r="H7" s="78">
         <v>0</v>
       </c>
-      <c r="I7" s="81">
+      <c r="I7" s="78">
         <v>23.170000000000002</v>
       </c>
-      <c r="J7" s="81">
+      <c r="J7" s="78">
         <v>13.33</v>
       </c>
-      <c r="K7" s="82">
+      <c r="K7" s="79">
         <v>552.03999999999996</v>
       </c>
-      <c r="L7" s="83"/>
-      <c r="M7" s="83"/>
-      <c r="N7" s="83"/>
-      <c r="O7" s="83"/>
+      <c r="L7" s="79"/>
+      <c r="M7" s="79"/>
+      <c r="N7" s="79"/>
+      <c r="O7" s="79"/>
       <c r="U7" s="6"/>
       <c r="Z7" s="6"/>
     </row>
     <row r="8">
       <c r="B8" t="s">
-        <v>482</v>
-      </c>
-      <c r="C8" s="77"/>
-      <c r="D8" s="81">
+        <v>487</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="78">
         <v>0</v>
       </c>
-      <c r="E8" s="81">
+      <c r="E8" s="78">
         <v>0</v>
       </c>
-      <c r="F8" s="81">
+      <c r="F8" s="78">
         <v>0</v>
       </c>
-      <c r="G8" s="81">
+      <c r="G8" s="78">
         <v>163.58000000000001</v>
       </c>
-      <c r="H8" s="81">
+      <c r="H8" s="78">
         <v>893.26999999999998</v>
       </c>
-      <c r="I8" s="81">
+      <c r="I8" s="78">
         <v>1110.29</v>
       </c>
-      <c r="J8" s="81">
+      <c r="J8" s="78">
         <v>1024.1300000000001</v>
       </c>
-      <c r="K8" s="82">
+      <c r="K8" s="79">
         <v>1418.9200000000001</v>
       </c>
-      <c r="L8" s="83"/>
-      <c r="M8" s="83"/>
-      <c r="N8" s="83"/>
-      <c r="O8" s="83"/>
+      <c r="L8" s="79"/>
+      <c r="M8" s="79"/>
+      <c r="N8" s="79"/>
+      <c r="O8" s="79"/>
       <c r="U8" s="8"/>
       <c r="Z8" s="8"/>
     </row>
     <row r="9" s="1" customFormat="1">
       <c r="B9" s="1" t="s">
-        <v>483</v>
-      </c>
-      <c r="C9" s="84">
+        <v>488</v>
+      </c>
+      <c r="C9" s="80">
         <v>9966.7099999999991</v>
       </c>
-      <c r="D9" s="84">
+      <c r="D9" s="80">
         <v>13442.040000000001</v>
       </c>
-      <c r="E9" s="84">
+      <c r="E9" s="80">
         <f>SUM(E3:E8)</f>
         <v>18487.139999999999</v>
       </c>
-      <c r="F9" s="84">
+      <c r="F9" s="80">
         <f>SUM(F3:F8)</f>
         <v>26373.800000000003</v>
       </c>
-      <c r="G9" s="84">
+      <c r="G9" s="80">
         <f>SUM(G3:G8)</f>
         <v>26668.080000000002</v>
       </c>
-      <c r="H9" s="84">
+      <c r="H9" s="80">
         <f>SUM(H3:H8)</f>
         <v>31632.419999999998</v>
       </c>
-      <c r="I9" s="84">
+      <c r="I9" s="80">
         <f>SUM(I3:I8)</f>
         <v>41410.159999999996</v>
       </c>
-      <c r="J9" s="84">
+      <c r="J9" s="80">
         <f>SUM(J3:J8)</f>
         <v>54969.489999999998</v>
       </c>
-      <c r="K9" s="85">
+      <c r="K9" s="81">
         <f>SUM(K3:K8)</f>
         <v>69682.959999999992</v>
       </c>
-      <c r="L9" s="82"/>
-      <c r="M9" s="82"/>
-      <c r="N9" s="82"/>
-      <c r="O9" s="82"/>
+      <c r="L9" s="79"/>
+      <c r="M9" s="79"/>
+      <c r="N9" s="79"/>
+      <c r="O9" s="79"/>
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
@@ -4170,127 +4193,127 @@
     </row>
     <row r="10">
       <c r="B10" t="s">
-        <v>180</v>
-      </c>
-      <c r="C10" s="86">
+        <v>186</v>
+      </c>
+      <c r="C10" s="78">
         <v>25.48</v>
       </c>
-      <c r="D10" s="81">
+      <c r="D10" s="78">
         <v>23.870000000000001</v>
       </c>
-      <c r="E10" s="81">
+      <c r="E10" s="78">
         <v>13.039999999999999</v>
       </c>
-      <c r="F10" s="81">
+      <c r="F10" s="78">
         <v>11.83</v>
       </c>
-      <c r="G10" s="81">
+      <c r="G10" s="78">
         <v>14.949999999999999</v>
       </c>
-      <c r="H10" s="81">
+      <c r="H10" s="78">
         <v>7.9900000000000002</v>
       </c>
-      <c r="I10" s="81">
+      <c r="I10" s="78">
         <v>8.0999999999999996</v>
       </c>
-      <c r="J10" s="81">
+      <c r="J10" s="78">
         <v>13.02</v>
       </c>
-      <c r="K10" s="82">
+      <c r="K10" s="79">
         <v>41.270000000000003</v>
       </c>
-      <c r="L10" s="83"/>
-      <c r="M10" s="83"/>
-      <c r="N10" s="83"/>
-      <c r="O10" s="83"/>
+      <c r="L10" s="79"/>
+      <c r="M10" s="79"/>
+      <c r="N10" s="79"/>
+      <c r="O10" s="79"/>
       <c r="U10" s="8"/>
       <c r="Z10" s="8"/>
     </row>
     <row r="11">
       <c r="B11" t="s">
-        <v>356</v>
-      </c>
-      <c r="C11" s="87">
+        <v>362</v>
+      </c>
+      <c r="C11" s="82">
         <f>C9+C10</f>
         <v>9992.1899999999987</v>
       </c>
-      <c r="D11" s="88">
+      <c r="D11" s="82">
         <f>D9+D10</f>
         <v>13465.910000000002</v>
       </c>
-      <c r="E11" s="88">
+      <c r="E11" s="82">
         <f>E9+E10</f>
         <v>18500.18</v>
       </c>
-      <c r="F11" s="88">
+      <c r="F11" s="82">
         <f>F9+F10</f>
         <v>26385.630000000005</v>
       </c>
-      <c r="G11" s="88">
+      <c r="G11" s="82">
         <f>G9+G10</f>
         <v>26683.030000000002</v>
       </c>
-      <c r="H11" s="88">
+      <c r="H11" s="82">
         <f>H9+H10</f>
         <v>31640.41</v>
       </c>
-      <c r="I11" s="88">
+      <c r="I11" s="82">
         <f>I9+I10</f>
         <v>41418.259999999995</v>
       </c>
-      <c r="J11" s="88">
+      <c r="J11" s="82">
         <f>J9+J10</f>
         <v>54982.509999999995</v>
       </c>
-      <c r="K11" s="88">
+      <c r="K11" s="82">
         <f>K9+K10</f>
         <v>69724.229999999996</v>
       </c>
-      <c r="L11" s="82"/>
-      <c r="M11" s="82"/>
-      <c r="N11" s="82"/>
-      <c r="O11" s="82"/>
-      <c r="P11" s="89">
+      <c r="L11" s="79"/>
+      <c r="M11" s="79"/>
+      <c r="N11" s="79"/>
+      <c r="O11" s="79"/>
+      <c r="P11" s="83">
         <f>K11*(1+$Q$40)</f>
         <v>80880.106799999994</v>
       </c>
-      <c r="Q11" s="89">
+      <c r="Q11" s="83">
         <f>P11*(1+$Q$40)</f>
         <v>93820.92388799999</v>
       </c>
-      <c r="R11" s="89">
+      <c r="R11" s="83">
         <f>Q11*(1+$Q$40)</f>
         <v>108832.27171007998</v>
       </c>
-      <c r="S11" s="89">
+      <c r="S11" s="83">
         <f>R11*(1+$Q$40)</f>
         <v>126245.43518369277</v>
       </c>
-      <c r="T11" s="89">
+      <c r="T11" s="83">
         <f>S11*(1+$Q$40)</f>
         <v>146444.7048130836</v>
       </c>
-      <c r="U11" s="90">
+      <c r="U11" s="84">
         <f>T11*(1+$Q$40)</f>
         <v>169875.85758317696</v>
       </c>
-      <c r="V11" s="89">
+      <c r="V11" s="83">
         <f>U11*(1+$V$40)</f>
         <v>190260.9604931582</v>
       </c>
-      <c r="W11" s="89">
+      <c r="W11" s="83">
         <f>V11*(1+$V$40)</f>
         <v>213092.27575233721</v>
       </c>
-      <c r="X11" s="89">
+      <c r="X11" s="83">
         <f>W11*(1+$V$40)</f>
         <v>238663.34884261771</v>
       </c>
-      <c r="Y11" s="89">
+      <c r="Y11" s="83">
         <f>X11*(1+$V$40)</f>
         <v>267302.95070373185</v>
       </c>
-      <c r="Z11" s="90">
+      <c r="Z11" s="84">
         <f>Y11*(1+$V$40)</f>
         <v>299379.3047881797</v>
       </c>
@@ -4298,117 +4321,117 @@
     </row>
     <row r="12">
       <c r="B12" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="C12" s="88"/>
-      <c r="D12" s="88"/>
-      <c r="E12" s="88"/>
-      <c r="F12" s="88"/>
-      <c r="G12" s="88"/>
-      <c r="H12" s="88"/>
-      <c r="I12" s="88"/>
-      <c r="J12" s="88"/>
-      <c r="K12" s="82"/>
-      <c r="L12" s="83"/>
-      <c r="M12" s="83"/>
-      <c r="N12" s="83"/>
-      <c r="O12" s="83"/>
+        <v>363</v>
+      </c>
+      <c r="C12" s="82"/>
+      <c r="D12" s="82"/>
+      <c r="E12" s="82"/>
+      <c r="F12" s="82"/>
+      <c r="G12" s="82"/>
+      <c r="H12" s="82"/>
+      <c r="I12" s="82"/>
+      <c r="J12" s="82"/>
+      <c r="K12" s="79"/>
+      <c r="L12" s="79"/>
+      <c r="M12" s="79"/>
+      <c r="N12" s="79"/>
+      <c r="O12" s="79"/>
       <c r="U12" s="8"/>
       <c r="Z12" s="8"/>
     </row>
     <row r="13">
-      <c r="C13" s="88"/>
-      <c r="D13" s="88"/>
-      <c r="E13" s="88"/>
-      <c r="F13" s="88"/>
-      <c r="G13" s="88"/>
-      <c r="H13" s="88"/>
-      <c r="I13" s="88"/>
-      <c r="J13" s="88"/>
-      <c r="K13" s="82"/>
-      <c r="L13" s="83"/>
-      <c r="M13" s="83"/>
-      <c r="N13" s="83"/>
-      <c r="O13" s="83"/>
+      <c r="C13" s="82"/>
+      <c r="D13" s="82"/>
+      <c r="E13" s="82"/>
+      <c r="F13" s="82"/>
+      <c r="G13" s="82"/>
+      <c r="H13" s="82"/>
+      <c r="I13" s="82"/>
+      <c r="J13" s="82"/>
+      <c r="K13" s="79"/>
+      <c r="L13" s="79"/>
+      <c r="M13" s="79"/>
+      <c r="N13" s="79"/>
+      <c r="O13" s="79"/>
       <c r="U13" s="8"/>
       <c r="Z13" s="8"/>
     </row>
     <row r="14" s="1" customFormat="1">
       <c r="B14" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="C14" s="91">
+        <v>415</v>
+      </c>
+      <c r="C14" s="85">
         <v>3803.71</v>
       </c>
-      <c r="D14" s="91">
+      <c r="D14" s="85">
         <v>4634.3299999999999</v>
       </c>
-      <c r="E14" s="91">
+      <c r="E14" s="85">
         <v>6623.5600000000004</v>
       </c>
-      <c r="F14" s="91">
+      <c r="F14" s="85">
         <v>9473.2099999999991</v>
       </c>
-      <c r="G14" s="91">
+      <c r="G14" s="85">
         <v>9414</v>
       </c>
-      <c r="H14" s="91">
+      <c r="H14" s="85">
         <v>9748.2399999999998</v>
       </c>
-      <c r="I14" s="91">
+      <c r="I14" s="85">
         <v>12559.889999999999</v>
       </c>
-      <c r="J14" s="91">
+      <c r="J14" s="85">
         <v>18724.689999999999</v>
       </c>
-      <c r="K14" s="82">
+      <c r="K14" s="79">
         <v>24770.790000000001</v>
       </c>
-      <c r="L14" s="82"/>
-      <c r="M14" s="82"/>
-      <c r="N14" s="82"/>
-      <c r="O14" s="82"/>
-      <c r="P14" s="91">
+      <c r="L14" s="79"/>
+      <c r="M14" s="79"/>
+      <c r="N14" s="79"/>
+      <c r="O14" s="79"/>
+      <c r="P14" s="85">
         <f>P11*0.35</f>
         <v>28308.037379999998</v>
       </c>
-      <c r="Q14" s="91">
+      <c r="Q14" s="85">
         <f>Q11*0.35</f>
         <v>32837.323360799994</v>
       </c>
-      <c r="R14" s="91">
+      <c r="R14" s="85">
         <f>R11*0.35</f>
         <v>38091.295098527989</v>
       </c>
-      <c r="S14" s="91">
+      <c r="S14" s="85">
         <f>S11*0.35</f>
         <v>44185.902314292463</v>
       </c>
-      <c r="T14" s="91">
+      <c r="T14" s="85">
         <f>T11*0.35</f>
         <v>51255.64668457926</v>
       </c>
-      <c r="U14" s="92">
+      <c r="U14" s="86">
         <f>U11*0.35</f>
         <v>59456.55015411193</v>
       </c>
-      <c r="V14" s="91">
+      <c r="V14" s="85">
         <f>V11*0.35</f>
         <v>66591.33617260537</v>
       </c>
-      <c r="W14" s="91">
+      <c r="W14" s="85">
         <f>W11*0.35</f>
         <v>74582.296513318026</v>
       </c>
-      <c r="X14" s="91">
+      <c r="X14" s="85">
         <f>X11*0.35</f>
         <v>83532.172094916197</v>
       </c>
-      <c r="Y14" s="91">
+      <c r="Y14" s="85">
         <f>Y11*0.35</f>
         <v>93556.03274630614</v>
       </c>
-      <c r="Z14" s="92">
+      <c r="Z14" s="86">
         <f>Z11*0.35</f>
         <v>104782.75667586288</v>
       </c>
@@ -4417,1390 +4440,1390 @@
       <c r="DK14" s="1"/>
       <c r="DL14" s="1"/>
       <c r="DM14" s="1"/>
-      <c r="DN14" s="93">
+      <c r="DN14" s="87">
         <f>DN11*0.35</f>
         <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="s">
-        <v>484</v>
-      </c>
-      <c r="C15" s="86">
+        <v>489</v>
+      </c>
+      <c r="C15" s="78">
         <v>0</v>
       </c>
-      <c r="D15" s="81">
+      <c r="D15" s="78">
         <v>0</v>
       </c>
-      <c r="E15" s="81">
+      <c r="E15" s="78">
         <v>712.88</v>
       </c>
-      <c r="F15" s="81">
+      <c r="F15" s="78">
         <v>1056.3699999999999</v>
       </c>
-      <c r="G15" s="81">
+      <c r="G15" s="78">
         <v>1246.48</v>
       </c>
-      <c r="H15" s="81">
+      <c r="H15" s="78">
         <v>1745.55</v>
       </c>
-      <c r="I15" s="81">
+      <c r="I15" s="78">
         <v>1891.47</v>
       </c>
-      <c r="J15" s="81">
+      <c r="J15" s="78">
         <v>1931.5</v>
       </c>
-      <c r="K15" s="82">
+      <c r="K15" s="79">
         <v>2597.6599999999999</v>
       </c>
-      <c r="L15" s="82"/>
-      <c r="M15" s="82"/>
-      <c r="N15" s="82"/>
-      <c r="O15" s="82"/>
-      <c r="P15" s="81">
+      <c r="L15" s="79"/>
+      <c r="M15" s="79"/>
+      <c r="N15" s="79"/>
+      <c r="O15" s="79"/>
+      <c r="P15" s="78">
         <f>K15*1.06</f>
         <v>2753.5196000000001</v>
       </c>
-      <c r="Q15" s="88">
+      <c r="Q15" s="82">
         <f>P15*1.06</f>
         <v>2918.7307760000003</v>
       </c>
-      <c r="R15" s="88">
+      <c r="R15" s="82">
         <f>Q15*1.06</f>
         <v>3093.8546225600007</v>
       </c>
-      <c r="S15" s="88">
+      <c r="S15" s="82">
         <f>R15*1.06</f>
         <v>3279.4858999136009</v>
       </c>
-      <c r="T15" s="88">
+      <c r="T15" s="82">
         <f>S15*1.06</f>
         <v>3476.2550539084173</v>
       </c>
-      <c r="U15" s="94">
+      <c r="U15" s="88">
         <f>T15*1.06</f>
         <v>3684.8303571429224</v>
       </c>
-      <c r="V15" s="95">
+      <c r="V15" s="89">
         <f>U15*1.05</f>
         <v>3869.0718750000688</v>
       </c>
-      <c r="W15" s="95">
+      <c r="W15" s="89">
         <f>V15*1.05</f>
         <v>4062.5254687500724</v>
       </c>
-      <c r="X15" s="95">
+      <c r="X15" s="89">
         <f>W15*1.05</f>
         <v>4265.651742187576</v>
       </c>
-      <c r="Y15" s="95">
+      <c r="Y15" s="89">
         <f>X15*1.05</f>
         <v>4478.9343292969552</v>
       </c>
-      <c r="Z15" s="96">
+      <c r="Z15" s="90">
         <f>Y15*1.05</f>
         <v>4702.8810457618029</v>
       </c>
-      <c r="DN15" s="97">
+      <c r="DN15" s="91">
         <f>DM15*1.06</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" ht="14.25">
       <c r="A16" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="B16" t="s">
-        <v>486</v>
-      </c>
-      <c r="C16" s="86">
+        <v>491</v>
+      </c>
+      <c r="C16" s="78">
         <v>803.88999999999999</v>
       </c>
-      <c r="D16" s="81">
+      <c r="D16" s="78">
         <v>1045.1900000000001</v>
       </c>
-      <c r="E16" s="81">
+      <c r="E16" s="78">
         <v>1501.3499999999999</v>
       </c>
-      <c r="F16" s="81">
+      <c r="F16" s="78">
         <v>3929.48</v>
       </c>
-      <c r="G16" s="81">
+      <c r="G16" s="78">
         <v>5968.5799999999999</v>
       </c>
-      <c r="H16" s="81">
+      <c r="H16" s="78">
         <v>4803.3999999999996</v>
       </c>
-      <c r="I16" s="81">
+      <c r="I16" s="78">
         <v>3189.6500000000001</v>
       </c>
-      <c r="J16" s="81">
+      <c r="J16" s="78">
         <v>4630.6999999999998</v>
       </c>
-      <c r="K16" s="82">
+      <c r="K16" s="79">
         <v>7966.0299999999997</v>
       </c>
-      <c r="L16" s="82"/>
-      <c r="M16" s="82"/>
-      <c r="N16" s="82"/>
-      <c r="O16" s="82"/>
-      <c r="P16" s="95">
+      <c r="L16" s="79"/>
+      <c r="M16" s="79"/>
+      <c r="N16" s="79"/>
+      <c r="O16" s="79"/>
+      <c r="P16" s="89">
         <f>K16*1.1</f>
         <v>8762.6329999999998</v>
       </c>
-      <c r="Q16" s="98">
+      <c r="Q16" s="92">
         <f>P16*1.1</f>
         <v>9638.8963000000003</v>
       </c>
-      <c r="R16" s="98">
+      <c r="R16" s="92">
         <f>Q16*1.1</f>
         <v>10602.785930000002</v>
       </c>
-      <c r="S16" s="98">
+      <c r="S16" s="92">
         <f>R16*1.1</f>
         <v>11663.064523000003</v>
       </c>
-      <c r="T16" s="98">
+      <c r="T16" s="92">
         <f>S16*1.1</f>
         <v>12829.370975300004</v>
       </c>
-      <c r="U16" s="99">
+      <c r="U16" s="93">
         <f>T16*1.1</f>
         <v>14112.308072830005</v>
       </c>
-      <c r="V16" s="95">
+      <c r="V16" s="89">
         <f>U16*1.08</f>
         <v>15241.292718656407</v>
       </c>
-      <c r="W16" s="95">
+      <c r="W16" s="89">
         <f>V16*1.08</f>
         <v>16460.596136148921</v>
       </c>
-      <c r="X16" s="95">
+      <c r="X16" s="89">
         <f>W16*1.08</f>
         <v>17777.443827040835</v>
       </c>
-      <c r="Y16" s="95">
+      <c r="Y16" s="89">
         <f>X16*1.08</f>
         <v>19199.639333204104</v>
       </c>
-      <c r="Z16" s="96">
+      <c r="Z16" s="90">
         <f>Y16*1.08</f>
         <v>20735.610479860436</v>
       </c>
     </row>
     <row r="17" ht="14.25">
       <c r="B17" t="s">
-        <v>86</v>
-      </c>
-      <c r="C17" s="86">
+        <v>92</v>
+      </c>
+      <c r="C17" s="78">
         <v>931.66999999999996</v>
       </c>
-      <c r="D17" s="81">
+      <c r="D17" s="78">
         <v>1419.5899999999999</v>
       </c>
-      <c r="E17" s="81">
+      <c r="E17" s="78">
         <v>1938.53</v>
       </c>
-      <c r="F17" s="81">
+      <c r="F17" s="78">
         <v>2549.0799999999999</v>
       </c>
-      <c r="G17" s="81">
+      <c r="G17" s="78">
         <v>2498.6700000000001</v>
       </c>
-      <c r="H17" s="81">
+      <c r="H17" s="78">
         <v>3589.6599999999999</v>
       </c>
-      <c r="I17" s="81">
+      <c r="I17" s="78">
         <v>5100.1899999999996</v>
       </c>
-      <c r="J17" s="81">
+      <c r="J17" s="78">
         <v>6396.0100000000002</v>
       </c>
-      <c r="K17" s="82">
+      <c r="K17" s="79">
         <v>7508.3400000000001</v>
       </c>
-      <c r="L17" s="82"/>
-      <c r="M17" s="82"/>
-      <c r="N17" s="82"/>
-      <c r="O17" s="82"/>
-      <c r="P17" s="95">
-        <f>K17*1.15</f>
+      <c r="L17" s="79"/>
+      <c r="M17" s="79"/>
+      <c r="N17" s="79"/>
+      <c r="O17" s="79"/>
+      <c r="P17" s="89">
+        <f t="shared" ref="P17:P18" si="23">K17*1.15</f>
         <v>8634.5910000000003</v>
       </c>
-      <c r="Q17" s="98">
-        <f>P17*1.15</f>
+      <c r="Q17" s="92">
+        <f t="shared" ref="Q17:Q18" si="24">P17*1.15</f>
         <v>9929.7796500000004</v>
       </c>
-      <c r="R17" s="98">
-        <f>Q17*1.15</f>
+      <c r="R17" s="92">
+        <f t="shared" ref="R17:R18" si="25">Q17*1.15</f>
         <v>11419.2465975</v>
       </c>
-      <c r="S17" s="98">
-        <f>R17*1.15</f>
+      <c r="S17" s="92">
+        <f t="shared" ref="S17:S18" si="26">R17*1.15</f>
         <v>13132.133587124998</v>
       </c>
-      <c r="T17" s="98">
-        <f>S17*1.15</f>
+      <c r="T17" s="92">
+        <f t="shared" ref="T17:T18" si="27">S17*1.15</f>
         <v>15101.953625193746</v>
       </c>
-      <c r="U17" s="99">
-        <f>T17*1.15</f>
+      <c r="U17" s="93">
+        <f t="shared" ref="U17:U18" si="28">T17*1.15</f>
         <v>17367.246668972806</v>
       </c>
-      <c r="V17" s="95">
+      <c r="V17" s="89">
         <f>U17*1.06</f>
         <v>18409.281469111174</v>
       </c>
-      <c r="W17" s="95">
+      <c r="W17" s="89">
         <f>V17*1.06</f>
         <v>19513.838357257846</v>
       </c>
-      <c r="X17" s="95">
+      <c r="X17" s="89">
         <f>W17*1.06</f>
         <v>20684.668658693317</v>
       </c>
-      <c r="Y17" s="95">
+      <c r="Y17" s="89">
         <f>X17*1.06</f>
         <v>21925.748778214918</v>
       </c>
-      <c r="Z17" s="96">
+      <c r="Z17" s="90">
         <f>Y17*1.06</f>
         <v>23241.293704907814</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="s">
-        <v>184</v>
-      </c>
-      <c r="C18" s="86">
+        <v>190</v>
+      </c>
+      <c r="C18" s="78">
         <v>71.170000000000002</v>
       </c>
-      <c r="D18" s="81">
+      <c r="D18" s="78">
         <v>102.06999999999999</v>
       </c>
-      <c r="E18" s="81">
+      <c r="E18" s="78">
         <v>144.15000000000001</v>
       </c>
-      <c r="F18" s="81">
+      <c r="F18" s="78">
         <v>294.63</v>
       </c>
-      <c r="G18" s="81">
+      <c r="G18" s="78">
         <v>325.26999999999998</v>
       </c>
-      <c r="H18" s="81">
+      <c r="H18" s="78">
         <v>384.56999999999999</v>
       </c>
-      <c r="I18" s="81">
+      <c r="I18" s="78">
         <v>485.38</v>
       </c>
-      <c r="J18" s="81">
+      <c r="J18" s="78">
         <v>683.32000000000005</v>
       </c>
-      <c r="K18" s="82">
+      <c r="K18" s="79">
         <v>880.99000000000001</v>
       </c>
-      <c r="L18" s="82"/>
-      <c r="M18" s="82"/>
-      <c r="N18" s="82"/>
-      <c r="O18" s="82"/>
-      <c r="P18" s="95">
-        <f>K18*1.15</f>
+      <c r="L18" s="79"/>
+      <c r="M18" s="79"/>
+      <c r="N18" s="79"/>
+      <c r="O18" s="79"/>
+      <c r="P18" s="89">
+        <f t="shared" si="23"/>
         <v>1013.1384999999999</v>
       </c>
-      <c r="Q18" s="98">
-        <f>P18*1.15</f>
+      <c r="Q18" s="92">
+        <f t="shared" si="24"/>
         <v>1165.1092749999998</v>
       </c>
-      <c r="R18" s="98">
-        <f>Q18*1.15</f>
+      <c r="R18" s="92">
+        <f t="shared" si="25"/>
         <v>1339.8756662499998</v>
       </c>
-      <c r="S18" s="98">
-        <f>R18*1.15</f>
+      <c r="S18" s="92">
+        <f t="shared" si="26"/>
         <v>1540.8570161874995</v>
       </c>
-      <c r="T18" s="98">
-        <f>S18*1.15</f>
+      <c r="T18" s="92">
+        <f t="shared" si="27"/>
         <v>1771.9855686156243</v>
       </c>
-      <c r="U18" s="99">
-        <f>T18*1.15</f>
+      <c r="U18" s="93">
+        <f t="shared" si="28"/>
         <v>2037.7834039079678</v>
       </c>
-      <c r="V18" s="95">
+      <c r="V18" s="89">
         <f>U18*1.1</f>
         <v>2241.5617442987646</v>
       </c>
-      <c r="W18" s="95">
+      <c r="W18" s="89">
         <f>V18*1.1</f>
         <v>2465.7179187286411</v>
       </c>
-      <c r="X18" s="95">
+      <c r="X18" s="89">
         <f>W18*1.1</f>
         <v>2712.2897106015052</v>
       </c>
-      <c r="Y18" s="95">
+      <c r="Y18" s="89">
         <f>X18*1.1</f>
         <v>2983.518681661656</v>
       </c>
-      <c r="Z18" s="96">
+      <c r="Z18" s="90">
         <f>Y18*1.1</f>
         <v>3281.8705498278218</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="s">
-        <v>185</v>
-      </c>
-      <c r="C19" s="86">
+        <v>191</v>
+      </c>
+      <c r="C19" s="78">
         <v>1564.3399999999999</v>
       </c>
-      <c r="D19" s="81">
+      <c r="D19" s="78">
         <v>2168.5300000000002</v>
       </c>
-      <c r="E19" s="81">
+      <c r="E19" s="78">
         <v>1400.55</v>
       </c>
-      <c r="F19" s="81">
+      <c r="F19" s="78">
         <v>1760.74</v>
       </c>
-      <c r="G19" s="81">
+      <c r="G19" s="78">
         <v>1237.79</v>
       </c>
-      <c r="H19" s="81">
+      <c r="H19" s="78">
         <v>1865.21</v>
       </c>
-      <c r="I19" s="81">
+      <c r="I19" s="78">
         <v>2665.4899999999998</v>
       </c>
-      <c r="J19" s="81">
+      <c r="J19" s="78">
         <v>3314.3600000000001</v>
       </c>
-      <c r="K19" s="82">
+      <c r="K19" s="79">
         <v>3939.1500000000001</v>
       </c>
-      <c r="L19" s="82"/>
-      <c r="M19" s="82"/>
-      <c r="N19" s="82"/>
-      <c r="O19" s="82"/>
-      <c r="P19" s="95">
+      <c r="L19" s="79"/>
+      <c r="M19" s="79"/>
+      <c r="N19" s="79"/>
+      <c r="O19" s="79"/>
+      <c r="P19" s="89">
         <f>K19*1.2</f>
         <v>4726.9799999999996</v>
       </c>
-      <c r="Q19" s="98">
+      <c r="Q19" s="92">
         <f>P19*1.2</f>
         <v>5672.3759999999993</v>
       </c>
-      <c r="R19" s="98">
+      <c r="R19" s="92">
         <f>Q19*1.2</f>
         <v>6806.8511999999992</v>
       </c>
-      <c r="S19" s="98">
+      <c r="S19" s="92">
         <f>R19*1.2</f>
         <v>8168.2214399999984</v>
       </c>
-      <c r="T19" s="98">
+      <c r="T19" s="92">
         <f>S19*1.2</f>
         <v>9801.865727999997</v>
       </c>
-      <c r="U19" s="99">
+      <c r="U19" s="93">
         <f>T19*1.2</f>
         <v>11762.238873599996</v>
       </c>
-      <c r="V19" s="95">
+      <c r="V19" s="89">
         <f>U19*1.14</f>
         <v>13408.952315903995</v>
       </c>
-      <c r="W19" s="95">
+      <c r="W19" s="89">
         <f>V19*1.14</f>
         <v>15286.205640130553</v>
       </c>
-      <c r="X19" s="95">
+      <c r="X19" s="89">
         <f>W19*1.14</f>
         <v>17426.274429748828</v>
       </c>
-      <c r="Y19" s="95">
+      <c r="Y19" s="89">
         <f>X19*1.14</f>
         <v>19865.952849913661</v>
       </c>
-      <c r="Z19" s="96">
+      <c r="Z19" s="90">
         <f>Y19*1.14</f>
         <v>22647.186248901573</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1">
       <c r="B20" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="C20" s="91">
+        <v>492</v>
+      </c>
+      <c r="C20" s="85">
         <f>SUM(C14:C19)</f>
         <v>7174.7800000000007</v>
       </c>
-      <c r="D20" s="91">
+      <c r="D20" s="85">
         <f>SUM(D14:D19)</f>
         <v>9369.7100000000009</v>
       </c>
-      <c r="E20" s="91">
+      <c r="E20" s="85">
         <f>SUM(E14:E19)</f>
         <v>12321.02</v>
       </c>
-      <c r="F20" s="91">
+      <c r="F20" s="85">
         <f>SUM(F14:F19)</f>
         <v>19063.510000000002</v>
       </c>
-      <c r="G20" s="91">
+      <c r="G20" s="85">
         <f>SUM(G14:G19)</f>
         <v>20690.789999999997</v>
       </c>
-      <c r="H20" s="91">
+      <c r="H20" s="85">
         <f>SUM(H14:H19)</f>
         <v>22136.629999999997</v>
       </c>
-      <c r="I20" s="91">
+      <c r="I20" s="85">
         <f>SUM(I14:I19)</f>
         <v>25892.07</v>
       </c>
-      <c r="J20" s="91">
+      <c r="J20" s="85">
         <f>SUM(J14:J19)</f>
         <v>35680.580000000002</v>
       </c>
-      <c r="K20" s="91">
+      <c r="K20" s="85">
         <f>SUM(K14:K19)</f>
         <v>47662.960000000006</v>
       </c>
-      <c r="L20" s="82"/>
-      <c r="M20" s="82"/>
-      <c r="N20" s="82"/>
-      <c r="O20" s="82"/>
-      <c r="P20" s="91">
+      <c r="L20" s="79"/>
+      <c r="M20" s="79"/>
+      <c r="N20" s="79"/>
+      <c r="O20" s="79"/>
+      <c r="P20" s="85">
         <f>SUM(P14:P19)</f>
         <v>54198.899479999993</v>
       </c>
-      <c r="Q20" s="91">
+      <c r="Q20" s="85">
         <f>SUM(Q14:Q19)</f>
         <v>62162.215361800001</v>
       </c>
-      <c r="R20" s="91">
+      <c r="R20" s="85">
         <f>SUM(R14:R19)</f>
         <v>71353.909114837996</v>
       </c>
-      <c r="S20" s="91">
+      <c r="S20" s="85">
         <f>SUM(S14:S19)</f>
         <v>81969.664780518549</v>
       </c>
-      <c r="T20" s="91">
+      <c r="T20" s="85">
         <f>SUM(T14:T19)</f>
         <v>94237.07763559703</v>
       </c>
-      <c r="U20" s="92">
+      <c r="U20" s="86">
         <f>SUM(U14:U19)</f>
         <v>108420.95753056562</v>
       </c>
-      <c r="V20" s="91">
+      <c r="V20" s="85">
         <f>SUM(V14:V19)</f>
         <v>119761.49629557578</v>
       </c>
-      <c r="W20" s="91">
+      <c r="W20" s="85">
         <f>SUM(W14:W19)</f>
         <v>132371.18003433404</v>
       </c>
-      <c r="X20" s="91">
+      <c r="X20" s="85">
         <f>SUM(X14:X19)</f>
         <v>146398.50046318825</v>
       </c>
-      <c r="Y20" s="91">
+      <c r="Y20" s="85">
         <f>SUM(Y14:Y19)</f>
         <v>162009.82671859744</v>
       </c>
-      <c r="Z20" s="92">
+      <c r="Z20" s="86">
         <f>SUM(Z14:Z19)</f>
         <v>179391.59870512231</v>
       </c>
     </row>
     <row r="21">
-      <c r="C21" s="81"/>
-      <c r="D21" s="81"/>
-      <c r="E21" s="81"/>
-      <c r="F21" s="81"/>
-      <c r="G21" s="81"/>
-      <c r="H21" s="81"/>
-      <c r="I21" s="81"/>
-      <c r="J21" s="81"/>
-      <c r="K21" s="82"/>
-      <c r="L21" s="82"/>
-      <c r="M21" s="82"/>
-      <c r="N21" s="82"/>
-      <c r="O21" s="82"/>
-      <c r="P21" s="95"/>
-      <c r="Q21" s="95"/>
-      <c r="R21" s="95"/>
-      <c r="S21" s="95"/>
-      <c r="T21" s="95"/>
-      <c r="U21" s="96"/>
-      <c r="V21" s="95"/>
-      <c r="W21" s="95"/>
-      <c r="X21" s="95"/>
-      <c r="Y21" s="95"/>
-      <c r="Z21" s="96"/>
+      <c r="C21" s="78"/>
+      <c r="D21" s="78"/>
+      <c r="E21" s="78"/>
+      <c r="F21" s="78"/>
+      <c r="G21" s="78"/>
+      <c r="H21" s="78"/>
+      <c r="I21" s="78"/>
+      <c r="J21" s="78"/>
+      <c r="K21" s="79"/>
+      <c r="L21" s="79"/>
+      <c r="M21" s="79"/>
+      <c r="N21" s="79"/>
+      <c r="O21" s="79"/>
+      <c r="P21" s="89"/>
+      <c r="Q21" s="89"/>
+      <c r="R21" s="89"/>
+      <c r="S21" s="89"/>
+      <c r="T21" s="89"/>
+      <c r="U21" s="90"/>
+      <c r="V21" s="89"/>
+      <c r="W21" s="89"/>
+      <c r="X21" s="89"/>
+      <c r="Y21" s="89"/>
+      <c r="Z21" s="90"/>
     </row>
     <row r="22">
       <c r="B22" t="s">
-        <v>488</v>
-      </c>
-      <c r="C22" s="86">
+        <v>493</v>
+      </c>
+      <c r="C22" s="78">
         <v>0</v>
       </c>
-      <c r="D22" s="81">
+      <c r="D22" s="78">
         <v>0</v>
       </c>
-      <c r="E22" s="81">
+      <c r="E22" s="78">
         <v>0</v>
       </c>
-      <c r="F22" s="81">
+      <c r="F22" s="78">
         <v>0</v>
       </c>
-      <c r="G22" s="81">
+      <c r="G22" s="78">
         <v>0</v>
       </c>
-      <c r="H22" s="81">
+      <c r="H22" s="78">
         <v>0</v>
       </c>
-      <c r="I22" s="81">
+      <c r="I22" s="78">
         <v>1.6699999999999999</v>
       </c>
-      <c r="J22" s="81">
+      <c r="J22" s="78">
         <v>7.6399999999999997</v>
       </c>
-      <c r="K22" s="82">
+      <c r="K22" s="79">
         <v>17.809999999999999</v>
       </c>
-      <c r="L22" s="82"/>
-      <c r="M22" s="82"/>
-      <c r="N22" s="82"/>
-      <c r="O22" s="82"/>
-      <c r="P22" s="95">
+      <c r="L22" s="79"/>
+      <c r="M22" s="79"/>
+      <c r="N22" s="79"/>
+      <c r="O22" s="79"/>
+      <c r="P22" s="89">
         <v>0</v>
       </c>
-      <c r="Q22" s="98">
+      <c r="Q22" s="92">
         <v>0</v>
       </c>
-      <c r="R22" s="98">
+      <c r="R22" s="92">
         <v>0</v>
       </c>
-      <c r="S22" s="98">
+      <c r="S22" s="92">
         <v>0</v>
       </c>
-      <c r="T22" s="98">
+      <c r="T22" s="92">
         <v>0</v>
       </c>
-      <c r="U22" s="96"/>
-      <c r="V22" s="95"/>
-      <c r="W22" s="95"/>
-      <c r="X22" s="95"/>
-      <c r="Y22" s="95"/>
-      <c r="Z22" s="96"/>
+      <c r="U22" s="90"/>
+      <c r="V22" s="89"/>
+      <c r="W22" s="89"/>
+      <c r="X22" s="89"/>
+      <c r="Y22" s="89"/>
+      <c r="Z22" s="90"/>
     </row>
     <row r="23" ht="14.25">
       <c r="B23" t="s">
-        <v>90</v>
-      </c>
-      <c r="C23" s="86">
+        <v>96</v>
+      </c>
+      <c r="C23" s="78">
         <f>C11-C20+C22</f>
         <v>2817.409999999998</v>
       </c>
-      <c r="D23" s="81">
+      <c r="D23" s="78">
         <f>D11-D20+D22</f>
         <v>4096.2000000000007</v>
       </c>
-      <c r="E23" s="81">
+      <c r="E23" s="78">
         <f>E11-E20+E22</f>
         <v>6179.1599999999999</v>
       </c>
-      <c r="F23" s="81">
+      <c r="F23" s="78">
         <f>F11-F20+F22</f>
         <v>7322.1200000000026</v>
       </c>
-      <c r="G23" s="81">
+      <c r="G23" s="78">
         <f>G11-G20+G22</f>
         <v>5992.2400000000052</v>
       </c>
-      <c r="H23" s="81">
+      <c r="H23" s="78">
         <f>H11-H20+H22</f>
         <v>9503.7800000000025</v>
       </c>
-      <c r="I23" s="81">
+      <c r="I23" s="78">
         <f>I11-I20+I22</f>
         <v>15527.859999999995</v>
       </c>
-      <c r="J23" s="81">
+      <c r="J23" s="78">
         <f>J11-J20+J22</f>
         <v>19309.569999999992</v>
       </c>
-      <c r="K23" s="81">
+      <c r="K23" s="78">
         <f>K11-K20+K22</f>
         <v>22079.079999999991</v>
       </c>
-      <c r="L23" s="82"/>
-      <c r="M23" s="82"/>
-      <c r="N23" s="82"/>
-      <c r="O23" s="82"/>
-      <c r="P23" s="81">
+      <c r="L23" s="79"/>
+      <c r="M23" s="79"/>
+      <c r="N23" s="79"/>
+      <c r="O23" s="79"/>
+      <c r="P23" s="78">
         <f>P11-P20+P22</f>
         <v>26681.207320000001</v>
       </c>
-      <c r="Q23" s="81">
+      <c r="Q23" s="78">
         <f>Q11-Q20+Q22</f>
         <v>31658.708526199989</v>
       </c>
-      <c r="R23" s="81">
+      <c r="R23" s="78">
         <f>R11-R20+R22</f>
         <v>37478.362595241982</v>
       </c>
-      <c r="S23" s="81">
+      <c r="S23" s="78">
         <f>S11-S20+S22</f>
         <v>44275.770403174218</v>
       </c>
-      <c r="T23" s="81">
+      <c r="T23" s="78">
         <f>T11-T20+T22</f>
         <v>52207.627177486575</v>
       </c>
-      <c r="U23" s="100">
+      <c r="U23" s="94">
         <f>U11-U20+U22</f>
         <v>61454.900052611338</v>
       </c>
-      <c r="V23" s="81">
+      <c r="V23" s="78">
         <f>V11-V20+V22</f>
         <v>70499.46419758242</v>
       </c>
-      <c r="W23" s="81">
+      <c r="W23" s="78">
         <f>W11-W20+W22</f>
         <v>80721.095718003169</v>
       </c>
-      <c r="X23" s="81">
+      <c r="X23" s="78">
         <f>X11-X20+X22</f>
         <v>92264.848379429459</v>
       </c>
-      <c r="Y23" s="81">
+      <c r="Y23" s="78">
         <f>Y11-Y20+Y22</f>
         <v>105293.12398513441</v>
       </c>
-      <c r="Z23" s="100">
+      <c r="Z23" s="94">
         <f>Z11-Z20+Z22</f>
         <v>119987.70608305739</v>
       </c>
     </row>
     <row r="24" ht="14.25">
       <c r="B24" t="s">
-        <v>91</v>
-      </c>
-      <c r="C24" s="86">
+        <v>97</v>
+      </c>
+      <c r="C24" s="78">
         <v>-981.02999999999997</v>
       </c>
-      <c r="D24" s="81">
+      <c r="D24" s="78">
         <v>-1422.0899999999999</v>
       </c>
-      <c r="E24" s="81">
+      <c r="E24" s="78">
         <v>-2184.1700000000001</v>
       </c>
-      <c r="F24" s="81">
+      <c r="F24" s="78">
         <v>-2058.3699999999999</v>
       </c>
-      <c r="G24" s="81">
+      <c r="G24" s="78">
         <f>-1660.26+87.82</f>
         <v>-1572.4400000000001</v>
       </c>
-      <c r="H24" s="81">
+      <c r="H24" s="78">
         <f>-2497.45+21.9</f>
         <v>-2475.5499999999997</v>
       </c>
-      <c r="I24" s="81">
+      <c r="I24" s="78">
         <f>-3998.18-21.99</f>
         <v>-4020.1699999999996</v>
       </c>
-      <c r="J24" s="81">
+      <c r="J24" s="78">
         <f>-4957.72+99.32</f>
         <v>-4858.4000000000005</v>
       </c>
-      <c r="K24" s="101">
+      <c r="K24" s="79">
         <f>5300.15*-1</f>
         <v>-5300.1499999999996</v>
       </c>
-      <c r="L24" s="82"/>
-      <c r="M24" s="82"/>
-      <c r="N24" s="82"/>
-      <c r="O24" s="82"/>
-      <c r="P24" s="95">
+      <c r="L24" s="79"/>
+      <c r="M24" s="79"/>
+      <c r="N24" s="79"/>
+      <c r="O24" s="79"/>
+      <c r="P24" s="89">
         <f ca="1">-P23*$Q$48</f>
         <v>-6670.3018300000003</v>
       </c>
-      <c r="Q24" s="95">
+      <c r="Q24" s="89">
         <f>-Q23*$Q$48</f>
         <v>-7914.6771315499973</v>
       </c>
-      <c r="R24" s="95">
+      <c r="R24" s="89">
         <f>-R23*$Q$48</f>
         <v>-9369.5906488104956</v>
       </c>
-      <c r="S24" s="95">
+      <c r="S24" s="89">
         <f>-S23*$Q$48</f>
         <v>-11068.942600793554</v>
       </c>
-      <c r="T24" s="95">
+      <c r="T24" s="89">
         <f>-T23*$Q$48</f>
         <v>-13051.906794371644</v>
       </c>
-      <c r="U24" s="96">
+      <c r="U24" s="90">
         <f>-U23*$Q$48</f>
         <v>-15363.725013152834</v>
       </c>
-      <c r="V24" s="95">
+      <c r="V24" s="89">
         <f ca="1">-V23*$Q$48</f>
         <v>-17624.866049395605</v>
       </c>
-      <c r="W24" s="95">
+      <c r="W24" s="89">
         <f>-W23*$Q$48</f>
         <v>-20180.273929500792</v>
       </c>
-      <c r="X24" s="95">
+      <c r="X24" s="89">
         <f>-X23*$Q$48</f>
         <v>-23066.212094857365</v>
       </c>
-      <c r="Y24" s="95">
+      <c r="Y24" s="89">
         <f>-Y23*$Q$48</f>
         <v>-26323.280996283604</v>
       </c>
-      <c r="Z24" s="96">
+      <c r="Z24" s="90">
         <f>-Z23*$Q$48</f>
         <v>-29996.926520764348</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="14.25">
       <c r="B25" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C25" s="91">
+        <v>98</v>
+      </c>
+      <c r="C25" s="85">
         <f>C23+C24</f>
         <v>1836.3799999999981</v>
       </c>
-      <c r="D25" s="91">
+      <c r="D25" s="85">
         <f>D23+D24</f>
         <v>2674.1100000000006</v>
       </c>
-      <c r="E25" s="91">
+      <c r="E25" s="85">
         <f>E23+E24</f>
         <v>3994.9899999999998</v>
       </c>
-      <c r="F25" s="91">
+      <c r="F25" s="85">
         <f>F23+F24</f>
         <v>5263.7500000000027</v>
       </c>
-      <c r="G25" s="91">
+      <c r="G25" s="85">
         <f>G23+G24</f>
         <v>4419.8000000000047</v>
       </c>
-      <c r="H25" s="91">
+      <c r="H25" s="85">
         <f>H23+H24</f>
         <v>7028.2300000000032</v>
       </c>
-      <c r="I25" s="91">
+      <c r="I25" s="85">
         <f>I23+I24</f>
         <v>11507.689999999995</v>
       </c>
-      <c r="J25" s="91">
+      <c r="J25" s="85">
         <f>J23+J24</f>
         <v>14451.169999999991</v>
       </c>
-      <c r="K25" s="91">
+      <c r="K25" s="85">
         <f>K23+K24</f>
         <v>16778.929999999993</v>
       </c>
-      <c r="L25" s="82"/>
-      <c r="M25" s="82"/>
-      <c r="N25" s="82"/>
-      <c r="O25" s="82"/>
-      <c r="P25" s="91">
+      <c r="L25" s="79"/>
+      <c r="M25" s="79"/>
+      <c r="N25" s="79"/>
+      <c r="O25" s="79"/>
+      <c r="P25" s="85">
         <f>P23+P24</f>
         <v>20010.905490000001</v>
       </c>
-      <c r="Q25" s="91">
+      <c r="Q25" s="85">
         <f>Q23+Q24</f>
         <v>23744.031394649992</v>
       </c>
-      <c r="R25" s="91">
+      <c r="R25" s="85">
         <f>R23+R24</f>
         <v>28108.771946431487</v>
       </c>
-      <c r="S25" s="91">
+      <c r="S25" s="85">
         <f>S23+S24</f>
         <v>33206.827802380663</v>
       </c>
-      <c r="T25" s="91">
+      <c r="T25" s="85">
         <f>T23+T24</f>
         <v>39155.720383114931</v>
       </c>
-      <c r="U25" s="92">
+      <c r="U25" s="86">
         <f>U23+U24</f>
         <v>46091.175039458503</v>
       </c>
-      <c r="V25" s="91">
+      <c r="V25" s="85">
         <f>V23+V24</f>
         <v>52874.598148186815</v>
       </c>
-      <c r="W25" s="91">
+      <c r="W25" s="85">
         <f>W23+W24</f>
         <v>60540.821788502377</v>
       </c>
-      <c r="X25" s="91">
+      <c r="X25" s="85">
         <f>X23+X24</f>
         <v>69198.636284572101</v>
       </c>
-      <c r="Y25" s="91">
+      <c r="Y25" s="85">
         <f>Y23+Y24</f>
         <v>78969.842988850811</v>
       </c>
-      <c r="Z25" s="92">
+      <c r="Z25" s="86">
         <f>Z23+Z24</f>
         <v>89990.779562293043</v>
       </c>
     </row>
     <row r="26" ht="14.25">
       <c r="B26" t="s">
-        <v>230</v>
-      </c>
-      <c r="C26" s="86">
+        <v>236</v>
+      </c>
+      <c r="C26" s="78">
         <v>0</v>
       </c>
-      <c r="D26" s="81">
+      <c r="D26" s="78">
         <v>0</v>
       </c>
-      <c r="E26" s="81">
+      <c r="E26" s="78">
         <v>0</v>
       </c>
-      <c r="F26" s="81">
+      <c r="F26" s="78">
         <v>0</v>
       </c>
-      <c r="G26" s="81">
+      <c r="G26" s="78">
         <v>0</v>
       </c>
-      <c r="H26" s="81">
+      <c r="H26" s="78">
         <v>34.270000000000003</v>
       </c>
-      <c r="I26" s="81">
+      <c r="I26" s="78">
         <v>-22.84</v>
       </c>
-      <c r="J26" s="81">
+      <c r="J26" s="78">
         <v>89.540000000000006</v>
       </c>
-      <c r="K26" s="82">
+      <c r="K26" s="79">
         <f>J26</f>
         <v>89.540000000000006</v>
       </c>
-      <c r="L26" s="83"/>
-      <c r="M26" s="83"/>
-      <c r="N26" s="83"/>
-      <c r="O26" s="83"/>
+      <c r="L26" s="79"/>
+      <c r="M26" s="79"/>
+      <c r="N26" s="79"/>
+      <c r="O26" s="79"/>
       <c r="U26" s="8"/>
       <c r="V26" s="7"/>
       <c r="W26" s="7"/>
       <c r="X26" s="7"/>
       <c r="Y26" s="7"/>
-      <c r="Z26" s="80"/>
+      <c r="Z26" s="77"/>
     </row>
     <row r="27" ht="14.25">
-      <c r="D27" s="81"/>
-      <c r="E27" s="81"/>
-      <c r="F27" s="81"/>
-      <c r="G27" s="81"/>
-      <c r="H27" s="81"/>
-      <c r="I27" s="81"/>
-      <c r="J27" s="81"/>
-      <c r="K27" s="82"/>
-      <c r="L27" s="83"/>
-      <c r="M27" s="83"/>
-      <c r="N27" s="83"/>
-      <c r="O27" s="83"/>
+      <c r="D27" s="78"/>
+      <c r="E27" s="78"/>
+      <c r="F27" s="78"/>
+      <c r="G27" s="78"/>
+      <c r="H27" s="78"/>
+      <c r="I27" s="78"/>
+      <c r="J27" s="78"/>
+      <c r="K27" s="79"/>
+      <c r="L27" s="79"/>
+      <c r="M27" s="79"/>
+      <c r="N27" s="79"/>
+      <c r="O27" s="79"/>
       <c r="U27" s="8"/>
       <c r="V27" s="7"/>
       <c r="W27" s="7"/>
       <c r="X27" s="7"/>
       <c r="Y27" s="7"/>
-      <c r="Z27" s="80"/>
+      <c r="Z27" s="77"/>
     </row>
     <row r="28" s="1" customFormat="1" ht="14.25">
       <c r="B28" s="1" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="C28" s="1"/>
-      <c r="D28" s="91">
+      <c r="D28" s="85">
         <f>D25+D26</f>
         <v>2674.1100000000006</v>
       </c>
-      <c r="E28" s="91">
+      <c r="E28" s="85">
         <f>E25+E26</f>
         <v>3994.9899999999998</v>
       </c>
-      <c r="F28" s="91">
+      <c r="F28" s="85">
         <f>F25+F26</f>
         <v>5263.7500000000027</v>
       </c>
-      <c r="G28" s="91">
+      <c r="G28" s="85">
         <f>G25+G26</f>
         <v>4419.8000000000047</v>
       </c>
-      <c r="H28" s="91">
+      <c r="H28" s="85">
         <f>H25+H26</f>
         <v>7062.5000000000036</v>
       </c>
-      <c r="I28" s="91">
+      <c r="I28" s="85">
         <f>I25+I26</f>
         <v>11484.849999999995</v>
       </c>
-      <c r="J28" s="91">
+      <c r="J28" s="85">
         <f>J25+J26</f>
         <v>14540.709999999992</v>
       </c>
-      <c r="K28" s="82">
-        <f>J28</f>
+      <c r="K28" s="79">
+        <f t="shared" ref="K28:K36" si="29">J28</f>
         <v>14540.709999999992</v>
       </c>
-      <c r="L28" s="82"/>
-      <c r="M28" s="82"/>
-      <c r="N28" s="82"/>
-      <c r="O28" s="82"/>
-      <c r="P28" s="102">
+      <c r="L28" s="79"/>
+      <c r="M28" s="79"/>
+      <c r="N28" s="79"/>
+      <c r="O28" s="79"/>
+      <c r="P28" s="95">
         <f>P25</f>
         <v>20010.905490000001</v>
       </c>
-      <c r="Q28" s="102">
+      <c r="Q28" s="95">
         <f>Q25</f>
         <v>23744.031394649992</v>
       </c>
-      <c r="R28" s="102">
+      <c r="R28" s="95">
         <f>R25</f>
         <v>28108.771946431487</v>
       </c>
-      <c r="S28" s="102">
+      <c r="S28" s="95">
         <f>S25</f>
         <v>33206.827802380663</v>
       </c>
-      <c r="T28" s="102">
+      <c r="T28" s="95">
         <f>T25</f>
         <v>39155.720383114931</v>
       </c>
-      <c r="U28" s="103">
+      <c r="U28" s="96">
         <f>U25</f>
         <v>46091.175039458503</v>
       </c>
-      <c r="V28" s="102">
+      <c r="V28" s="95">
         <f>V25</f>
         <v>52874.598148186815</v>
       </c>
-      <c r="W28" s="102">
+      <c r="W28" s="95">
         <f>W25</f>
         <v>60540.821788502377</v>
       </c>
-      <c r="X28" s="102">
+      <c r="X28" s="95">
         <f>X25</f>
         <v>69198.636284572101</v>
       </c>
-      <c r="Y28" s="102">
+      <c r="Y28" s="95">
         <f>Y25</f>
         <v>78969.842988850811</v>
       </c>
-      <c r="Z28" s="103">
+      <c r="Z28" s="96">
         <f>Z25</f>
         <v>89990.779562293043</v>
       </c>
-      <c r="AA28" s="102">
+      <c r="AA28" s="95">
         <f>Z28+Z28*$AB$32</f>
         <v>90890.687357915973</v>
       </c>
-      <c r="AB28" s="102">
+      <c r="AB28" s="95">
         <f>AA28+AA28*$AB$32</f>
         <v>91799.594231495139</v>
       </c>
-      <c r="AC28" s="102">
+      <c r="AC28" s="95">
         <f>AB28+AB28*$AB$32</f>
         <v>92717.590173810095</v>
       </c>
-      <c r="AD28" s="102">
+      <c r="AD28" s="95">
         <f>AC28+AC28*$AB$32</f>
         <v>93644.766075548192</v>
       </c>
-      <c r="AE28" s="102">
+      <c r="AE28" s="95">
         <f>AD28+AD28*$AB$32</f>
         <v>94581.213736303675</v>
       </c>
-      <c r="AF28" s="102">
+      <c r="AF28" s="95">
         <f>AE28+AE28*$AB$32</f>
         <v>95527.025873666717</v>
       </c>
-      <c r="AG28" s="102">
+      <c r="AG28" s="95">
         <f>AF28+AF28*$AB$32</f>
         <v>96482.296132403382</v>
       </c>
-      <c r="AH28" s="102">
+      <c r="AH28" s="95">
         <f>AG28+AG28*$AB$32</f>
         <v>97447.119093727422</v>
       </c>
-      <c r="AI28" s="102">
+      <c r="AI28" s="95">
         <f>AH28+AH28*$AB$32</f>
         <v>98421.590284664693</v>
       </c>
-      <c r="AJ28" s="102">
+      <c r="AJ28" s="95">
         <f>AI28+AI28*$AB$32</f>
         <v>99405.806187511334</v>
       </c>
-      <c r="AK28" s="102">
+      <c r="AK28" s="95">
         <f>AJ28+AJ28*$AB$32</f>
         <v>100399.86424938645</v>
       </c>
-      <c r="AL28" s="102">
+      <c r="AL28" s="95">
         <f>AK28+AK28*$AB$32</f>
         <v>101403.86289188032</v>
       </c>
-      <c r="AM28" s="102">
+      <c r="AM28" s="95">
         <f>AL28+AL28*$AB$32</f>
         <v>102417.90152079912</v>
       </c>
-      <c r="AN28" s="102">
+      <c r="AN28" s="95">
         <f>AM28+AM28*$AB$32</f>
         <v>103442.08053600711</v>
       </c>
-      <c r="AO28" s="102">
+      <c r="AO28" s="95">
         <f>AN28+AN28*$AB$32</f>
         <v>104476.50134136718</v>
       </c>
-      <c r="AP28" s="102">
+      <c r="AP28" s="95">
         <f>AO28+AO28*$AB$32</f>
         <v>105521.26635478086</v>
       </c>
-      <c r="AQ28" s="102">
+      <c r="AQ28" s="95">
         <f>AP28+AP28*$AB$32</f>
         <v>106576.47901832867</v>
       </c>
-      <c r="AR28" s="102">
+      <c r="AR28" s="95">
         <f>AQ28+AQ28*$AB$32</f>
         <v>107642.24380851195</v>
       </c>
-      <c r="AS28" s="102">
+      <c r="AS28" s="95">
         <f>AR28+AR28*$AB$32</f>
         <v>108718.66624659707</v>
       </c>
-      <c r="AT28" s="102">
+      <c r="AT28" s="95">
         <f>AS28+AS28*$AB$32</f>
         <v>109805.85290906305</v>
       </c>
-      <c r="AU28" s="102">
+      <c r="AU28" s="95">
         <f>AT28+AT28*$AB$32</f>
         <v>110903.91143815368</v>
       </c>
-      <c r="AV28" s="102">
+      <c r="AV28" s="95">
         <f>AU28+AU28*$AB$32</f>
         <v>112012.95055253521</v>
       </c>
-      <c r="AW28" s="102">
+      <c r="AW28" s="95">
         <f>AV28+AV28*$AB$32</f>
         <v>113133.08005806057</v>
       </c>
-      <c r="AX28" s="102">
+      <c r="AX28" s="95">
         <f>AW28+AW28*$AB$32</f>
         <v>114264.41085864117</v>
       </c>
-      <c r="AY28" s="102">
+      <c r="AY28" s="95">
         <f>AX28+AX28*$AB$32</f>
         <v>115407.05496722758</v>
       </c>
-      <c r="AZ28" s="102">
+      <c r="AZ28" s="95">
         <f>AY28+AY28*$AB$32</f>
         <v>116561.12551689986</v>
       </c>
-      <c r="BA28" s="102">
+      <c r="BA28" s="95">
         <f>AZ28+AZ28*$AB$32</f>
         <v>117726.73677206886</v>
       </c>
-      <c r="BB28" s="102">
+      <c r="BB28" s="95">
         <f>BA28+BA28*$AB$32</f>
         <v>118904.00413978955</v>
       </c>
-      <c r="BC28" s="102">
+      <c r="BC28" s="95">
         <f>BB28+BB28*$AB$32</f>
         <v>120093.04418118745</v>
       </c>
-      <c r="BD28" s="102">
+      <c r="BD28" s="95">
         <f>BC28+BC28*$AB$32</f>
         <v>121293.97462299932</v>
       </c>
-      <c r="BE28" s="102">
+      <c r="BE28" s="95">
         <f>BD28+BD28*$AB$32</f>
         <v>122506.91436922931</v>
       </c>
-      <c r="BF28" s="102">
+      <c r="BF28" s="95">
         <f>BE28+BE28*$AB$32</f>
         <v>123731.98351292161</v>
       </c>
-      <c r="BG28" s="102">
+      <c r="BG28" s="95">
         <f>BF28+BF28*$AB$32</f>
         <v>124969.30334805083</v>
       </c>
-      <c r="BH28" s="102">
+      <c r="BH28" s="95">
         <f>BG28+BG28*$AB$32</f>
         <v>126218.99638153134</v>
       </c>
-      <c r="BI28" s="102">
+      <c r="BI28" s="95">
         <f>BH28+BH28*$AB$32</f>
         <v>127481.18634534665</v>
       </c>
-      <c r="BJ28" s="102">
+      <c r="BJ28" s="95">
         <f>BI28+BI28*$AB$32</f>
         <v>128755.99820880011</v>
       </c>
-      <c r="BK28" s="102">
+      <c r="BK28" s="95">
         <f>BJ28+BJ28*$AB$32</f>
         <v>130043.55819088811</v>
       </c>
-      <c r="BL28" s="102">
+      <c r="BL28" s="95">
         <f>BK28+BK28*$AB$32</f>
         <v>131343.993772797</v>
       </c>
-      <c r="BM28" s="102">
+      <c r="BM28" s="95">
         <f>BL28+BL28*$AB$32</f>
         <v>132657.43371052496</v>
       </c>
-      <c r="BN28" s="102">
+      <c r="BN28" s="95">
         <f>BM28+BM28*$AB$32</f>
         <v>133984.0080476302</v>
       </c>
-      <c r="BO28" s="102">
+      <c r="BO28" s="95">
         <f>BN28+BN28*$AB$32</f>
         <v>135323.8481281065</v>
       </c>
-      <c r="BP28" s="102">
+      <c r="BP28" s="95">
         <f>BO28+BO28*$AB$32</f>
         <v>136677.08660938757</v>
       </c>
-      <c r="BQ28" s="102">
+      <c r="BQ28" s="95">
         <f>BP28+BP28*$AB$32</f>
         <v>138043.85747548143</v>
       </c>
-      <c r="BR28" s="102">
+      <c r="BR28" s="95">
         <f>BQ28+BQ28*$AB$32</f>
         <v>139424.29605023624</v>
       </c>
-      <c r="BS28" s="102">
+      <c r="BS28" s="95">
         <f>BR28+BR28*$AB$32</f>
         <v>140818.5390107386</v>
       </c>
-      <c r="BT28" s="102">
+      <c r="BT28" s="95">
         <f>BS28+BS28*$AB$32</f>
         <v>142226.724400846</v>
       </c>
-      <c r="BU28" s="102">
+      <c r="BU28" s="95">
         <f>BT28+BT28*$AB$32</f>
         <v>143648.99164485445</v>
       </c>
-      <c r="BV28" s="102">
+      <c r="BV28" s="95">
         <f>BU28+BU28*$AB$32</f>
         <v>145085.48156130299</v>
       </c>
-      <c r="BW28" s="102">
+      <c r="BW28" s="95">
         <f>BV28+BV28*$AB$32</f>
         <v>146536.33637691604</v>
       </c>
-      <c r="BX28" s="102">
+      <c r="BX28" s="95">
         <f>BW28+BW28*$AB$32</f>
         <v>148001.6997406852</v>
       </c>
-      <c r="BY28" s="102">
+      <c r="BY28" s="95">
         <f>BX28+BX28*$AB$32</f>
         <v>149481.71673809204</v>
       </c>
-      <c r="BZ28" s="102">
+      <c r="BZ28" s="95">
         <f>BY28+BY28*$AB$32</f>
         <v>150976.53390547296</v>
       </c>
-      <c r="CA28" s="102">
+      <c r="CA28" s="95">
         <f>BZ28+BZ28*$AB$32</f>
         <v>152486.29924452768</v>
       </c>
-      <c r="CB28" s="102">
+      <c r="CB28" s="95">
         <f>CA28+CA28*$AB$32</f>
         <v>154011.16223697294</v>
       </c>
-      <c r="CC28" s="102">
+      <c r="CC28" s="95">
         <f>CB28+CB28*$AB$32</f>
         <v>155551.27385934268</v>
       </c>
-      <c r="CD28" s="102">
+      <c r="CD28" s="95">
         <f>CC28+CC28*$AB$32</f>
         <v>157106.78659793609</v>
       </c>
-      <c r="CE28" s="102">
+      <c r="CE28" s="95">
         <f>CD28+CD28*$AB$32</f>
         <v>158677.85446391546</v>
       </c>
-      <c r="CF28" s="102">
+      <c r="CF28" s="95">
         <f>CE28+CE28*$AB$32</f>
         <v>160264.63300855461</v>
       </c>
-      <c r="CG28" s="102">
+      <c r="CG28" s="95">
         <f>CF28+CF28*$AB$32</f>
         <v>161867.27933864016</v>
       </c>
-      <c r="CH28" s="102">
+      <c r="CH28" s="95">
         <f>CG28+CG28*$AB$32</f>
         <v>163485.95213202655</v>
       </c>
-      <c r="CI28" s="102">
+      <c r="CI28" s="95">
         <f>CH28+CH28*$AB$32</f>
         <v>165120.81165334681</v>
       </c>
-      <c r="CJ28" s="102">
+      <c r="CJ28" s="95">
         <f>CI28+CI28*$AB$32</f>
         <v>166772.01976988028</v>
       </c>
-      <c r="CK28" s="102">
+      <c r="CK28" s="95">
         <f>CJ28+CJ28*$AB$32</f>
         <v>168439.73996757908</v>
       </c>
-      <c r="CL28" s="102">
+      <c r="CL28" s="95">
         <f>CK28+CK28*$AB$32</f>
         <v>170124.13736725488</v>
       </c>
-      <c r="CM28" s="102">
+      <c r="CM28" s="95">
         <f>CL28+CL28*$AB$32</f>
         <v>171825.37874092744</v>
       </c>
-      <c r="CN28" s="102">
+      <c r="CN28" s="95">
         <f>CM28+CM28*$AB$32</f>
         <v>173543.63252833672</v>
       </c>
-      <c r="CO28" s="102">
+      <c r="CO28" s="95">
         <f>CN28+CN28*$AB$32</f>
         <v>175279.06885362009</v>
       </c>
-      <c r="CP28" s="102">
+      <c r="CP28" s="95">
         <f>CO28+CO28*$AB$32</f>
         <v>177031.85954215628</v>
       </c>
-      <c r="CQ28" s="102">
+      <c r="CQ28" s="95">
         <f>CP28+CP28*$AB$32</f>
         <v>178802.17813757784</v>
       </c>
-      <c r="CR28" s="102">
+      <c r="CR28" s="95">
         <f>CQ28+CQ28*$AB$32</f>
         <v>180590.19991895361</v>
       </c>
-      <c r="CS28" s="102">
+      <c r="CS28" s="95">
         <f>CR28+CR28*$AB$32</f>
         <v>182396.10191814316</v>
       </c>
-      <c r="CT28" s="102">
+      <c r="CT28" s="95">
         <f>CS28+CS28*$AB$32</f>
         <v>184220.0629373246</v>
       </c>
-      <c r="CU28" s="102">
+      <c r="CU28" s="95">
         <f>CT28+CT28*$AB$32</f>
         <v>186062.26356669786</v>
       </c>
-      <c r="CV28" s="102">
+      <c r="CV28" s="95">
         <f>CU28+CU28*$AB$32</f>
         <v>187922.88620236484</v>
       </c>
-      <c r="CW28" s="102">
+      <c r="CW28" s="95">
         <f>CV28+CV28*$AB$32</f>
         <v>189802.11506438849</v>
       </c>
-      <c r="CX28" s="102">
+      <c r="CX28" s="95">
         <f>CW28+CW28*$AB$32</f>
         <v>191700.13621503237</v>
       </c>
-      <c r="CY28" s="102">
+      <c r="CY28" s="95">
         <f>CX28+CX28*$AB$32</f>
         <v>193617.1375771827</v>
       </c>
-      <c r="CZ28" s="102">
+      <c r="CZ28" s="95">
         <f>CY28+CY28*$AB$32</f>
         <v>195553.30895295454</v>
       </c>
-      <c r="DA28" s="102">
+      <c r="DA28" s="95">
         <f>CZ28+CZ28*$AB$32</f>
         <v>197508.84204248409</v>
       </c>
-      <c r="DB28" s="102">
+      <c r="DB28" s="95">
         <f>DA28+DA28*$AB$32</f>
         <v>199483.93046290893</v>
       </c>
-      <c r="DC28" s="102">
+      <c r="DC28" s="95">
         <f>DB28+DB28*$AB$32</f>
         <v>201478.76976753803</v>
       </c>
-      <c r="DD28" s="102">
+      <c r="DD28" s="95">
         <f>DC28+DC28*$AB$32</f>
         <v>203493.55746521341</v>
       </c>
-      <c r="DE28" s="102">
+      <c r="DE28" s="95">
         <f>DD28+DD28*$AB$32</f>
         <v>205528.49303986554</v>
       </c>
-      <c r="DF28" s="102">
+      <c r="DF28" s="95">
         <f>DE28+DE28*$AB$32</f>
         <v>207583.7779702642</v>
       </c>
-      <c r="DG28" s="102">
+      <c r="DG28" s="95">
         <f>DF28+DF28*$AB$32</f>
         <v>209659.61574996685</v>
       </c>
-      <c r="DH28" s="102">
+      <c r="DH28" s="95">
         <f>DG28+DG28*$AB$32</f>
         <v>211756.21190746652</v>
       </c>
-      <c r="DI28" s="102">
+      <c r="DI28" s="95">
         <f>DH28+DH28*$AB$32</f>
         <v>213873.77402654118</v>
       </c>
-      <c r="DJ28" s="102">
+      <c r="DJ28" s="95">
         <f>DI28+DI28*$AB$32</f>
         <v>216012.51176680659</v>
       </c>
-      <c r="DK28" s="102">
+      <c r="DK28" s="95">
         <f>DJ28+DJ28*$AB$32</f>
         <v>218172.63688447466</v>
       </c>
-      <c r="DL28" s="102">
+      <c r="DL28" s="95">
         <f>DK28+DK28*$AB$32</f>
         <v>220354.3632533194</v>
       </c>
-      <c r="DM28" s="102"/>
-      <c r="DN28" s="102"/>
-      <c r="DO28" s="102"/>
-      <c r="DP28" s="102"/>
-      <c r="DQ28" s="102"/>
-      <c r="DR28" s="102"/>
-      <c r="DS28" s="102"/>
-      <c r="DT28" s="102"/>
-      <c r="DU28" s="102"/>
-      <c r="DV28" s="102"/>
-      <c r="DW28" s="102"/>
-      <c r="DX28" s="102"/>
-      <c r="DY28" s="102"/>
-      <c r="DZ28" s="102"/>
-      <c r="EA28" s="102"/>
-      <c r="EB28" s="102"/>
-      <c r="EC28" s="102"/>
-      <c r="ED28" s="102"/>
-      <c r="EE28" s="102"/>
-      <c r="EF28" s="102"/>
-      <c r="EG28" s="102"/>
-      <c r="EH28" s="102"/>
-      <c r="EI28" s="102"/>
+      <c r="DM28" s="95"/>
+      <c r="DN28" s="95"/>
+      <c r="DO28" s="95"/>
+      <c r="DP28" s="95"/>
+      <c r="DQ28" s="95"/>
+      <c r="DR28" s="95"/>
+      <c r="DS28" s="95"/>
+      <c r="DT28" s="95"/>
+      <c r="DU28" s="95"/>
+      <c r="DV28" s="95"/>
+      <c r="DW28" s="95"/>
+      <c r="DX28" s="95"/>
+      <c r="DY28" s="95"/>
+      <c r="DZ28" s="95"/>
+      <c r="EA28" s="95"/>
+      <c r="EB28" s="95"/>
+      <c r="EC28" s="95"/>
+      <c r="ED28" s="95"/>
+      <c r="EE28" s="95"/>
+      <c r="EF28" s="95"/>
+      <c r="EG28" s="95"/>
+      <c r="EH28" s="95"/>
+      <c r="EI28" s="95"/>
     </row>
     <row r="29" ht="14.25">
       <c r="B29" t="s">
-        <v>490</v>
-      </c>
-      <c r="C29" s="77"/>
+        <v>495</v>
+      </c>
+      <c r="C29" s="2"/>
       <c r="D29" s="7">
         <v>4419.8199999999997</v>
       </c>
@@ -5822,58 +5845,57 @@
       <c r="J29" s="11">
         <v>12644.110000000001</v>
       </c>
-      <c r="K29" s="82">
-        <f>J29</f>
+      <c r="K29" s="79">
+        <f t="shared" si="29"/>
         <v>12644.110000000001</v>
       </c>
-      <c r="L29" s="83"/>
-      <c r="M29" s="83"/>
-      <c r="N29" s="83"/>
-      <c r="O29" s="83"/>
+      <c r="L29" s="79"/>
+      <c r="M29" s="79"/>
+      <c r="N29" s="79"/>
+      <c r="O29" s="79"/>
       <c r="U29" s="8"/>
       <c r="Z29" s="8"/>
     </row>
     <row r="30" ht="14.25">
       <c r="B30" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="C30"/>
-      <c r="D30" s="104">
+        <v>496</v>
+      </c>
+      <c r="D30" s="97">
         <f>D28/D29-1</f>
         <v>-0.39497309845197304</v>
       </c>
-      <c r="E30" s="104">
+      <c r="E30" s="97">
         <f>E28/E29-1</f>
         <v>-0.096119298975976375</v>
       </c>
-      <c r="F30" s="104">
+      <c r="F30" s="97">
         <f>F28/F29-1</f>
         <v>0.19094216506554629</v>
       </c>
-      <c r="G30" s="104">
+      <c r="G30" s="97">
         <f>G28/G29-1</f>
         <v>-4.5250711555588907e-06</v>
       </c>
-      <c r="H30" s="104">
+      <c r="H30" s="97">
         <f>H28/H29-1</f>
         <v>0.0048760498731550417</v>
       </c>
-      <c r="I30" s="104">
+      <c r="I30" s="97">
         <f>I28/I29-1</f>
         <v>0.116145791827587</v>
       </c>
-      <c r="J30" s="104">
+      <c r="J30" s="97">
         <f>J28/J29-1</f>
         <v>0.14999869504456953</v>
       </c>
-      <c r="K30" s="82">
-        <f>J30</f>
+      <c r="K30" s="79">
+        <f t="shared" si="29"/>
         <v>0.14999869504456953</v>
       </c>
-      <c r="L30" s="82"/>
-      <c r="M30" s="82"/>
-      <c r="N30" s="82"/>
-      <c r="O30" s="82"/>
+      <c r="L30" s="79"/>
+      <c r="M30" s="79"/>
+      <c r="N30" s="79"/>
+      <c r="O30" s="79"/>
       <c r="P30" s="2"/>
       <c r="U30" s="8"/>
       <c r="Z30" s="8"/>
@@ -5881,27 +5903,27 @@
     <row r="31" s="21" customFormat="1" ht="14.25">
       <c r="A31" s="21"/>
       <c r="B31" s="21"/>
-      <c r="C31" s="105"/>
+      <c r="C31" s="21"/>
       <c r="F31" s="41"/>
       <c r="H31" s="21"/>
       <c r="I31" s="21"/>
       <c r="J31" s="41"/>
-      <c r="K31" s="82"/>
-      <c r="L31" s="83"/>
-      <c r="M31" s="83"/>
-      <c r="N31" s="83"/>
-      <c r="O31" s="83"/>
+      <c r="K31" s="79"/>
+      <c r="L31" s="79"/>
+      <c r="M31" s="79"/>
+      <c r="N31" s="79"/>
+      <c r="O31" s="79"/>
       <c r="U31" s="29"/>
       <c r="Z31" s="29"/>
     </row>
     <row r="32" s="21" customFormat="1" ht="16.5">
       <c r="A32" s="21" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="B32" s="21" t="s">
-        <v>493</v>
-      </c>
-      <c r="C32" s="105"/>
+        <v>498</v>
+      </c>
+      <c r="C32" s="21"/>
       <c r="F32" s="41"/>
       <c r="G32" s="21"/>
       <c r="H32" s="75">
@@ -5913,18 +5935,18 @@
       <c r="J32" s="75">
         <v>618996320</v>
       </c>
-      <c r="K32" s="82">
-        <f>J32</f>
+      <c r="K32" s="79">
+        <f t="shared" si="29"/>
         <v>618996320</v>
       </c>
-      <c r="L32" s="83"/>
-      <c r="M32" s="83"/>
-      <c r="N32" s="83"/>
-      <c r="O32" s="83"/>
+      <c r="L32" s="79"/>
+      <c r="M32" s="79"/>
+      <c r="N32" s="79"/>
+      <c r="O32" s="79"/>
       <c r="U32" s="29"/>
       <c r="Z32" s="29"/>
       <c r="AA32" s="21" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="AB32" s="42">
         <v>0.01</v>
@@ -5932,9 +5954,9 @@
     </row>
     <row r="33" ht="14.25">
       <c r="B33" t="s">
-        <v>233</v>
-      </c>
-      <c r="C33" s="77"/>
+        <v>239</v>
+      </c>
+      <c r="C33" s="2"/>
       <c r="F33" s="11"/>
       <c r="G33">
         <v>600670592</v>
@@ -5942,24 +5964,24 @@
       <c r="H33">
         <v>602574303</v>
       </c>
-      <c r="I33" s="106">
+      <c r="I33" s="98">
         <v>603976750</v>
       </c>
-      <c r="J33" s="106">
+      <c r="J33" s="98">
         <v>610032743</v>
       </c>
-      <c r="K33" s="82">
-        <f>J33</f>
+      <c r="K33" s="79">
+        <f t="shared" si="29"/>
         <v>610032743</v>
       </c>
-      <c r="L33" s="83"/>
-      <c r="M33" s="83"/>
-      <c r="N33" s="83"/>
-      <c r="O33" s="83"/>
+      <c r="L33" s="79"/>
+      <c r="M33" s="79"/>
+      <c r="N33" s="79"/>
+      <c r="O33" s="79"/>
       <c r="U33" s="8"/>
       <c r="Z33" s="8"/>
       <c r="AA33" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="AB33" s="19">
         <v>0.11</v>
@@ -5967,12 +5989,12 @@
     </row>
     <row r="34" ht="14.25">
       <c r="A34" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="B34" t="s">
-        <v>496</v>
-      </c>
-      <c r="C34" s="77"/>
+        <v>501</v>
+      </c>
+      <c r="C34" s="2"/>
       <c r="F34" s="11"/>
       <c r="G34">
         <v>5149.8500000000004</v>
@@ -5980,24 +6002,24 @@
       <c r="H34">
         <v>7259.9499999999998</v>
       </c>
-      <c r="I34" s="106">
+      <c r="I34" s="98">
         <v>5616.75</v>
       </c>
-      <c r="J34" s="106">
+      <c r="J34" s="98">
         <v>7110</v>
       </c>
-      <c r="K34" s="82">
-        <f>J34</f>
+      <c r="K34" s="79">
+        <f t="shared" si="29"/>
         <v>7110</v>
       </c>
-      <c r="L34" s="83"/>
-      <c r="M34" s="83"/>
-      <c r="N34" s="83"/>
-      <c r="O34" s="83"/>
+      <c r="L34" s="79"/>
+      <c r="M34" s="79"/>
+      <c r="N34" s="79"/>
+      <c r="O34" s="79"/>
       <c r="U34" s="8"/>
       <c r="Z34" s="8"/>
       <c r="AA34" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="AB34">
         <f>NPV(AB33,P28:DL28)</f>
@@ -6006,89 +6028,89 @@
     </row>
     <row r="35" ht="14.25">
       <c r="A35" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="B35" t="s">
-        <v>93</v>
-      </c>
-      <c r="C35" s="77"/>
+        <v>99</v>
+      </c>
+      <c r="C35" s="2"/>
       <c r="F35" s="11"/>
-      <c r="G35" s="82">
+      <c r="G35" s="79">
         <f>G29*10000000/G33</f>
         <v>73.581428138236546</v>
       </c>
-      <c r="H35" s="82">
+      <c r="H35" s="79">
         <f>H29*10000000/H33</f>
         <v>116.63673616695866</v>
       </c>
-      <c r="I35" s="82">
+      <c r="I35" s="79">
         <f>I29*10000000/I33</f>
         <v>170.36649175651215</v>
       </c>
-      <c r="J35" s="82">
+      <c r="J35" s="79">
         <f>J29*10000000/J33</f>
         <v>207.26936619531585</v>
       </c>
-      <c r="K35" s="82">
+      <c r="K35" s="79">
         <v>268.94</v>
       </c>
-      <c r="L35" s="83"/>
-      <c r="M35" s="83"/>
-      <c r="N35" s="83"/>
-      <c r="O35" s="83"/>
+      <c r="L35" s="79"/>
+      <c r="M35" s="79"/>
+      <c r="N35" s="79"/>
+      <c r="O35" s="79"/>
       <c r="U35" s="8"/>
       <c r="Z35" s="8"/>
     </row>
     <row r="36" ht="14.25">
       <c r="B36" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="C36" s="77"/>
+        <v>503</v>
+      </c>
+      <c r="C36" s="2"/>
       <c r="F36" s="11"/>
-      <c r="G36" s="82">
+      <c r="G36" s="79">
         <f>G34/G35</f>
         <v>69.988448584132385</v>
       </c>
-      <c r="H36" s="82">
+      <c r="H36" s="79">
         <f>H34/H35</f>
         <v>62.244111405927946</v>
       </c>
-      <c r="I36" s="82">
+      <c r="I36" s="79">
         <f>I34/I35</f>
         <v>32.968630991283554</v>
       </c>
-      <c r="J36" s="82">
+      <c r="J36" s="79">
         <f>J34/J35</f>
         <v>34.30318782998566</v>
       </c>
-      <c r="K36" s="82">
-        <f>J36</f>
+      <c r="K36" s="79">
+        <f t="shared" si="29"/>
         <v>34.30318782998566</v>
       </c>
-      <c r="L36" s="83"/>
-      <c r="M36" s="83"/>
-      <c r="N36" s="83"/>
-      <c r="O36" s="83"/>
+      <c r="L36" s="79"/>
+      <c r="M36" s="79"/>
+      <c r="N36" s="79"/>
+      <c r="O36" s="79"/>
       <c r="U36" s="8"/>
       <c r="Z36" s="8"/>
       <c r="AA36" t="s">
-        <v>499</v>
-      </c>
-      <c r="AB36" s="107">
+        <v>504</v>
+      </c>
+      <c r="AB36" s="99">
         <f>K32</f>
         <v>618996320</v>
       </c>
     </row>
     <row r="37" ht="14.25">
-      <c r="K37" s="82"/>
-      <c r="L37" s="83"/>
-      <c r="M37" s="83"/>
-      <c r="N37" s="83"/>
-      <c r="O37" s="83"/>
+      <c r="K37" s="79"/>
+      <c r="L37" s="79"/>
+      <c r="M37" s="79"/>
+      <c r="N37" s="79"/>
+      <c r="O37" s="79"/>
       <c r="U37" s="8"/>
       <c r="Z37" s="8"/>
       <c r="AA37" s="1" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="AB37" s="1">
         <v>8994.5</v>
@@ -6096,49 +6118,49 @@
     </row>
     <row r="38" ht="14.25">
       <c r="A38" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="B38" t="s">
         <v>46</v>
       </c>
-      <c r="C38" s="77"/>
-      <c r="K38" s="82"/>
-      <c r="L38" s="83"/>
-      <c r="M38" s="83"/>
-      <c r="N38" s="83"/>
-      <c r="O38" s="83"/>
+      <c r="C38" s="2"/>
+      <c r="K38" s="79"/>
+      <c r="L38" s="79"/>
+      <c r="M38" s="79"/>
+      <c r="N38" s="79"/>
+      <c r="O38" s="79"/>
       <c r="U38" s="8"/>
       <c r="Z38" s="8"/>
       <c r="AA38" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="AB38" s="91">
+        <v>507</v>
+      </c>
+      <c r="AB38" s="85">
         <f>AB34*10000000/AB36</f>
         <v>8902.8219280661087</v>
       </c>
     </row>
     <row r="39" ht="14.25">
-      <c r="K39" s="82"/>
-      <c r="L39" s="108" t="s">
-        <v>237</v>
-      </c>
-      <c r="M39" s="108" t="s">
-        <v>238</v>
-      </c>
-      <c r="N39" s="108" t="s">
-        <v>95</v>
-      </c>
-      <c r="O39" s="108" t="s">
-        <v>239</v>
+      <c r="K39" s="79"/>
+      <c r="L39" s="81" t="s">
+        <v>243</v>
+      </c>
+      <c r="M39" s="81" t="s">
+        <v>244</v>
+      </c>
+      <c r="N39" s="81" t="s">
+        <v>101</v>
+      </c>
+      <c r="O39" s="81" t="s">
+        <v>245</v>
       </c>
       <c r="U39" s="8"/>
       <c r="Z39" s="8"/>
     </row>
     <row r="40" ht="14.25">
       <c r="B40" t="s">
-        <v>200</v>
-      </c>
-      <c r="C40" s="109" t="e">
+        <v>206</v>
+      </c>
+      <c r="C40" s="17" t="e">
         <f>C11/B11-1</f>
         <v>#VALUE!</v>
       </c>
@@ -6175,7 +6197,7 @@
         <v>0.26811653378501643</v>
       </c>
       <c r="P40" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="Q40" s="19">
         <v>0.16</v>
@@ -6188,56 +6210,56 @@
     </row>
     <row r="41" ht="14.25">
       <c r="B41" t="s">
-        <v>377</v>
-      </c>
-      <c r="C41" s="110">
+        <v>383</v>
+      </c>
+      <c r="C41" s="100">
         <f>C11-C14</f>
         <v>6188.4799999999987</v>
       </c>
-      <c r="D41" s="111">
+      <c r="D41" s="100">
         <f>D11-D14</f>
         <v>8831.5800000000017</v>
       </c>
-      <c r="E41" s="111">
+      <c r="E41" s="100">
         <f>E11-E14</f>
         <v>11876.619999999999</v>
       </c>
-      <c r="F41" s="111">
+      <c r="F41" s="100">
         <f>F11-F14</f>
         <v>16912.420000000006</v>
       </c>
-      <c r="G41" s="111">
+      <c r="G41" s="100">
         <f>G11-G14</f>
         <v>17269.030000000002</v>
       </c>
-      <c r="H41" s="111">
+      <c r="H41" s="100">
         <f>H11-H14</f>
         <v>21892.169999999998</v>
       </c>
-      <c r="I41" s="111">
+      <c r="I41" s="100">
         <f>I11-I14</f>
         <v>28858.369999999995</v>
       </c>
-      <c r="J41" s="111">
+      <c r="J41" s="100">
         <f>J11-J14</f>
         <v>36257.819999999992</v>
       </c>
-      <c r="K41" s="111">
+      <c r="K41" s="100">
         <f>K11-K14</f>
         <v>44953.439999999995</v>
       </c>
-      <c r="L41" s="83"/>
-      <c r="M41" s="83"/>
-      <c r="N41" s="83"/>
-      <c r="O41" s="83"/>
+      <c r="L41" s="79"/>
+      <c r="M41" s="79"/>
+      <c r="N41" s="79"/>
+      <c r="O41" s="79"/>
       <c r="U41" s="8"/>
       <c r="Z41" s="8"/>
     </row>
     <row r="42" ht="14.25">
       <c r="B42" t="s">
-        <v>504</v>
-      </c>
-      <c r="C42" s="109">
+        <v>509</v>
+      </c>
+      <c r="C42" s="17">
         <f>C41/C11</f>
         <v>0.61933169805618182</v>
       </c>
@@ -6273,10 +6295,10 @@
         <f>K41/K11</f>
         <v>0.64473196763879637</v>
       </c>
-      <c r="L42" s="83"/>
-      <c r="M42" s="83"/>
-      <c r="N42" s="83"/>
-      <c r="O42" s="83"/>
+      <c r="L42" s="79"/>
+      <c r="M42" s="79"/>
+      <c r="N42" s="79"/>
+      <c r="O42" s="79"/>
       <c r="Q42" s="19">
         <f>35%</f>
         <v>0.34999999999999998</v>
@@ -6286,9 +6308,9 @@
     </row>
     <row r="43" ht="14.25">
       <c r="B43" t="s">
-        <v>505</v>
-      </c>
-      <c r="C43" s="109" t="e">
+        <v>510</v>
+      </c>
+      <c r="C43" s="17" t="e">
         <f>D15/C15-1</f>
         <v>#DIV/0!</v>
       </c>
@@ -6297,37 +6319,37 @@
         <v>#DIV/0!</v>
       </c>
       <c r="E43" s="17" t="e">
-        <f>E15/D15-1</f>
+        <f t="shared" ref="E43:E46" si="30">E15/D15-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F43" s="17">
-        <f>F15/E15-1</f>
+        <f t="shared" ref="F43:F46" si="31">F15/E15-1</f>
         <v>0.48183424980361345</v>
       </c>
       <c r="G43" s="17">
-        <f>G15/F15-1</f>
+        <f t="shared" ref="G43:G46" si="32">G15/F15-1</f>
         <v>0.1799653530486478</v>
       </c>
       <c r="H43" s="17">
-        <f>H15/G15-1</f>
+        <f t="shared" ref="H43:H46" si="33">H15/G15-1</f>
         <v>0.4003834798793402</v>
       </c>
       <c r="I43" s="17">
-        <f>I15/H15-1</f>
+        <f t="shared" ref="I43:I46" si="34">I15/H15-1</f>
         <v>0.083595428375010883</v>
       </c>
       <c r="J43" s="17">
-        <f>J15/I15-1</f>
+        <f t="shared" ref="J43:J46" si="35">J15/I15-1</f>
         <v>0.021163433731436365</v>
       </c>
       <c r="K43" s="17">
-        <f>K15/J15-1</f>
+        <f t="shared" ref="K43:K46" si="36">K15/J15-1</f>
         <v>0.34489257054103017</v>
       </c>
-      <c r="L43" s="83"/>
-      <c r="M43" s="83"/>
-      <c r="N43" s="83"/>
-      <c r="O43" s="83"/>
+      <c r="L43" s="79"/>
+      <c r="M43" s="79"/>
+      <c r="N43" s="79"/>
+      <c r="O43" s="79"/>
       <c r="Q43" s="19">
         <v>0.059999999999999998</v>
       </c>
@@ -6337,48 +6359,48 @@
     </row>
     <row r="44" ht="14.25">
       <c r="B44" t="s">
-        <v>506</v>
-      </c>
-      <c r="C44" s="109" t="e">
-        <f>C16/B16-1</f>
+        <v>511</v>
+      </c>
+      <c r="C44" s="17" t="e">
+        <f t="shared" ref="C44:C46" si="37">C16/B16-1</f>
         <v>#VALUE!</v>
       </c>
       <c r="D44" s="17">
-        <f>D16/C16-1</f>
+        <f t="shared" ref="D44:D46" si="38">D16/C16-1</f>
         <v>0.30016544552115354</v>
       </c>
       <c r="E44" s="17">
-        <f>E16/D16-1</f>
+        <f t="shared" si="30"/>
         <v>0.43643739415799976</v>
       </c>
       <c r="F44" s="17">
-        <f>F16/E16-1</f>
+        <f t="shared" si="31"/>
         <v>1.6172977653445235</v>
       </c>
       <c r="G44" s="17">
-        <f>G16/F16-1</f>
+        <f t="shared" si="32"/>
         <v>0.51892362348198739</v>
       </c>
       <c r="H44" s="17">
-        <f>H16/G16-1</f>
+        <f t="shared" si="33"/>
         <v>-0.19521896330450461</v>
       </c>
       <c r="I44" s="17">
-        <f>I16/H16-1</f>
+        <f t="shared" si="34"/>
         <v>-0.33595994503893067</v>
       </c>
       <c r="J44" s="17">
-        <f>J16/I16-1</f>
+        <f t="shared" si="35"/>
         <v>0.45178938128007773</v>
       </c>
       <c r="K44" s="17">
-        <f>K16/J16-1</f>
+        <f t="shared" si="36"/>
         <v>0.7202647547886929</v>
       </c>
-      <c r="L44" s="83"/>
-      <c r="M44" s="83"/>
-      <c r="N44" s="83"/>
-      <c r="O44" s="83"/>
+      <c r="L44" s="79"/>
+      <c r="M44" s="79"/>
+      <c r="N44" s="79"/>
+      <c r="O44" s="79"/>
       <c r="Q44" s="19">
         <v>0.10000000000000001</v>
       </c>
@@ -6388,48 +6410,48 @@
     </row>
     <row r="45" ht="14.25">
       <c r="B45" t="s">
-        <v>507</v>
-      </c>
-      <c r="C45" s="109" t="e">
-        <f>C17/B17-1</f>
+        <v>512</v>
+      </c>
+      <c r="C45" s="17" t="e">
+        <f t="shared" si="37"/>
         <v>#VALUE!</v>
       </c>
       <c r="D45" s="17">
-        <f>D17/C17-1</f>
+        <f t="shared" si="38"/>
         <v>0.52370474524241417</v>
       </c>
       <c r="E45" s="17">
-        <f>E17/D17-1</f>
+        <f t="shared" si="30"/>
         <v>0.36555625215731302</v>
       </c>
       <c r="F45" s="17">
-        <f>F17/E17-1</f>
+        <f t="shared" si="31"/>
         <v>0.31495514642538414</v>
       </c>
       <c r="G45" s="17">
-        <f>G17/F17-1</f>
+        <f t="shared" si="32"/>
         <v>-0.01977576223578692</v>
       </c>
       <c r="H45" s="17">
-        <f>H17/G17-1</f>
+        <f t="shared" si="33"/>
         <v>0.43662828624828398</v>
       </c>
       <c r="I45" s="17">
-        <f>I17/H17-1</f>
+        <f t="shared" si="34"/>
         <v>0.42080029863552526</v>
       </c>
       <c r="J45" s="17">
-        <f>J17/I17-1</f>
+        <f t="shared" si="35"/>
         <v>0.25407288748066259</v>
       </c>
       <c r="K45" s="17">
-        <f>K17/J17-1</f>
+        <f t="shared" si="36"/>
         <v>0.17390998450596551</v>
       </c>
-      <c r="L45" s="83"/>
-      <c r="M45" s="83"/>
-      <c r="N45" s="83"/>
-      <c r="O45" s="83"/>
+      <c r="L45" s="79"/>
+      <c r="M45" s="79"/>
+      <c r="N45" s="79"/>
+      <c r="O45" s="79"/>
       <c r="Q45" s="19">
         <v>0.14999999999999999</v>
       </c>
@@ -6439,48 +6461,48 @@
     </row>
     <row r="46" ht="14.25">
       <c r="B46" t="s">
-        <v>508</v>
-      </c>
-      <c r="C46" s="109" t="e">
-        <f>C18/B18-1</f>
+        <v>513</v>
+      </c>
+      <c r="C46" s="17" t="e">
+        <f t="shared" si="37"/>
         <v>#VALUE!</v>
       </c>
       <c r="D46" s="17">
-        <f>D18/C18-1</f>
+        <f t="shared" si="38"/>
         <v>0.4341717015596458</v>
       </c>
       <c r="E46" s="17">
-        <f>E18/D18-1</f>
+        <f t="shared" si="30"/>
         <v>0.41226609189771746</v>
       </c>
       <c r="F46" s="17">
-        <f>F18/E18-1</f>
+        <f t="shared" si="31"/>
         <v>1.0439125910509883</v>
       </c>
       <c r="G46" s="17">
-        <f>G18/F18-1</f>
+        <f t="shared" si="32"/>
         <v>0.10399484098700063</v>
       </c>
       <c r="H46" s="17">
-        <f>H18/G18-1</f>
+        <f t="shared" si="33"/>
         <v>0.18231008085590439</v>
       </c>
       <c r="I46" s="17">
-        <f>I18/H18-1</f>
+        <f t="shared" si="34"/>
         <v>0.26213693215799472</v>
       </c>
       <c r="J46" s="17">
-        <f>J18/I18-1</f>
+        <f t="shared" si="35"/>
         <v>0.40780419465161333</v>
       </c>
       <c r="K46" s="17">
-        <f>K18/J18-1</f>
+        <f t="shared" si="36"/>
         <v>0.28927881519639409</v>
       </c>
-      <c r="L46" s="83"/>
-      <c r="M46" s="83"/>
-      <c r="N46" s="83"/>
-      <c r="O46" s="83"/>
+      <c r="L46" s="79"/>
+      <c r="M46" s="79"/>
+      <c r="N46" s="79"/>
+      <c r="O46" s="79"/>
       <c r="Q46" s="19">
         <v>0.14999999999999999</v>
       </c>
@@ -6490,9 +6512,9 @@
     </row>
     <row r="47" ht="14.25">
       <c r="B47" t="s">
-        <v>509</v>
-      </c>
-      <c r="C47" s="109" t="e">
+        <v>514</v>
+      </c>
+      <c r="C47" s="17" t="e">
         <f>C20/B20-1</f>
         <v>#VALUE!</v>
       </c>
@@ -6528,10 +6550,10 @@
         <f>K20/J20-1</f>
         <v>0.33582357685889641</v>
       </c>
-      <c r="L47" s="83"/>
-      <c r="M47" s="83"/>
-      <c r="N47" s="83"/>
-      <c r="O47" s="83"/>
+      <c r="L47" s="79"/>
+      <c r="M47" s="79"/>
+      <c r="N47" s="79"/>
+      <c r="O47" s="79"/>
       <c r="Q47" s="19">
         <v>0.20000000000000001</v>
       </c>
@@ -6541,9 +6563,9 @@
     </row>
     <row r="48" ht="14.25">
       <c r="B48" t="s">
-        <v>510</v>
-      </c>
-      <c r="C48" s="109">
+        <v>515</v>
+      </c>
+      <c r="C48" s="17">
         <f>-C24/C23</f>
         <v>0.34820278198771237</v>
       </c>
@@ -6579,10 +6601,10 @@
         <f>-K24/K23</f>
         <v>0.24005302757180108</v>
       </c>
-      <c r="L48" s="83"/>
-      <c r="M48" s="83"/>
-      <c r="N48" s="83"/>
-      <c r="O48" s="83"/>
+      <c r="L48" s="79"/>
+      <c r="M48" s="79"/>
+      <c r="N48" s="79"/>
+      <c r="O48" s="79"/>
       <c r="Q48" s="19">
         <v>0.25</v>
       </c>
@@ -6592,9 +6614,9 @@
     </row>
     <row r="49" ht="14.25">
       <c r="B49" t="s">
-        <v>511</v>
-      </c>
-      <c r="C49" s="112">
+        <v>516</v>
+      </c>
+      <c r="C49" s="16">
         <f>C16/C11</f>
         <v>0.080451832881480445</v>
       </c>
@@ -6614,19 +6636,19 @@
         <f>G16/G11</f>
         <v>0.22368449160383957</v>
       </c>
-      <c r="H49" s="113">
+      <c r="H49" s="101">
         <f>H16/H11</f>
         <v>0.15181219206704336</v>
       </c>
-      <c r="I49" s="113">
+      <c r="I49" s="101">
         <f>I16/I11</f>
         <v>0.077010719426649027</v>
       </c>
-      <c r="J49" s="113">
+      <c r="J49" s="101">
         <f>J16/J11</f>
         <v>0.08422132783679756</v>
       </c>
-      <c r="K49" s="113">
+      <c r="K49" s="101">
         <f>K16/K11</f>
         <v>0.1142505266820444</v>
       </c>
@@ -6637,19 +6659,19 @@
     </row>
     <row r="50" ht="14.25">
       <c r="A50" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
     </row>
     <row r="51" ht="14.25"/>
     <row r="52" ht="14.25">
       <c r="B52" t="s">
-        <v>513</v>
-      </c>
-      <c r="C52" s="77"/>
-      <c r="I52" s="81">
+        <v>518</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="I52" s="78">
         <v>120.89</v>
       </c>
-      <c r="J52" s="81">
+      <c r="J52" s="78">
         <v>123.59999999999999</v>
       </c>
     </row>
@@ -6657,24 +6679,24 @@
       <c r="B53" t="s">
         <v>22</v>
       </c>
-      <c r="C53" s="77"/>
-      <c r="I53" s="81">
+      <c r="C53" s="2"/>
+      <c r="I53" s="78">
         <v>51372.239999999998</v>
       </c>
-      <c r="J53" s="81">
+      <c r="J53" s="78">
         <v>71886.929999999993</v>
       </c>
     </row>
     <row r="54" ht="14.25">
       <c r="B54" t="s">
-        <v>514</v>
-      </c>
-      <c r="C54" s="77"/>
-      <c r="I54" s="81">
+        <v>519</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="I54" s="78">
         <f>I53+I52</f>
         <v>51493.129999999997</v>
       </c>
-      <c r="J54" s="88">
+      <c r="J54" s="82">
         <f>J53+J52</f>
         <v>72010.529999999999</v>
       </c>
@@ -6682,62 +6704,62 @@
     <row r="55" ht="14.25"/>
     <row r="56" ht="14.25">
       <c r="B56" t="s">
-        <v>515</v>
-      </c>
-      <c r="C56" s="77"/>
-      <c r="I56" s="81">
+        <v>520</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="I56" s="78">
         <v>87596.089999999997</v>
       </c>
-      <c r="J56" s="81">
+      <c r="J56" s="78">
         <v>65669.850000000006</v>
       </c>
     </row>
     <row r="57" ht="14.25">
       <c r="B57" t="s">
-        <v>516</v>
-      </c>
-      <c r="C57" s="77"/>
-      <c r="I57" s="81">
+        <v>521</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="I57" s="78">
         <v>69238</v>
       </c>
-      <c r="J57" s="81">
+      <c r="J57" s="78">
         <v>47894.699999999997</v>
       </c>
     </row>
     <row r="58" ht="14.25">
       <c r="B58" t="s">
-        <v>331</v>
-      </c>
-      <c r="C58" s="77"/>
-      <c r="I58" s="81">
+        <v>337</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="I58" s="78">
         <v>59966.660000000003</v>
       </c>
-      <c r="J58" s="81">
+      <c r="J58" s="78">
         <v>44489.790000000001</v>
       </c>
     </row>
     <row r="59" ht="14.25">
       <c r="B59" t="s">
-        <v>517</v>
-      </c>
-      <c r="C59" s="77"/>
-      <c r="I59" s="81">
+        <v>522</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="I59" s="78">
         <v>3577.9000000000001</v>
       </c>
-      <c r="J59" s="81">
+      <c r="J59" s="78">
         <v>3630.29</v>
       </c>
     </row>
     <row r="60" ht="14.25">
       <c r="B60" t="s">
-        <v>518</v>
-      </c>
-      <c r="C60" s="77"/>
-      <c r="I60" s="81">
+        <v>523</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="I60" s="78">
         <f>SUM(I56:I59)</f>
         <v>220378.64999999999</v>
       </c>
-      <c r="J60" s="88">
+      <c r="J60" s="82">
         <f>SUM(J56:J59)</f>
         <v>161684.63</v>
       </c>
@@ -6765,234 +6787,234 @@
   </cols>
   <sheetData>
     <row r="1" ht="16.5">
-      <c r="A1" s="114"/>
-      <c r="B1" s="115" t="s">
-        <v>519</v>
-      </c>
-      <c r="C1" s="116"/>
-      <c r="D1" s="116"/>
-      <c r="E1" s="116"/>
-      <c r="F1" s="116"/>
+      <c r="A1" s="102"/>
+      <c r="B1" s="103" t="s">
+        <v>524</v>
+      </c>
+      <c r="C1" s="104"/>
+      <c r="D1" s="104"/>
+      <c r="E1" s="104"/>
+      <c r="F1" s="104"/>
     </row>
     <row r="2">
-      <c r="A2" s="114"/>
-      <c r="B2" s="114"/>
-      <c r="C2" s="114"/>
-      <c r="D2" s="114"/>
-      <c r="E2" s="114"/>
-      <c r="F2" s="114"/>
+      <c r="A2" s="102"/>
+      <c r="B2" s="102"/>
+      <c r="C2" s="102"/>
+      <c r="D2" s="102"/>
+      <c r="E2" s="102"/>
+      <c r="F2" s="102"/>
     </row>
     <row r="3" ht="15">
-      <c r="A3" s="114"/>
-      <c r="B3" s="117" t="s">
-        <v>520</v>
-      </c>
-      <c r="C3" s="118" t="s">
-        <v>521</v>
-      </c>
-      <c r="D3" s="114"/>
-      <c r="E3" s="114"/>
-      <c r="F3" s="114"/>
+      <c r="A3" s="102"/>
+      <c r="B3" s="105" t="s">
+        <v>525</v>
+      </c>
+      <c r="C3" s="106" t="s">
+        <v>526</v>
+      </c>
+      <c r="D3" s="102"/>
+      <c r="E3" s="102"/>
+      <c r="F3" s="102"/>
     </row>
     <row r="4" ht="15">
-      <c r="A4" s="119" t="s">
-        <v>522</v>
-      </c>
-      <c r="B4" s="119" t="s">
-        <v>523</v>
-      </c>
-      <c r="C4" s="120">
+      <c r="A4" s="107" t="s">
+        <v>527</v>
+      </c>
+      <c r="B4" s="107" t="s">
+        <v>528</v>
+      </c>
+      <c r="C4" s="108">
         <v>52.700000000000003</v>
       </c>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
+      <c r="D4" s="102"/>
+      <c r="E4" s="102"/>
+      <c r="F4" s="102"/>
     </row>
     <row r="5" ht="15">
-      <c r="A5" s="114"/>
-      <c r="B5" s="119" t="s">
-        <v>524</v>
-      </c>
-      <c r="C5" s="120">
+      <c r="A5" s="102"/>
+      <c r="B5" s="107" t="s">
+        <v>529</v>
+      </c>
+      <c r="C5" s="108">
         <v>16.300000000000001</v>
       </c>
-      <c r="D5" s="114"/>
-      <c r="E5" s="114"/>
-      <c r="F5" s="114"/>
+      <c r="D5" s="102"/>
+      <c r="E5" s="102"/>
+      <c r="F5" s="102"/>
     </row>
     <row r="6" ht="15">
-      <c r="A6" s="114"/>
-      <c r="B6" s="119" t="s">
-        <v>525</v>
-      </c>
-      <c r="C6" s="120">
+      <c r="A6" s="102"/>
+      <c r="B6" s="107" t="s">
+        <v>530</v>
+      </c>
+      <c r="C6" s="108">
         <v>31</v>
       </c>
-      <c r="D6" s="114"/>
-      <c r="E6" s="114"/>
-      <c r="F6" s="114"/>
+      <c r="D6" s="102"/>
+      <c r="E6" s="102"/>
+      <c r="F6" s="102"/>
     </row>
     <row r="7">
-      <c r="A7" s="114"/>
-      <c r="B7" s="114"/>
-      <c r="C7" s="114"/>
-      <c r="D7" s="114"/>
-      <c r="E7" s="114"/>
-      <c r="F7" s="114"/>
+      <c r="A7" s="102"/>
+      <c r="B7" s="102"/>
+      <c r="C7" s="102"/>
+      <c r="D7" s="102"/>
+      <c r="E7" s="102"/>
+      <c r="F7" s="102"/>
     </row>
     <row r="8">
-      <c r="A8" s="114"/>
-      <c r="B8" s="114"/>
-      <c r="C8" s="114"/>
-      <c r="D8" s="114"/>
-      <c r="E8" s="114"/>
-      <c r="F8" s="114"/>
+      <c r="A8" s="102"/>
+      <c r="B8" s="102"/>
+      <c r="C8" s="102"/>
+      <c r="D8" s="102"/>
+      <c r="E8" s="102"/>
+      <c r="F8" s="102"/>
     </row>
     <row r="9" ht="15">
-      <c r="A9" s="114"/>
-      <c r="B9" s="117" t="s">
-        <v>526</v>
-      </c>
-      <c r="C9" s="119" t="s">
-        <v>527</v>
-      </c>
-      <c r="D9" s="119" t="s">
-        <v>528</v>
-      </c>
-      <c r="E9" s="114"/>
-      <c r="F9" s="114"/>
+      <c r="A9" s="102"/>
+      <c r="B9" s="105" t="s">
+        <v>531</v>
+      </c>
+      <c r="C9" s="107" t="s">
+        <v>532</v>
+      </c>
+      <c r="D9" s="107" t="s">
+        <v>533</v>
+      </c>
+      <c r="E9" s="102"/>
+      <c r="F9" s="102"/>
     </row>
     <row r="10" ht="15">
-      <c r="A10" s="114"/>
-      <c r="B10" s="119" t="s">
-        <v>529</v>
-      </c>
-      <c r="C10" s="120">
+      <c r="A10" s="102"/>
+      <c r="B10" s="107" t="s">
+        <v>534</v>
+      </c>
+      <c r="C10" s="108">
         <v>100</v>
       </c>
-      <c r="D10" s="119" t="s">
+      <c r="D10" s="107" t="s">
         <v>0</v>
       </c>
-      <c r="E10" s="114"/>
-      <c r="F10" s="114"/>
+      <c r="E10" s="102"/>
+      <c r="F10" s="102"/>
     </row>
     <row r="11" ht="15">
-      <c r="A11" s="114"/>
-      <c r="B11" s="119" t="s">
-        <v>530</v>
-      </c>
-      <c r="C11" s="120">
+      <c r="A11" s="102"/>
+      <c r="B11" s="107" t="s">
+        <v>535</v>
+      </c>
+      <c r="C11" s="108">
         <v>100</v>
       </c>
-      <c r="D11" s="118" t="s">
-        <v>531</v>
-      </c>
-      <c r="E11" s="114"/>
-      <c r="F11" s="114"/>
+      <c r="D11" s="106" t="s">
+        <v>536</v>
+      </c>
+      <c r="E11" s="102"/>
+      <c r="F11" s="102"/>
     </row>
     <row r="12" ht="15">
-      <c r="A12" s="119" t="s">
-        <v>434</v>
-      </c>
-      <c r="B12" s="119" t="s">
-        <v>532</v>
-      </c>
-      <c r="C12" s="120">
+      <c r="A12" s="107" t="s">
+        <v>439</v>
+      </c>
+      <c r="B12" s="107" t="s">
+        <v>537</v>
+      </c>
+      <c r="C12" s="108">
         <v>74</v>
       </c>
-      <c r="D12" s="118" t="s">
-        <v>533</v>
-      </c>
-      <c r="E12" s="116"/>
-      <c r="F12" s="114"/>
+      <c r="D12" s="106" t="s">
+        <v>538</v>
+      </c>
+      <c r="E12" s="104"/>
+      <c r="F12" s="102"/>
     </row>
     <row r="13" ht="15">
-      <c r="A13" s="114"/>
-      <c r="B13" s="119" t="s">
-        <v>534</v>
-      </c>
-      <c r="C13" s="120">
+      <c r="A13" s="102"/>
+      <c r="B13" s="107" t="s">
+        <v>539</v>
+      </c>
+      <c r="C13" s="108">
         <v>50</v>
       </c>
-      <c r="D13" s="118" t="s">
-        <v>535</v>
-      </c>
-      <c r="E13" s="114"/>
-      <c r="F13" s="114"/>
+      <c r="D13" s="106" t="s">
+        <v>540</v>
+      </c>
+      <c r="E13" s="102"/>
+      <c r="F13" s="102"/>
     </row>
     <row r="14" ht="15">
-      <c r="A14" s="114"/>
-      <c r="B14" s="119" t="s">
-        <v>536</v>
-      </c>
-      <c r="C14" s="120">
+      <c r="A14" s="102"/>
+      <c r="B14" s="107" t="s">
+        <v>541</v>
+      </c>
+      <c r="C14" s="108">
         <v>51</v>
       </c>
-      <c r="D14" s="118" t="s">
-        <v>537</v>
-      </c>
-      <c r="E14" s="114"/>
-      <c r="F14" s="114"/>
+      <c r="D14" s="106" t="s">
+        <v>542</v>
+      </c>
+      <c r="E14" s="102"/>
+      <c r="F14" s="102"/>
     </row>
     <row r="15" ht="15">
-      <c r="A15" s="119" t="s">
-        <v>436</v>
-      </c>
-      <c r="B15" s="119" t="s">
-        <v>538</v>
-      </c>
-      <c r="C15" s="120">
+      <c r="A15" s="107" t="s">
+        <v>441</v>
+      </c>
+      <c r="B15" s="107" t="s">
+        <v>543</v>
+      </c>
+      <c r="C15" s="108">
         <v>45</v>
       </c>
-      <c r="D15" s="118" t="s">
-        <v>539</v>
-      </c>
-      <c r="E15" s="114"/>
-      <c r="F15" s="114"/>
+      <c r="D15" s="106" t="s">
+        <v>544</v>
+      </c>
+      <c r="E15" s="102"/>
+      <c r="F15" s="102"/>
     </row>
     <row r="16" ht="15">
-      <c r="A16" s="114"/>
-      <c r="B16" s="119" t="s">
-        <v>540</v>
-      </c>
-      <c r="C16" s="120">
+      <c r="A16" s="102"/>
+      <c r="B16" s="107" t="s">
+        <v>545</v>
+      </c>
+      <c r="C16" s="108">
         <v>46</v>
       </c>
-      <c r="D16" s="118" t="s">
-        <v>541</v>
-      </c>
-      <c r="E16" s="116"/>
-      <c r="F16" s="114"/>
+      <c r="D16" s="106" t="s">
+        <v>546</v>
+      </c>
+      <c r="E16" s="104"/>
+      <c r="F16" s="102"/>
     </row>
     <row r="17" ht="15">
-      <c r="A17" s="114"/>
-      <c r="B17" s="119" t="s">
-        <v>542</v>
-      </c>
-      <c r="C17" s="120">
+      <c r="A17" s="102"/>
+      <c r="B17" s="107" t="s">
+        <v>547</v>
+      </c>
+      <c r="C17" s="108">
         <v>100</v>
       </c>
-      <c r="D17" s="118" t="s">
-        <v>543</v>
-      </c>
-      <c r="E17" s="114"/>
-      <c r="F17" s="114"/>
+      <c r="D17" s="106" t="s">
+        <v>548</v>
+      </c>
+      <c r="E17" s="102"/>
+      <c r="F17" s="102"/>
     </row>
     <row r="18">
-      <c r="A18" s="114"/>
-      <c r="B18" s="114"/>
-      <c r="C18" s="114"/>
-      <c r="D18" s="114"/>
-      <c r="E18" s="114"/>
-      <c r="F18" s="114"/>
+      <c r="A18" s="102"/>
+      <c r="B18" s="102"/>
+      <c r="C18" s="102"/>
+      <c r="D18" s="102"/>
+      <c r="E18" s="102"/>
+      <c r="F18" s="102"/>
     </row>
     <row r="19">
-      <c r="A19" s="114"/>
-      <c r="B19" s="114"/>
-      <c r="C19" s="114"/>
-      <c r="D19" s="114"/>
-      <c r="E19" s="114"/>
-      <c r="F19" s="114"/>
+      <c r="A19" s="102"/>
+      <c r="B19" s="102"/>
+      <c r="C19" s="102"/>
+      <c r="D19" s="102"/>
+      <c r="E19" s="102"/>
+      <c r="F19" s="102"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -7016,37 +7038,37 @@
   <sheetData>
     <row r="1" ht="14.25">
       <c r="A1" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
     </row>
     <row r="2" ht="14.25"/>
     <row r="3" ht="14.25">
       <c r="C3" s="1" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4" ht="14.25">
       <c r="B4" t="s">
-        <v>545</v>
-      </c>
-      <c r="C4" s="106">
+        <v>550</v>
+      </c>
+      <c r="C4" s="98">
         <v>4410</v>
       </c>
-      <c r="D4" s="106">
+      <c r="D4" s="98">
         <v>6296</v>
       </c>
     </row>
     <row r="5" ht="14.25">
       <c r="B5" t="s">
-        <v>546</v>
-      </c>
-      <c r="C5" s="106">
+        <v>551</v>
+      </c>
+      <c r="C5" s="98">
         <v>1417</v>
       </c>
-      <c r="D5" s="106">
+      <c r="D5" s="98">
         <v>1957</v>
       </c>
     </row>
@@ -7058,107 +7080,107 @@
     </row>
     <row r="7" ht="14.25">
       <c r="A7" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="C7" s="121">
+        <v>361</v>
+      </c>
+      <c r="C7" s="109">
         <f>C4-C5</f>
         <v>2993</v>
       </c>
-      <c r="D7" s="121">
+      <c r="D7" s="109">
         <f>D4-D5</f>
         <v>4339</v>
       </c>
     </row>
     <row r="8" ht="14.25">
       <c r="B8" t="s">
-        <v>548</v>
-      </c>
-      <c r="C8" s="106">
+        <v>553</v>
+      </c>
+      <c r="C8" s="98">
         <v>903</v>
       </c>
-      <c r="D8" s="106">
+      <c r="D8" s="98">
         <v>1352</v>
       </c>
     </row>
     <row r="9" ht="14.25">
       <c r="B9" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C9" s="121">
+        <v>96</v>
+      </c>
+      <c r="C9" s="109">
         <f>C4-C5-C8</f>
         <v>2090</v>
       </c>
-      <c r="D9" s="121">
+      <c r="D9" s="109">
         <f>D4-D5-D8</f>
         <v>2987</v>
       </c>
     </row>
     <row r="10" ht="14.25">
       <c r="B10" t="s">
-        <v>91</v>
-      </c>
-      <c r="C10" s="106">
+        <v>97</v>
+      </c>
+      <c r="C10" s="98">
         <v>536</v>
       </c>
-      <c r="D10" s="106">
+      <c r="D10" s="98">
         <v>766</v>
       </c>
     </row>
     <row r="11" ht="14.25">
       <c r="B11" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="C11" s="121">
+        <v>554</v>
+      </c>
+      <c r="C11" s="109">
         <f>C9-C10</f>
         <v>1554</v>
       </c>
-      <c r="D11" s="121">
+      <c r="D11" s="109">
         <f>D9-D10</f>
         <v>2221</v>
       </c>
     </row>
     <row r="12" ht="14.25">
       <c r="B12" t="s">
-        <v>550</v>
-      </c>
-      <c r="C12" s="106">
+        <v>555</v>
+      </c>
+      <c r="C12" s="98">
         <v>11426</v>
       </c>
-      <c r="D12" s="106">
+      <c r="D12" s="98">
         <v>15224</v>
       </c>
     </row>
     <row r="13" ht="14.25">
       <c r="B13" t="s">
-        <v>551</v>
-      </c>
-      <c r="C13" s="106">
+        <v>556</v>
+      </c>
+      <c r="C13" s="98">
         <v>70771</v>
       </c>
-      <c r="D13" s="106">
+      <c r="D13" s="98">
         <v>92292</v>
       </c>
     </row>
     <row r="14" ht="14.25"/>
     <row r="15" ht="14.25">
       <c r="B15" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="C15" s="16">
         <f>C11/C12</f>
         <v>0.13600560126028358</v>
       </c>
-      <c r="D15" s="113">
+      <c r="D15" s="101">
         <f>D11/D12</f>
         <v>0.14588807146610616</v>
       </c>
     </row>
     <row r="16" ht="14.25">
       <c r="B16" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="C16" s="11">
         <f>C13/C12</f>
@@ -7171,36 +7193,36 @@
     </row>
     <row r="17" ht="14.25">
       <c r="B17" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="C17" s="16">
         <f>C5/C4</f>
         <v>0.32131519274376419</v>
       </c>
-      <c r="D17" s="113">
+      <c r="D17" s="101">
         <f>D5/D4</f>
         <v>0.31083227445997458</v>
       </c>
     </row>
     <row r="18" ht="14.25">
       <c r="B18" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="C18" s="16">
         <f>C8/C7</f>
         <v>0.30170397594386905</v>
       </c>
-      <c r="D18" s="113">
+      <c r="D18" s="101">
         <f>D8/D7</f>
         <v>0.3115925328416686</v>
       </c>
     </row>
     <row r="19" ht="14.25">
       <c r="A19" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="B19" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
     </row>
   </sheetData>
@@ -7237,10 +7259,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="B1" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1">
@@ -7304,7 +7326,7 @@
     </row>
     <row r="3">
       <c r="B3" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D3" s="7">
         <v>8927.7800000000007</v>
@@ -7323,7 +7345,7 @@
     </row>
     <row r="4">
       <c r="B4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D4" s="7">
         <v>2633.9299999999998</v>
@@ -7342,7 +7364,7 @@
     </row>
     <row r="5">
       <c r="B5" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="D5" s="7">
         <v>756.40999999999997</v>
@@ -7361,7 +7383,7 @@
     </row>
     <row r="6">
       <c r="B6" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D6" s="7">
         <v>85.069999999999993</v>
@@ -7380,7 +7402,7 @@
     </row>
     <row r="7">
       <c r="B7" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D7" s="7">
         <v>-0.31</v>
@@ -7399,7 +7421,7 @@
     </row>
     <row r="8" s="1" customFormat="1">
       <c r="B8" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D8" s="1">
         <f>SUM(D3:D7)</f>
@@ -7460,7 +7482,7 @@
     </row>
     <row r="9" s="0" customFormat="1">
       <c r="B9" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="F9" s="2"/>
       <c r="J9" s="11"/>
@@ -7476,7 +7498,7 @@
     </row>
     <row r="10" s="0" customFormat="1">
       <c r="B10" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F10" s="2"/>
       <c r="J10" s="11"/>
@@ -7524,7 +7546,7 @@
     </row>
     <row r="13">
       <c r="B13" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D13" s="7">
         <v>3511.9200000000001</v>
@@ -7581,7 +7603,7 @@
     </row>
     <row r="14">
       <c r="B14" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D14" s="7">
         <v>1330.4000000000001</v>
@@ -7628,7 +7650,7 @@
     </row>
     <row r="15">
       <c r="B15" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="D15" s="7">
         <v>4057.5700000000002</v>
@@ -7685,7 +7707,7 @@
     </row>
     <row r="16">
       <c r="B16" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D16" s="7">
         <v>111.84</v>
@@ -7742,7 +7764,7 @@
     </row>
     <row r="17">
       <c r="B17" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D17" s="7">
         <v>763.75</v>
@@ -7799,7 +7821,7 @@
     </row>
     <row r="18" s="1" customFormat="1">
       <c r="B18" s="1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D18" s="1">
         <f>SUM(D13:D17)</f>
@@ -7875,7 +7897,7 @@
     </row>
     <row r="20">
       <c r="B20" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D20" s="7">
         <f>D8-D18</f>
@@ -7936,7 +7958,7 @@
     </row>
     <row r="21">
       <c r="B21" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D21" s="7">
         <v>668.04999999999995</v>
@@ -7993,7 +8015,7 @@
     </row>
     <row r="22" s="1" customFormat="1">
       <c r="B22" s="1" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D22" s="1">
         <f>D20-D21</f>
@@ -8257,7 +8279,7 @@
     </row>
     <row r="24">
       <c r="B24" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D24">
         <v>24.780000000000001</v>
@@ -8282,13 +8304,13 @@
     </row>
     <row r="26">
       <c r="G26" s="1" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="T26" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="U26" s="16">
         <v>0.01</v>
@@ -8296,7 +8318,7 @@
     </row>
     <row r="27">
       <c r="B27" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="D27">
         <f>D8-D13</f>
@@ -8311,7 +8333,7 @@
         <v>9910.130000000001</v>
       </c>
       <c r="T27" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="U27" s="16">
         <v>0.12</v>
@@ -8319,7 +8341,7 @@
     </row>
     <row r="28">
       <c r="B28" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D28" s="17">
         <f>D27/D8</f>
@@ -8340,7 +8362,7 @@
         <v>0.63</v>
       </c>
       <c r="T28" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="U28" s="11">
         <f>NPV(U27,J22:BP22)</f>
@@ -8349,7 +8371,7 @@
     </row>
     <row r="29">
       <c r="B29" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D29" s="17"/>
       <c r="E29" s="17">
@@ -8362,7 +8384,7 @@
       </c>
       <c r="H29" s="7"/>
       <c r="T29" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="U29">
         <v>168900000</v>
@@ -8370,7 +8392,7 @@
     </row>
     <row r="30">
       <c r="B30" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="D30" s="17"/>
       <c r="E30" s="17">
@@ -8388,7 +8410,7 @@
         <v>0.070000000000000007</v>
       </c>
       <c r="T30" s="1" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="U30" s="1">
         <v>700</v>
@@ -8396,7 +8418,7 @@
     </row>
     <row r="31">
       <c r="B31" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D31" s="17"/>
       <c r="E31" s="17">
@@ -8414,7 +8436,7 @@
         <v>0.070000000000000007</v>
       </c>
       <c r="T31" s="1" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="U31" s="9">
         <f>U28*10000000/U29</f>
@@ -8423,7 +8445,7 @@
     </row>
     <row r="32">
       <c r="B32" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="D32" s="17"/>
       <c r="E32" s="17">
@@ -8443,7 +8465,7 @@
     </row>
     <row r="33">
       <c r="B33" s="2" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="D33" s="17"/>
       <c r="E33" s="17">
@@ -8464,7 +8486,7 @@
     </row>
     <row r="34">
       <c r="B34" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D34" s="17"/>
       <c r="E34" s="17">
@@ -8509,26 +8531,26 @@
   <sheetData>
     <row r="1" ht="16.5">
       <c r="A1" s="21" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B1" s="21" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" ht="16.5">
       <c r="A2" s="22" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" ht="16.5">
       <c r="A3" s="21" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" ht="14.25">
@@ -8540,10 +8562,10 @@
     </row>
     <row r="5" ht="16.5">
       <c r="A5" s="21" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="G5" s="22">
         <v>1999</v>
@@ -8558,34 +8580,34 @@
     <row r="6" ht="16.5">
       <c r="A6" s="21"/>
       <c r="G6" s="21" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="H6" s="21" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="I6" s="21" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" ht="16.5">
       <c r="A7" s="22" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="D7" s="21"/>
       <c r="I7" s="21" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="K7" s="21"/>
       <c r="L7" s="22" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" ht="16.5">
       <c r="A8" s="21" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="D8" s="24">
         <v>1</v>
@@ -8599,19 +8621,19 @@
     </row>
     <row r="9" ht="16.5">
       <c r="A9" s="21" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="D9" s="24">
         <v>1</v>
       </c>
       <c r="F9" s="21" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="K9" s="22" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="L9" s="25">
         <v>6353284188</v>
@@ -8619,16 +8641,16 @@
     </row>
     <row r="10" ht="16.5">
       <c r="A10" s="21" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="D10" s="24">
         <v>1</v>
       </c>
       <c r="K10" s="22" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="L10" s="26">
         <f>(L8*L9)/10000000</f>
@@ -8637,16 +8659,16 @@
     </row>
     <row r="11" ht="16.5">
       <c r="A11" s="21" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="D11" s="24">
         <v>1</v>
       </c>
       <c r="K11" s="22" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="L11" s="27">
         <f>67.18+10892.59</f>
@@ -8655,16 +8677,16 @@
     </row>
     <row r="12" ht="16.5">
       <c r="A12" s="21" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D12" s="24">
         <v>1</v>
       </c>
       <c r="K12" s="22" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="L12" s="21">
         <f>0</f>
@@ -8673,19 +8695,19 @@
     </row>
     <row r="13" ht="16.5">
       <c r="A13" s="21" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="D13" s="24">
         <v>0.77249999999999996</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="K13" s="22" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L13" s="28">
         <f>L10+L12-L11</f>
@@ -8694,10 +8716,10 @@
     </row>
     <row r="14" ht="16.5">
       <c r="A14" s="21" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="D14" s="24">
         <v>0.5</v>
@@ -8709,16 +8731,16 @@
     </row>
     <row r="17" ht="16.5">
       <c r="A17" s="21" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="18" ht="16.5">
       <c r="A18" s="21"/>
       <c r="B18" s="21" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="19" ht="14.25">
@@ -8727,20 +8749,20 @@
     </row>
     <row r="20" ht="16.5">
       <c r="A20" s="21" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
     </row>
     <row r="21" ht="16.5">
       <c r="B21" s="21" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="22" ht="16.5">
       <c r="B22" s="21" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="23" ht="14.25">
@@ -8749,15 +8771,15 @@
     </row>
     <row r="24" ht="16.5">
       <c r="A24" s="21" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="25" ht="16.5">
       <c r="B25" s="21" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
     </row>
     <row r="26" ht="14.25">
@@ -8766,15 +8788,15 @@
     </row>
     <row r="27" ht="16.5">
       <c r="A27" s="21" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="B27" s="21" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="28" ht="16.5">
       <c r="B28" s="21" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
     </row>
     <row r="30" ht="14.25">
@@ -8783,12 +8805,12 @@
     </row>
     <row r="31" ht="16.5">
       <c r="A31" s="21" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
     </row>
     <row r="32" ht="16.5">
       <c r="B32" s="21" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -8820,63 +8842,63 @@
   <sheetData>
     <row r="1" ht="16.5">
       <c r="A1" s="21" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="B1" s="21" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="C1" s="21" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="D1" s="23" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="F1" s="21" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="H1" s="23" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" s="22" customFormat="1" ht="16.5">
       <c r="B2" s="22"/>
       <c r="C2" s="22" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="D2" s="22" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E2" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="F2" s="22" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="G2" s="22" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="H2" s="22" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="I2" s="22" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="J2" s="22" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="K2" s="22" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="L2" s="22" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3" ht="16.5">
       <c r="A3" s="21" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="C3" s="21">
         <v>295.39999999999998</v>
@@ -8899,10 +8921,10 @@
     </row>
     <row r="4" ht="16.5">
       <c r="A4" s="21" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="C4" s="21">
         <v>1.48</v>
@@ -8925,10 +8947,10 @@
     </row>
     <row r="5" ht="16.5">
       <c r="A5" s="21" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C5" s="21">
         <v>0</v>
@@ -8952,10 +8974,10 @@
     </row>
     <row r="6" ht="16.5">
       <c r="A6" s="21" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="C6" s="21">
         <v>52.369999999999997</v>
@@ -8978,7 +9000,7 @@
     </row>
     <row r="7" s="22" customFormat="1" ht="16.5">
       <c r="B7" s="22" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="C7" s="22">
         <f>C3+C4+C5+C6</f>
@@ -9008,7 +9030,7 @@
     </row>
     <row r="8" ht="16.5">
       <c r="B8" s="21" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="C8" s="21">
         <v>0</v>
@@ -9031,7 +9053,7 @@
     </row>
     <row r="9" s="22" customFormat="1" ht="16.5">
       <c r="B9" s="22" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="C9" s="22">
         <f>C7+C8</f>
@@ -9068,7 +9090,7 @@
     </row>
     <row r="11" ht="16.5">
       <c r="B11" s="21" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="C11" s="21">
         <v>127.76000000000001</v>
@@ -9091,7 +9113,7 @@
     </row>
     <row r="12" ht="16.5">
       <c r="B12" s="21" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="C12" s="21">
         <v>0</v>
@@ -9114,7 +9136,7 @@
     </row>
     <row r="13" ht="16.5">
       <c r="B13" s="21" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C13" s="21">
         <v>0</v>
@@ -9137,7 +9159,7 @@
     </row>
     <row r="14" ht="16.5">
       <c r="B14" s="21" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="C14" s="21">
         <v>0</v>
@@ -9160,7 +9182,7 @@
     </row>
     <row r="15" ht="16.5">
       <c r="B15" s="21" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="C15" s="21">
         <v>27.649999999999999</v>
@@ -9183,7 +9205,7 @@
     </row>
     <row r="16" s="22" customFormat="1" ht="16.5">
       <c r="B16" s="22" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C16" s="22">
         <f>SUM(C11:C15)</f>
@@ -9219,7 +9241,7 @@
     </row>
     <row r="18" ht="16.5">
       <c r="B18" s="21" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="C18" s="21">
         <f>C9-C16</f>
@@ -9247,7 +9269,7 @@
     </row>
     <row r="19" ht="16.5">
       <c r="B19" s="21" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="C19" s="21">
         <v>0</v>
@@ -9270,7 +9292,7 @@
     </row>
     <row r="20" ht="16.5">
       <c r="B20" s="21" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C20" s="21">
         <f>C18+C19</f>
@@ -9305,7 +9327,7 @@
     </row>
     <row r="22" ht="16.5">
       <c r="B22" s="21" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C22" s="21">
         <f>12.9+0-49.01</f>
@@ -9334,7 +9356,7 @@
     </row>
     <row r="23" s="22" customFormat="1" ht="16.5">
       <c r="B23" s="22" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C23" s="22">
         <f>C20-C22</f>
@@ -9364,10 +9386,10 @@
     </row>
     <row r="24" ht="16.5">
       <c r="A24" s="21" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="C24" s="21">
         <v>0</v>
@@ -9391,7 +9413,7 @@
     </row>
     <row r="25" s="22" customFormat="1" ht="16.5">
       <c r="B25" s="22" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="C25" s="22">
         <f>C24+C23</f>
@@ -9421,10 +9443,10 @@
     </row>
     <row r="26" s="22" customFormat="1" ht="16.5">
       <c r="A26" s="21" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B26" s="22" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="C26" s="22">
         <f>C25</f>
@@ -9464,7 +9486,7 @@
     </row>
     <row r="28" s="22" customFormat="1" ht="16.5">
       <c r="B28" s="22" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="C28" s="22"/>
       <c r="D28" s="22">
@@ -9506,7 +9528,7 @@
     </row>
     <row r="31" ht="16.5">
       <c r="B31" s="21" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="C31" s="31">
         <v>5168355</v>
@@ -9529,7 +9551,7 @@
     </row>
     <row r="32" ht="16.5">
       <c r="B32" s="21" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C32" s="27">
         <f>C25*10000000/C31</f>
@@ -9567,7 +9589,7 @@
     </row>
     <row r="34" ht="16.5">
       <c r="B34" s="21" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="C34" s="21"/>
       <c r="D34" s="34">
@@ -9590,7 +9612,7 @@
     </row>
     <row r="35" ht="16.5">
       <c r="B35" s="21" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C35" s="21"/>
       <c r="D35" s="34">
@@ -9604,7 +9626,7 @@
     </row>
     <row r="36" ht="16.5">
       <c r="B36" s="21" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="C36" s="21"/>
       <c r="D36" s="34">
@@ -9624,7 +9646,7 @@
     </row>
     <row r="37" ht="16.5">
       <c r="B37" s="21" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="C37" s="21"/>
       <c r="D37" s="34">
@@ -9644,7 +9666,7 @@
     </row>
     <row r="38" ht="16.5">
       <c r="B38" s="21" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="C38" s="21"/>
       <c r="D38" s="34">
@@ -9664,10 +9686,10 @@
     </row>
     <row r="40" s="36" customFormat="1" ht="16.5">
       <c r="A40" s="37" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="B40" s="38" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="C40" s="36"/>
       <c r="D40" s="36"/>
@@ -9679,7 +9701,7 @@
     <row r="41" ht="13.800000000000001" customHeight="1"/>
     <row r="42" ht="16.5">
       <c r="B42" s="21" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="G42" s="21"/>
       <c r="H42" s="21">
@@ -9688,7 +9710,7 @@
     </row>
     <row r="43" ht="16.5">
       <c r="B43" s="21" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="H43" s="21">
         <v>235.03</v>
@@ -9697,7 +9719,7 @@
     <row r="44" ht="16.5">
       <c r="A44" s="21"/>
       <c r="B44" s="21" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="H44" s="21">
         <v>6.4000000000000004</v>
@@ -9705,7 +9727,7 @@
     </row>
     <row r="45" ht="16.5">
       <c r="B45" s="21" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="H45" s="21">
         <v>447</v>
@@ -9713,7 +9735,7 @@
     </row>
     <row r="46" ht="16.5">
       <c r="B46" s="21" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="H46" s="21">
         <v>0</v>
@@ -9721,7 +9743,7 @@
     </row>
     <row r="47" ht="16.5">
       <c r="B47" s="21" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="H47" s="21">
         <v>0</v>
@@ -9729,7 +9751,7 @@
     </row>
     <row r="48" ht="16.5">
       <c r="B48" s="21" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="H48" s="21">
         <v>0</v>
@@ -9738,7 +9760,7 @@
     <row r="49" ht="16.5">
       <c r="A49" s="21"/>
       <c r="B49" s="22" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="H49" s="21">
         <f>SUM(H42:H48)</f>
@@ -9747,7 +9769,7 @@
     </row>
     <row r="50" ht="16.5">
       <c r="B50" s="21" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="H50" s="21">
         <v>33.719999999999999</v>
@@ -9755,7 +9777,7 @@
     </row>
     <row r="51" ht="16.5">
       <c r="B51" s="22" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="H51" s="21">
         <f>H49+H50</f>
@@ -9767,7 +9789,7 @@
     </row>
     <row r="53" ht="16.5">
       <c r="B53" s="21" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="H53" s="21">
         <v>0</v>
@@ -9775,7 +9797,7 @@
     </row>
     <row r="54" ht="16.5">
       <c r="B54" s="21" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="H54" s="21">
         <v>6.5499999999999998</v>
@@ -9783,7 +9805,7 @@
     </row>
     <row r="55" ht="16.5">
       <c r="B55" s="21" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="H55" s="21">
         <v>83.409999999999997</v>
@@ -9791,7 +9813,7 @@
     </row>
     <row r="56" ht="16.5">
       <c r="B56" s="21" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H56" s="21">
         <v>12.359999999999999</v>
@@ -9799,7 +9821,7 @@
     </row>
     <row r="57" ht="16.5">
       <c r="B57" s="21" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="H57" s="21">
         <v>83.469999999999999</v>
@@ -9807,7 +9829,7 @@
     </row>
     <row r="58" ht="16.5">
       <c r="B58" s="22" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H58" s="21">
         <f>SUM(H53:H57)</f>
@@ -9819,7 +9841,7 @@
     </row>
     <row r="60" ht="16.5">
       <c r="B60" s="21" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="H60" s="21">
         <f>H51-H58</f>
@@ -9828,7 +9850,7 @@
     </row>
     <row r="61" ht="16.5">
       <c r="B61" s="21" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="H61" s="21">
         <v>0</v>
@@ -9836,7 +9858,7 @@
     </row>
     <row r="62" ht="16.5">
       <c r="B62" s="21" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H62" s="21">
         <f>H60-H61</f>
@@ -9848,7 +9870,7 @@
     </row>
     <row r="64" ht="16.5">
       <c r="B64" s="21" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="H64" s="21">
         <f>-44.8-59.68</f>
@@ -9857,7 +9879,7 @@
     </row>
     <row r="65" ht="14.25">
       <c r="B65" s="22" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="H65" s="21">
         <f>H62+H64</f>
@@ -9866,7 +9888,7 @@
     </row>
     <row r="66" ht="14.25">
       <c r="B66" s="21" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="H66" s="21">
         <v>0</v>
@@ -9874,7 +9896,7 @@
     </row>
     <row r="67" ht="14.25">
       <c r="B67" s="22" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="H67" s="21">
         <f>H65+H66</f>
@@ -9883,7 +9905,7 @@
     </row>
     <row r="68" ht="14.25">
       <c r="B68" s="22" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="H68" s="21">
         <f>H67</f>
@@ -9892,7 +9914,7 @@
     </row>
     <row r="70" ht="14.25">
       <c r="B70" s="21" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="H70" s="39">
         <f>H68*10000000/H89</f>
@@ -9904,13 +9926,13 @@
     </row>
     <row r="86" ht="14.25">
       <c r="A86" s="21" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="B86" s="21"/>
     </row>
     <row r="87" ht="14.25">
       <c r="B87" s="21" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="H87" s="21">
         <v>6353.1400000000003</v>
@@ -9918,7 +9940,7 @@
     </row>
     <row r="88" ht="14.25">
       <c r="B88" s="21" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="H88" s="21">
         <v>10</v>
@@ -9926,7 +9948,7 @@
     </row>
     <row r="89" ht="14.25">
       <c r="B89" s="21" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="H89" s="21">
         <f>H87/H88*10000000</f>
@@ -9951,16 +9973,15 @@
   <cols>
     <col customWidth="1" min="1" max="1" style="21" width="16.7109375"/>
     <col customWidth="1" min="2" max="2" style="21" width="26.7109375"/>
-    <col customWidth="1" min="3" max="6" style="21" width="16.7109375"/>
-    <col customWidth="1" min="7" max="16384" style="21" width="16.7109375"/>
+    <col customWidth="1" min="3" max="16384" style="21" width="16.7109375"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5">
       <c r="A1" s="22" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="C1" s="22"/>
       <c r="D1" s="22"/>
@@ -9971,34 +9992,34 @@
     <row r="2" s="22" customFormat="1" ht="16.5">
       <c r="B2" s="22"/>
       <c r="C2" s="22" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="D2" s="22" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="E2" s="22" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="F2" s="22" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="G2" s="22" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="H2" s="22" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="I2" s="22" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="J2" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="K2" s="22" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="L2" s="22" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="M2" s="22"/>
       <c r="N2" s="22"/>
@@ -10053,7 +10074,7 @@
     </row>
     <row r="3" ht="16.5">
       <c r="B3" s="21" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="C3" s="21"/>
       <c r="D3" s="21"/>
@@ -10083,7 +10104,7 @@
     </row>
     <row r="4" ht="16.5">
       <c r="B4" s="21" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="C4" s="21"/>
       <c r="D4" s="21"/>
@@ -10113,7 +10134,7 @@
     </row>
     <row r="5" ht="16.5">
       <c r="B5" s="21" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="C5" s="21"/>
       <c r="D5" s="21"/>
@@ -10143,7 +10164,7 @@
     </row>
     <row r="6" ht="16.5">
       <c r="B6" s="21" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="C6" s="21"/>
       <c r="D6" s="21"/>
@@ -10173,7 +10194,7 @@
     </row>
     <row r="7" ht="16.5">
       <c r="B7" s="21" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="C7" s="21"/>
       <c r="D7" s="21"/>
@@ -10203,7 +10224,7 @@
     </row>
     <row r="8" s="22" customFormat="1" ht="16.5">
       <c r="B8" s="22" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="C8" s="22">
         <v>3714.8137000000002</v>
@@ -10250,7 +10271,7 @@
     </row>
     <row r="9" ht="16.5">
       <c r="B9" s="21" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="C9" s="21">
         <v>0.65659999999999996</v>
@@ -10288,7 +10309,7 @@
     </row>
     <row r="10" ht="16.5">
       <c r="B10" s="21" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="C10" s="21">
         <f>C8+C9</f>
@@ -10382,10 +10403,10 @@
     </row>
     <row r="11" ht="16.5">
       <c r="A11" s="21" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="C11" s="21"/>
       <c r="D11" s="21"/>
@@ -10413,7 +10434,7 @@
     <row r="12" ht="16.5">
       <c r="A12" s="21"/>
       <c r="B12" s="21" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="C12" s="21"/>
       <c r="D12" s="21"/>
@@ -10465,7 +10486,7 @@
     </row>
     <row r="14" ht="16.5">
       <c r="B14" s="21" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C14" s="21">
         <v>1957.8152</v>
@@ -10547,7 +10568,7 @@
     </row>
     <row r="15" ht="16.5">
       <c r="B15" s="21" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="C15" s="21">
         <v>324.90370000000001</v>
@@ -10618,7 +10639,7 @@
     </row>
     <row r="16" ht="16.5">
       <c r="B16" s="21" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C16" s="21">
         <v>203.2252</v>
@@ -10700,7 +10721,7 @@
     </row>
     <row r="17" ht="16.5">
       <c r="B17" s="21" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="C17" s="21">
         <v>30.1022</v>
@@ -10782,7 +10803,7 @@
     </row>
     <row r="18" ht="16.5">
       <c r="B18" s="21" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="C18" s="21">
         <f>315.3412+190.8581</f>
@@ -10868,7 +10889,7 @@
     </row>
     <row r="19" s="22" customFormat="1" ht="16.5">
       <c r="B19" s="22" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="C19" s="22">
         <f>SUM(C14:C18)</f>
@@ -10962,7 +10983,7 @@
     </row>
     <row r="20" ht="16.5">
       <c r="B20" s="21" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C20" s="21">
         <f>C10-C19</f>
@@ -11058,7 +11079,7 @@
     </row>
     <row r="21" ht="16.5">
       <c r="B21" s="21" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C21" s="21">
         <v>-222.08850000000001</v>
@@ -11147,7 +11168,7 @@
     </row>
     <row r="22" s="22" customFormat="1" ht="16.5">
       <c r="B22" s="22" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C22" s="22">
         <f>C20+C21</f>
@@ -11447,7 +11468,7 @@
     </row>
     <row r="23" ht="16.5">
       <c r="B23" s="21" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="C23" s="21">
         <v>0</v>
@@ -11489,7 +11510,7 @@
     </row>
     <row r="24" ht="16.5">
       <c r="B24" s="21" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="C24" s="21">
         <f>C22</f>
@@ -11539,7 +11560,7 @@
     </row>
     <row r="25" ht="16.5">
       <c r="B25" s="21" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="C25" s="21">
         <v>0</v>
@@ -11577,7 +11598,7 @@
     </row>
     <row r="26" ht="16.5">
       <c r="B26" s="21" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C26" s="21">
         <v>0</v>
@@ -11624,7 +11645,7 @@
     <row r="27" ht="16.5">
       <c r="A27" s="21"/>
       <c r="B27" s="21" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="C27" s="21"/>
       <c r="D27" s="21"/>
@@ -11666,7 +11687,7 @@
     </row>
     <row r="29" ht="16.5">
       <c r="B29" s="21" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="C29" s="21"/>
       <c r="D29" s="21"/>
@@ -11695,7 +11716,7 @@
     </row>
     <row r="30" ht="16.5">
       <c r="B30" s="21" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="C30" s="21"/>
       <c r="D30" s="21"/>
@@ -11724,7 +11745,7 @@
     </row>
     <row r="31" ht="16.5">
       <c r="B31" s="21" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="C31" s="21"/>
       <c r="D31" s="21"/>
@@ -11761,7 +11782,7 @@
     </row>
     <row r="32" ht="16.5">
       <c r="A32" s="21" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E32" s="21"/>
       <c r="F32" s="21"/>
@@ -11772,20 +11793,20 @@
       <c r="K32" s="21"/>
       <c r="L32" s="21"/>
       <c r="M32" s="22" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="N32" s="22" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="O32" s="22" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="P32" s="22" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="Q32" s="21"/>
       <c r="AC32" s="21" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="AD32" s="42">
         <v>0.01</v>
@@ -11793,10 +11814,10 @@
     </row>
     <row r="33" s="22" customFormat="1" ht="16.5">
       <c r="A33" s="22" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="B33" s="22" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="C33" s="43">
         <f>C14/C8</f>
@@ -11843,7 +11864,7 @@
         <v>0.47699819880105726</v>
       </c>
       <c r="N33" s="44">
-        <f>MEDIAN(C33:L33)</f>
+        <f t="shared" ref="N33:N38" si="4">MEDIAN(C33:L33)</f>
         <v>0.47996430425352465</v>
       </c>
       <c r="O33" s="44">
@@ -11854,7 +11875,7 @@
       </c>
       <c r="Q33" s="22"/>
       <c r="AC33" s="22" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="AD33" s="44">
         <v>0.11</v>
@@ -11863,7 +11884,7 @@
     <row r="34" ht="16.5">
       <c r="A34" s="21"/>
       <c r="B34" s="21" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="C34" s="21"/>
       <c r="D34" s="24">
@@ -11907,7 +11928,7 @@
         <v>0.20759519512642644</v>
       </c>
       <c r="N34" s="44">
-        <f>MEDIAN(C34:L34)</f>
+        <f t="shared" si="4"/>
         <v>0.17126890485872281</v>
       </c>
       <c r="O34" s="42">
@@ -11917,7 +11938,7 @@
         <v>0.12</v>
       </c>
       <c r="AC34" s="21" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="AD34" s="21">
         <f>NPV(AD33,S22:CA22)</f>
@@ -11926,7 +11947,7 @@
     </row>
     <row r="35" ht="16.5">
       <c r="B35" s="21" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="C35" s="34" t="e">
         <f>D26/C26-1</f>
@@ -11970,7 +11991,7 @@
       </c>
       <c r="M35" s="21"/>
       <c r="AC35" s="21" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="AD35" s="21">
         <v>840437697</v>
@@ -11978,7 +11999,7 @@
     </row>
     <row r="36" ht="16.5">
       <c r="B36" s="21" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="C36" s="34" t="e">
         <f>C16/B16-1%</f>
@@ -12021,11 +12042,11 @@
         <v>1.8120043076515948</v>
       </c>
       <c r="M36" s="42">
-        <f>AVERAGE(D36:L36)</f>
+        <f t="shared" ref="M36:M38" si="5">AVERAGE(D36:L36)</f>
         <v>1.3272078184373999</v>
       </c>
       <c r="N36" s="44">
-        <f>MEDIAN(C36:L36)</f>
+        <f t="shared" si="4"/>
         <v>1.280072294183989</v>
       </c>
       <c r="O36" s="42">
@@ -12036,7 +12057,7 @@
       </c>
       <c r="Q36" s="21"/>
       <c r="AC36" s="21" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="AD36" s="21">
         <v>1651.8</v>
@@ -12044,7 +12065,7 @@
     </row>
     <row r="37" ht="16.5">
       <c r="B37" s="21" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="C37" s="34" t="e">
         <f>C18/B18-1%</f>
@@ -12087,11 +12108,11 @@
         <v>1.1159031024224395</v>
       </c>
       <c r="M37" s="42">
-        <f>AVERAGE(D37:L37)</f>
+        <f t="shared" si="5"/>
         <v>1.2150921279173628</v>
       </c>
       <c r="N37" s="44">
-        <f>MEDIAN(C37:L37)</f>
+        <f t="shared" si="4"/>
         <v>1.1403037073238846</v>
       </c>
       <c r="O37" s="42">
@@ -12101,7 +12122,7 @@
         <v>0.14999999999999999</v>
       </c>
       <c r="AC37" s="21" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="AD37" s="21">
         <f>AD34*10000000/AD35</f>
@@ -12110,7 +12131,7 @@
     </row>
     <row r="38" ht="16.5">
       <c r="B38" s="21" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="C38" s="34"/>
       <c r="D38" s="34">
@@ -12150,11 +12171,11 @@
         <v>0.56090612158887354</v>
       </c>
       <c r="M38" s="42">
-        <f>AVERAGE(D38:L38)</f>
+        <f t="shared" si="5"/>
         <v>0.2055263612820778</v>
       </c>
       <c r="N38" s="44">
-        <f>MEDIAN(C38:L38)</f>
+        <f t="shared" si="4"/>
         <v>0.11926513260746674</v>
       </c>
       <c r="O38" s="42">
@@ -12166,7 +12187,7 @@
     </row>
     <row r="39" ht="16.5">
       <c r="B39" s="21" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C39" s="34">
         <f>C21/C20*-1</f>
@@ -12238,66 +12259,66 @@
   <sheetData>
     <row r="3">
       <c r="B3" s="22" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="21" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="21" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="21" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="21" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="21" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="21" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="21" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="21" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="21" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
     </row>
     <row r="17">
       <c r="C17" s="21" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="21"/>
       <c r="C20" s="21" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
     </row>
   </sheetData>
@@ -12325,35 +12346,35 @@
   <sheetData>
     <row r="1" ht="16.5">
       <c r="A1" s="21" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="C1" s="21" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
     </row>
     <row r="2" ht="16.5">
       <c r="A2" s="21" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
     </row>
     <row r="3" ht="16.5">
       <c r="A3" s="22" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" ht="16.5">
       <c r="A4" s="21"/>
       <c r="B4" s="21" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
     </row>
     <row r="5" ht="16.5">
       <c r="A5" s="21"/>
       <c r="B5" s="22" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="C5" s="42">
         <v>0.84999999999999998</v>
@@ -12362,7 +12383,7 @@
     <row r="6" ht="16.5">
       <c r="A6" s="21"/>
       <c r="B6" s="22" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="C6" s="42">
         <v>0.80000000000000004</v>
@@ -12371,7 +12392,7 @@
     <row r="7" ht="16.5">
       <c r="A7" s="21"/>
       <c r="B7" s="22" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="C7" s="42">
         <v>0.75</v>
@@ -12385,13 +12406,13 @@
     </row>
     <row r="9" ht="16.5">
       <c r="A9" s="22" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="H9" s="21"/>
     </row>
     <row r="10" ht="16.5">
       <c r="A10" s="21" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="B10" s="21"/>
       <c r="G10" s="21" t="s">
@@ -12403,7 +12424,7 @@
     </row>
     <row r="11" ht="16.5">
       <c r="G11" s="21" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="H11" s="21">
         <v>401461676</v>
@@ -12412,10 +12433,10 @@
     <row r="12" ht="16.5">
       <c r="A12" s="22"/>
       <c r="B12" s="22" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="G12" s="21" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="H12" s="41">
         <f>H10*H11/1000000</f>
@@ -12426,7 +12447,7 @@
     <row r="13" ht="16.5">
       <c r="A13" s="21"/>
       <c r="G13" s="21" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="H13" s="21">
         <f>50365.46+93.14</f>
@@ -12436,7 +12457,7 @@
     <row r="14" ht="16.5">
       <c r="A14" s="21"/>
       <c r="G14" s="21" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="H14" s="21">
         <f>163714.7+423613.13</f>
@@ -12446,7 +12467,7 @@
     <row r="15" ht="16.5">
       <c r="A15" s="21"/>
       <c r="G15" s="21" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="H15" s="41">
         <f>H12+H14-H13</f>
@@ -12467,21 +12488,21 @@
     </row>
     <row r="23" ht="16.5">
       <c r="A23" s="46" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="B23" s="21"/>
     </row>
     <row r="24" ht="14.25">
       <c r="D24" s="23" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
     </row>
     <row r="25" ht="16.5">
       <c r="C25" s="22" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="D25" s="22" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="E25" s="21"/>
       <c r="G25" s="21"/>
@@ -12489,18 +12510,18 @@
     </row>
     <row r="26" ht="16.5">
       <c r="B26" s="22" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="G26" s="22" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="H26" s="21" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
     </row>
     <row r="27" ht="16.5">
       <c r="B27" s="21" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="C27" s="47">
         <v>60373.449999999997</v>
@@ -12509,18 +12530,18 @@
         <v>77701.830000000002</v>
       </c>
       <c r="G27" s="48" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="H27" s="48" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="I27" s="48" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28" ht="16.5">
       <c r="B28" s="21" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="C28" s="47">
         <v>2346.5700000000002</v>
@@ -12529,7 +12550,7 @@
         <v>2654.7600000000002</v>
       </c>
       <c r="G28" s="21" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="H28" s="49">
         <v>599079.01000000001</v>
@@ -12540,10 +12561,10 @@
     </row>
     <row r="29" ht="16.5">
       <c r="A29" s="21" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="B29" s="21" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="C29" s="47">
         <v>178.36000000000001</v>
@@ -12552,7 +12573,7 @@
         <v>98.950000000000003</v>
       </c>
       <c r="G29" s="21" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="H29" s="49">
         <v>206.81</v>
@@ -12564,7 +12585,7 @@
     <row r="30" ht="16.5">
       <c r="A30" s="21"/>
       <c r="B30" s="21" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="C30" s="47">
         <v>0</v>
@@ -12573,7 +12594,7 @@
         <v>0</v>
       </c>
       <c r="G30" s="21" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="H30" s="49">
         <v>3745.7600000000002</v>
@@ -12582,10 +12603,10 @@
     </row>
     <row r="31" ht="16.5">
       <c r="A31" s="21" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="B31" s="21" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="C31" s="47">
         <v>881871.70999999996</v>
@@ -12594,7 +12615,7 @@
         <v>705543.83999999997</v>
       </c>
       <c r="G31" s="21" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="H31" s="49">
         <v>26.379999999999999</v>
@@ -12603,10 +12624,10 @@
     </row>
     <row r="32" ht="16.5">
       <c r="A32" s="21" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="B32" s="21" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="C32" s="47">
         <v>7124.7200000000003</v>
@@ -12615,7 +12636,7 @@
         <v>5457.1199999999999</v>
       </c>
       <c r="G32" s="21" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="H32" s="49">
         <v>9202.5699999999997</v>
@@ -12626,7 +12647,7 @@
     </row>
     <row r="33" ht="16.5">
       <c r="B33" s="21" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="C33" s="47">
         <v>4136.1199999999999</v>
@@ -12635,7 +12656,7 @@
         <v>3453</v>
       </c>
       <c r="G33" s="21" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="H33" s="49">
         <v>1.0600000000000001</v>
@@ -12646,7 +12667,7 @@
       <c r="C34" s="47"/>
       <c r="D34" s="47"/>
       <c r="G34" s="21" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="H34" s="49">
         <v>371.29000000000002</v>
@@ -12657,7 +12678,7 @@
     </row>
     <row r="35" ht="16.5">
       <c r="B35" s="21" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="C35" s="47">
         <v>724.86000000000001</v>
@@ -12666,7 +12687,7 @@
         <v>474.56999999999999</v>
       </c>
       <c r="G35" s="21" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="H35" s="49">
         <v>27.059999999999999</v>
@@ -12675,7 +12696,7 @@
     </row>
     <row r="36" ht="16.5">
       <c r="B36" s="21" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="C36" s="47">
         <v>975.77999999999997</v>
@@ -12684,7 +12705,7 @@
         <v>640.98000000000002</v>
       </c>
       <c r="G36" s="21" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="H36" s="49">
         <v>1058.5699999999999</v>
@@ -12695,7 +12716,7 @@
     </row>
     <row r="37" ht="16.5">
       <c r="B37" s="21" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="C37" s="47">
         <v>91.069999999999993</v>
@@ -12704,7 +12725,7 @@
         <v>82.019999999999996</v>
       </c>
       <c r="G37" s="21" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="H37" s="49">
         <v>1868.26</v>
@@ -12715,7 +12736,7 @@
     </row>
     <row r="38" ht="16.5">
       <c r="B38" s="21" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="C38" s="47">
         <v>4255.2399999999998</v>
@@ -12724,10 +12745,10 @@
         <v>3272.3699999999999</v>
       </c>
       <c r="F38" s="21" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="G38" s="21" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="H38" s="49">
         <v>37963.510000000002</v>
@@ -12738,7 +12759,7 @@
     </row>
     <row r="39" ht="16.5">
       <c r="B39" s="21" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="C39" s="47">
         <v>111.11</v>
@@ -12747,7 +12768,7 @@
         <v>142.22999999999999</v>
       </c>
       <c r="G39" s="21" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="H39" s="49">
         <v>1894.0899999999999</v>
@@ -12756,7 +12777,7 @@
     </row>
     <row r="40" ht="16.5">
       <c r="B40" s="21" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="C40" s="47">
         <v>883.15999999999997</v>
@@ -12767,7 +12788,7 @@
     </row>
     <row r="41" ht="16.5">
       <c r="B41" s="21" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="C41" s="47">
         <v>299.95999999999998</v>
@@ -12778,7 +12799,7 @@
     </row>
     <row r="42" ht="16.5">
       <c r="B42" s="21" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="C42" s="47">
         <v>58.350000000000001</v>
@@ -12789,7 +12810,7 @@
     </row>
     <row r="43" ht="16.5">
       <c r="B43" s="21" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="C43" s="47">
         <v>3.6499999999999999</v>
@@ -12800,10 +12821,10 @@
     </row>
     <row r="44" ht="16.5">
       <c r="A44" s="21" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="B44" s="21" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="C44" s="47">
         <v>1260.0899999999999</v>
@@ -12819,7 +12840,7 @@
     <row r="46" s="22" customFormat="1" ht="16.5">
       <c r="A46" s="22"/>
       <c r="B46" s="22" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="C46" s="50">
         <f>SUM(C27:C44)</f>
@@ -12835,15 +12856,15 @@
     </row>
     <row r="48" ht="16.5">
       <c r="A48" s="21" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="B48" s="21" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
     </row>
     <row r="49" ht="16.5">
       <c r="B49" s="21" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
     </row>
     <row r="51" ht="14.25">
@@ -12852,17 +12873,17 @@
     </row>
     <row r="52" ht="16.5">
       <c r="B52" s="22" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="C52" s="21"/>
       <c r="D52" s="21"/>
     </row>
     <row r="53" ht="16.5">
       <c r="A53" s="21" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="B53" s="21" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="C53" s="21">
         <v>138.86000000000001</v>
@@ -12873,10 +12894,10 @@
     </row>
     <row r="54" ht="16.5">
       <c r="A54" s="21" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="B54" s="21" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="C54" s="21">
         <f>7.68+1381.23</f>
@@ -12889,7 +12910,7 @@
     </row>
     <row r="55" ht="16.5">
       <c r="B55" s="21" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="C55" s="21">
         <f>1280.7</f>
@@ -12903,7 +12924,7 @@
     <row r="56" ht="16.5">
       <c r="A56" s="21"/>
       <c r="B56" s="21" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="C56" s="21">
         <v>174762.20000000001</v>
@@ -12914,7 +12935,7 @@
     </row>
     <row r="57" ht="16.5">
       <c r="B57" s="21" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="C57" s="21">
         <v>500519.53000000003</v>
@@ -12925,7 +12946,7 @@
     </row>
     <row r="58" ht="16.5">
       <c r="B58" s="21" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="C58" s="21">
         <v>4018.2600000000002</v>
@@ -12936,7 +12957,7 @@
     </row>
     <row r="59" ht="16.5">
       <c r="B59" s="21" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="C59" s="21">
         <v>3309.73</v>
@@ -12947,7 +12968,7 @@
     </row>
     <row r="60" ht="16.5">
       <c r="B60" s="21" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="C60" s="21">
         <v>125.91</v>
@@ -12958,7 +12979,7 @@
     </row>
     <row r="61" ht="16.5">
       <c r="B61" s="21" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="C61" s="21">
         <v>16014.9</v>
@@ -12969,7 +12990,7 @@
     </row>
     <row r="63" ht="16.5">
       <c r="B63" s="21" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="C63" s="21">
         <v>551.67999999999995</v>
@@ -12980,7 +13001,7 @@
     </row>
     <row r="64" ht="16.5">
       <c r="B64" s="21" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="C64" s="21">
         <v>3733.27</v>
@@ -12991,7 +13012,7 @@
     </row>
     <row r="65" ht="16.5">
       <c r="B65" s="21" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="C65" s="21">
         <v>167.62</v>
@@ -13002,7 +13023,7 @@
     </row>
     <row r="66" ht="16.5">
       <c r="B66" s="21" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="C66" s="21">
         <v>11142.16</v>
@@ -13014,7 +13035,7 @@
     <row r="67" s="22" customFormat="1" ht="16.5">
       <c r="A67" s="22"/>
       <c r="B67" s="22" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="C67" s="22">
         <f>SUM(C53:C66)</f>
@@ -13037,17 +13058,17 @@
     </row>
     <row r="70" ht="16.5">
       <c r="B70" s="22" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="C70" s="21"/>
       <c r="D70" s="21"/>
     </row>
     <row r="71" ht="14.25">
       <c r="A71" s="21" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="B71" s="21" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="C71" s="21">
         <v>4014.6199999999999</v>
@@ -13071,7 +13092,7 @@
     <row r="73" s="22" customFormat="1" ht="14.25">
       <c r="A73" s="22"/>
       <c r="B73" s="22" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="C73" s="22">
         <f>SUM(C71:C72)</f>
@@ -13092,7 +13113,7 @@
     <row r="75" s="22" customFormat="1" ht="14.25">
       <c r="A75" s="22"/>
       <c r="B75" s="22" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="C75" s="22">
         <f>C73+C67</f>
@@ -13139,53 +13160,53 @@
   <sheetData>
     <row r="1" ht="16.5">
       <c r="A1" s="21" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="B1" s="21" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
     </row>
     <row r="2" ht="16.5">
       <c r="C2" s="23" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="E2" s="23" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="G2" s="23" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="K2" s="22" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
     </row>
     <row r="3" s="22" customFormat="1" ht="16.5">
       <c r="B3" s="22" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="D3" s="22" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="E3" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="F3" s="22" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="G3" s="22" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H3" s="22" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="I3" s="22" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="J3" s="22" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="K3" s="22" t="str">
         <f>C3</f>
@@ -13504,7 +13525,7 @@
     </row>
     <row r="5" ht="16.5">
       <c r="B5" s="21" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="C5" s="51">
         <v>145457.01000000001</v>
@@ -13527,7 +13548,7 @@
       <c r="I5" s="29"/>
       <c r="J5" s="29"/>
       <c r="K5" s="51">
-        <f t="shared" ref="K5:K9" si="4">C5</f>
+        <f t="shared" ref="K5:K9" si="6">C5</f>
         <v>145457.01000000001</v>
       </c>
       <c r="L5" s="25"/>
@@ -13535,10 +13556,10 @@
     </row>
     <row r="6" ht="16.5">
       <c r="A6" s="21" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="C6" s="51">
         <v>48.100000000000001</v>
@@ -13561,7 +13582,7 @@
       <c r="I6" s="29"/>
       <c r="J6" s="29"/>
       <c r="K6" s="51">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>48.100000000000001</v>
       </c>
       <c r="L6" s="25"/>
@@ -13569,7 +13590,7 @@
     </row>
     <row r="7" ht="16.5">
       <c r="B7" s="21" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="C7" s="51">
         <v>640.05999999999995</v>
@@ -13592,7 +13613,7 @@
       <c r="I7" s="29"/>
       <c r="J7" s="29"/>
       <c r="K7" s="51">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>640.05999999999995</v>
       </c>
       <c r="L7" s="25"/>
@@ -13600,7 +13621,7 @@
     </row>
     <row r="8" ht="16.5">
       <c r="B8" s="21" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="C8" s="51">
         <v>1723.3399999999999</v>
@@ -13623,7 +13644,7 @@
       <c r="I8" s="29"/>
       <c r="J8" s="29"/>
       <c r="K8" s="51">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1723.3399999999999</v>
       </c>
       <c r="L8" s="25"/>
@@ -13631,10 +13652,10 @@
     </row>
     <row r="9" ht="16.5">
       <c r="A9" s="21" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="C9" s="51">
         <v>88.870000000000005</v>
@@ -13657,7 +13678,7 @@
       <c r="I9" s="29"/>
       <c r="J9" s="29"/>
       <c r="K9" s="51">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>88.870000000000005</v>
       </c>
       <c r="L9" s="25"/>
@@ -13666,7 +13687,7 @@
     <row r="10" ht="16.5">
       <c r="A10" s="21"/>
       <c r="B10" s="21" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="C10" s="52">
         <v>2659.1900000000001</v>
@@ -13689,7 +13710,7 @@
       <c r="I10" s="29"/>
       <c r="J10" s="29"/>
       <c r="K10" s="51">
-        <f t="shared" ref="K10:K46" si="5">C10</f>
+        <f t="shared" ref="K10:K46" si="7">C10</f>
         <v>2659.1900000000001</v>
       </c>
       <c r="L10" s="25"/>
@@ -13698,7 +13719,7 @@
     <row r="11" s="22" customFormat="1" ht="16.5">
       <c r="A11" s="22"/>
       <c r="B11" s="22" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="C11" s="53">
         <f>SUM(C5:C10)</f>
@@ -13731,7 +13752,7 @@
         <v>59108</v>
       </c>
       <c r="K11" s="51">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>150616.57000000001</v>
       </c>
       <c r="L11" s="55"/>
@@ -13749,7 +13770,7 @@
     <row r="12" s="22" customFormat="1" ht="16.5">
       <c r="A12" s="22"/>
       <c r="B12" s="21" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="C12" s="53">
         <f>C5+C9+C10</f>
@@ -13782,7 +13803,7 @@
         <v>59108</v>
       </c>
       <c r="K12" s="51">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>148205.07000000001</v>
       </c>
       <c r="L12" s="55"/>
@@ -13799,7 +13820,7 @@
     </row>
     <row r="13" ht="16.5">
       <c r="B13" s="21" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="C13" s="25">
         <v>1010.85</v>
@@ -13826,7 +13847,7 @@
         <v>275.90199999999999</v>
       </c>
       <c r="K13" s="51">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1010.85</v>
       </c>
       <c r="L13" s="25"/>
@@ -13844,7 +13865,7 @@
     <row r="14" s="22" customFormat="1" ht="16.5">
       <c r="A14" s="22"/>
       <c r="B14" s="22" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="C14" s="55">
         <f>C11+C13</f>
@@ -13879,7 +13900,7 @@
         <v>59383.902000000002</v>
       </c>
       <c r="K14" s="51">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>151627.42000000001</v>
       </c>
       <c r="L14" s="58">
@@ -13930,7 +13951,7 @@
     <row r="15" s="22" customFormat="1" ht="16.5">
       <c r="A15" s="22"/>
       <c r="B15" s="22" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="C15" s="55">
         <f>C63</f>
@@ -13965,7 +13986,7 @@
         <v>307669.04000000004</v>
       </c>
       <c r="K15" s="51">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>682609.71999999997</v>
       </c>
       <c r="L15" s="55"/>
@@ -13990,7 +14011,7 @@
       <c r="I16" s="57"/>
       <c r="J16" s="57"/>
       <c r="K16" s="51">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L16" s="25"/>
@@ -14007,10 +14028,10 @@
     </row>
     <row r="17" ht="16.5">
       <c r="A17" s="21" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="C17" s="25">
         <v>54300.779999999999</v>
@@ -14037,7 +14058,7 @@
         <v>23685.924999999999</v>
       </c>
       <c r="K17" s="51">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>54300.779999999999</v>
       </c>
       <c r="L17" s="55">
@@ -14087,10 +14108,10 @@
     </row>
     <row r="18" ht="16.5">
       <c r="A18" s="21" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="C18" s="25">
         <v>5538.21</v>
@@ -14119,7 +14140,7 @@
         <v>0</v>
       </c>
       <c r="K18" s="51">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5538.21</v>
       </c>
       <c r="L18" s="25">
@@ -14146,32 +14167,32 @@
         <v>2676.4511552000008</v>
       </c>
       <c r="R18" s="25">
-        <f t="shared" ref="R18:R19" si="6">Q18*1.06</f>
+        <f t="shared" ref="R18:R19" si="8">Q18*1.06</f>
         <v>2837.0382245120009</v>
       </c>
       <c r="S18" s="25">
-        <f t="shared" ref="S18:S19" si="7">R18*1.06</f>
+        <f t="shared" ref="S18:S19" si="9">R18*1.06</f>
         <v>3007.260517982721</v>
       </c>
       <c r="T18" s="25">
-        <f t="shared" ref="T18:T19" si="8">S18*1.06</f>
+        <f t="shared" ref="T18:T19" si="10">S18*1.06</f>
         <v>3187.6961490616845</v>
       </c>
       <c r="U18" s="25">
-        <f t="shared" ref="U18:U19" si="9">T18*1.06</f>
+        <f t="shared" ref="U18:U19" si="11">T18*1.06</f>
         <v>3378.9579180053856</v>
       </c>
       <c r="V18" s="57">
-        <f t="shared" ref="V18:V19" si="10">U18*1.06</f>
+        <f t="shared" ref="V18:V19" si="12">U18*1.06</f>
         <v>3581.6953930857089</v>
       </c>
     </row>
     <row r="19" ht="16.5">
       <c r="A19" s="21" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C19" s="25">
         <v>18282.060000000001</v>
@@ -14198,7 +14219,7 @@
         <v>7603.6199999999999</v>
       </c>
       <c r="K19" s="51">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>18282.060000000001</v>
       </c>
       <c r="L19" s="25">
@@ -14226,29 +14247,29 @@
         <v>40128.621209155368</v>
       </c>
       <c r="R19" s="25">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>42536.33848170469</v>
       </c>
       <c r="S19" s="25">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>45088.518790606977</v>
       </c>
       <c r="T19" s="25">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>47793.829918043397</v>
       </c>
       <c r="U19" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>50661.459713126002</v>
       </c>
       <c r="V19" s="57">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>53701.147295913564</v>
       </c>
     </row>
     <row r="20" ht="16.5">
       <c r="B20" s="21" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="C20" s="25">
         <v>921.05999999999995</v>
@@ -14275,7 +14296,7 @@
         <v>519.20000000000005</v>
       </c>
       <c r="K20" s="51">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>921.05999999999995</v>
       </c>
       <c r="L20" s="25">
@@ -14323,12 +14344,12 @@
         <v>1938.6949391852863</v>
       </c>
       <c r="Y20" s="21" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
     </row>
     <row r="21" ht="16.5">
       <c r="B21" s="21" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="C21" s="25">
         <v>12620.27</v>
@@ -14357,7 +14378,7 @@
         <v>7989.3000000000002</v>
       </c>
       <c r="K21" s="51">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>12620.27</v>
       </c>
       <c r="L21" s="25">
@@ -14408,7 +14429,7 @@
     <row r="22" s="22" customFormat="1" ht="16.5">
       <c r="A22" s="22"/>
       <c r="B22" s="22" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="C22" s="55">
         <f>SUM(C17:C21)</f>
@@ -14443,7 +14464,7 @@
         <v>39798.044999999998</v>
       </c>
       <c r="K22" s="51">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>91662.380000000005</v>
       </c>
       <c r="L22" s="56">
@@ -14493,7 +14514,7 @@
     </row>
     <row r="23" ht="16.5">
       <c r="B23" s="21" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C23" s="25">
         <f>C14-C22</f>
@@ -14528,7 +14549,7 @@
         <v>19585.857000000004</v>
       </c>
       <c r="K23" s="51">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>59965.040000000008</v>
       </c>
       <c r="L23" s="57">
@@ -14578,7 +14599,7 @@
     </row>
     <row r="24" ht="16.5">
       <c r="B24" s="21" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C24" s="25">
         <f>512.3+5.84-15807.24</f>
@@ -14613,7 +14634,7 @@
         <v>-7513.2400000000007</v>
       </c>
       <c r="K24" s="51">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>-15289.1</v>
       </c>
       <c r="L24" s="55">
@@ -14664,7 +14685,7 @@
     <row r="25" s="22" customFormat="1" ht="16.5">
       <c r="A25" s="22"/>
       <c r="B25" s="22" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C25" s="55">
         <f>C23+C24</f>
@@ -14699,7 +14720,7 @@
         <v>12072.617000000002</v>
       </c>
       <c r="K25" s="51">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>44675.94000000001</v>
       </c>
       <c r="L25" s="56">
@@ -14749,10 +14770,10 @@
     </row>
     <row r="26" ht="16.5">
       <c r="A26" s="21" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="B26" s="21" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="C26" s="25">
         <v>704.13</v>
@@ -14780,7 +14801,7 @@
         <v>-24.23</v>
       </c>
       <c r="K26" s="51">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>704.13</v>
       </c>
       <c r="L26" s="25">
@@ -14810,7 +14831,7 @@
     <row r="27" ht="16.5">
       <c r="A27" s="21"/>
       <c r="B27" s="21" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="C27" s="25">
         <f>C28/10</f>
@@ -14863,7 +14884,7 @@
     <row r="28" s="22" customFormat="1" ht="16.5">
       <c r="A28" s="22"/>
       <c r="B28" s="22" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="C28" s="59">
         <f>SUM(C25:C26)</f>
@@ -14896,7 +14917,7 @@
         <v>11997.85</v>
       </c>
       <c r="K28" s="51">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>45380.070000000007</v>
       </c>
       <c r="L28" s="55">
@@ -15012,7 +15033,7 @@
     </row>
     <row r="29" ht="16.5">
       <c r="B29" s="21" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="C29" s="62">
         <v>43242.879999999997</v>
@@ -15039,7 +15060,7 @@
         <v>11997.85</v>
       </c>
       <c r="K29" s="51">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>43242.879999999997</v>
       </c>
       <c r="L29" s="55">
@@ -15353,7 +15374,7 @@
     </row>
     <row r="30" ht="16.5">
       <c r="B30" s="21" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="C30" s="24">
         <f>C28/C29-1</f>
@@ -15382,7 +15403,7 @@
       <c r="I30" s="60"/>
       <c r="J30" s="60"/>
       <c r="K30" s="51">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.049422933902645072</v>
       </c>
       <c r="L30" s="55"/>
@@ -15407,7 +15428,7 @@
       <c r="I31" s="60"/>
       <c r="J31" s="60"/>
       <c r="K31" s="51">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="V31" s="29"/>
@@ -15415,7 +15436,7 @@
     </row>
     <row r="32" ht="16.5">
       <c r="B32" s="21" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="C32" s="62">
         <v>251072.07000000001</v>
@@ -15442,7 +15463,7 @@
         <v>216657.51999999999</v>
       </c>
       <c r="K32" s="51">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>251072.07000000001</v>
       </c>
       <c r="V32" s="29"/>
@@ -15450,7 +15471,7 @@
     </row>
     <row r="33" ht="16.5">
       <c r="B33" s="21" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="C33" s="25">
         <v>401453679</v>
@@ -15477,7 +15498,7 @@
         <v>400041239</v>
       </c>
       <c r="K33" s="51">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>401453679</v>
       </c>
       <c r="V33" s="29"/>
@@ -15485,7 +15506,7 @@
     <row r="34" ht="16.5">
       <c r="A34" s="21"/>
       <c r="B34" s="21" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="C34" s="21">
         <f>C29*1000000/D33</f>
@@ -15520,14 +15541,14 @@
         <v>29.991532947931901</v>
       </c>
       <c r="K34" s="51">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>107.73071267045023</v>
       </c>
       <c r="V34" s="29"/>
     </row>
     <row r="35" ht="16.5">
       <c r="A35" s="21" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="B35" s="21"/>
       <c r="C35" s="21"/>
@@ -15539,7 +15560,7 @@
       <c r="I35" s="29"/>
       <c r="J35" s="29"/>
       <c r="K35" s="51">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="V35" s="29"/>
@@ -15547,7 +15568,7 @@
     <row r="36" ht="16.5">
       <c r="A36" s="21"/>
       <c r="B36" s="36" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="C36" s="24">
         <f>C11/D11-1</f>
@@ -15579,11 +15600,11 @@
       </c>
       <c r="J36" s="64"/>
       <c r="K36" s="65">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.26593407461616625</v>
       </c>
       <c r="U36" s="21" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="V36" s="66">
         <v>0.11</v>
@@ -15591,7 +15612,7 @@
     </row>
     <row r="37" ht="16.5">
       <c r="B37" s="36" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="C37" s="24">
         <f>C14/D14-1</f>
@@ -15626,23 +15647,23 @@
         <v>-0.60835644370919195</v>
       </c>
       <c r="K37" s="65">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.26619922079364478</v>
       </c>
       <c r="U37" s="21" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="V37" s="33">
         <f>NPV(V36,L29:CJ29)</f>
         <v>858348.73920576624</v>
       </c>
       <c r="W37" s="21" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
     </row>
     <row r="38" ht="16.5">
       <c r="B38" s="36" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="C38" s="41">
         <f>C14-C17</f>
@@ -15677,11 +15698,11 @@
         <v>35697.976999999999</v>
       </c>
       <c r="K38" s="68">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>97326.640000000014</v>
       </c>
       <c r="U38" s="22" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="V38" s="69">
         <v>2228.0999999999999</v>
@@ -15690,7 +15711,7 @@
     <row r="39" s="22" customFormat="1" ht="16.5">
       <c r="A39" s="22"/>
       <c r="B39" s="38" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="C39" s="70">
         <f>C17/C14</f>
@@ -15725,13 +15746,13 @@
         <v>0.39886104149909174</v>
       </c>
       <c r="K39" s="72">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.35811979126202897</v>
       </c>
       <c r="L39" s="73"/>
       <c r="M39" s="73"/>
       <c r="U39" s="22" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="V39" s="74">
         <v>401452876</v>
@@ -15739,7 +15760,7 @@
     </row>
     <row r="40" ht="16.5">
       <c r="B40" s="36" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="C40" s="24">
         <f>C28/D28-1</f>
@@ -15778,16 +15799,17 @@
         <v>-0.14801992128648367</v>
       </c>
       <c r="U40" s="21" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="V40" s="66">
         <v>0.01</v>
       </c>
+      <c r="Y40" s="21"/>
     </row>
     <row r="41" ht="16.5">
       <c r="A41" s="21"/>
       <c r="B41" s="36" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="C41" s="24">
         <f>(C22-D22)/D22</f>
@@ -15822,11 +15844,11 @@
         <v>-0.56581920521810591</v>
       </c>
       <c r="K41" s="65">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.29976539319151052</v>
       </c>
       <c r="U41" s="21" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="V41" s="22">
         <f>V37*1000000/V39</f>
@@ -15835,7 +15857,7 @@
     </row>
     <row r="42" ht="16.5">
       <c r="B42" s="36" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="C42" s="24">
         <f>C17/D17-1</f>
@@ -15870,19 +15892,19 @@
         <v>-0.56380138554179149</v>
       </c>
       <c r="K42" s="65">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.29005663338542576</v>
       </c>
       <c r="U42" s="21" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
     </row>
     <row r="43" ht="16.5">
       <c r="A43" s="21" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="B43" s="36" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="C43" s="24">
         <f>C28/D28-1</f>
@@ -15917,16 +15939,16 @@
         <v>-0.73561411430171875</v>
       </c>
       <c r="K43" s="65">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.22231499854685355</v>
       </c>
       <c r="U43" s="21" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
     </row>
     <row r="44" ht="16.5">
       <c r="B44" s="36" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="C44" s="24">
         <f>C34/D34-1</f>
@@ -15961,16 +15983,16 @@
         <v>-0.72160647410106327</v>
       </c>
       <c r="K44" s="65">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.19726808095135451</v>
       </c>
       <c r="U44" s="21" t="s">
-        <v>388</v>
+        <v>67</v>
       </c>
     </row>
     <row r="45" ht="16.5">
       <c r="B45" s="36" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="C45" s="24">
         <f>C26/D26-1</f>
@@ -16002,13 +16024,13 @@
       </c>
       <c r="J45" s="24"/>
       <c r="K45" s="65">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.64259220379312754</v>
       </c>
     </row>
     <row r="46" ht="16.5">
       <c r="B46" s="36" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="C46" s="24">
         <f>C29/D29-1</f>
@@ -16040,96 +16062,96 @@
       </c>
       <c r="J46" s="24"/>
       <c r="K46" s="65">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.19710167876515161</v>
       </c>
     </row>
     <row r="47" ht="16.5">
       <c r="B47" s="36" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="C47" s="24">
-        <f t="shared" ref="C47:C48" si="11">C19/D19-1</f>
+        <f t="shared" ref="C47:C48" si="13">C19/D19-1</f>
         <v>0.22841181830154245</v>
       </c>
       <c r="D47" s="24">
-        <f t="shared" ref="D47:D48" si="12">D19/E19-1</f>
+        <f t="shared" ref="D47:D48" si="14">D19/E19-1</f>
         <v>0.20071965663019986</v>
       </c>
       <c r="E47" s="24">
-        <f t="shared" ref="E47:E48" si="13">E19/F19-1</f>
+        <f t="shared" ref="E47:E48" si="15">E19/F19-1</f>
         <v>0.042217423768490248</v>
       </c>
       <c r="F47" s="24">
-        <f t="shared" ref="F47:F48" si="14">F19/G19-1</f>
+        <f t="shared" ref="F47:F48" si="16">F19/G19-1</f>
         <v>-0.015902489884070281</v>
       </c>
       <c r="G47" s="24">
-        <f t="shared" ref="G47:G48" si="15">G19/H19-1</f>
+        <f t="shared" ref="G47:G48" si="17">G19/H19-1</f>
         <v>0.19257743922837567</v>
       </c>
       <c r="H47" s="24">
-        <f t="shared" ref="H47:H48" si="16">H19/I19-1</f>
+        <f t="shared" ref="H47:H48" si="18">H19/I19-1</f>
         <v>0.21580637188442608</v>
       </c>
       <c r="I47" s="24">
-        <f t="shared" ref="I47:I48" si="17">I19/J19-1</f>
+        <f t="shared" ref="I47:I48" si="19">I19/J19-1</f>
         <v>0.096154200236203247</v>
       </c>
       <c r="J47" s="24">
-        <f t="shared" ref="J47:J48" si="18">J19/K19-1</f>
+        <f t="shared" ref="J47:J48" si="20">J19/K19-1</f>
         <v>-0.58409391501832952</v>
       </c>
       <c r="K47" s="34">
-        <f t="shared" ref="K47:K48" si="19">K19/L19-1</f>
+        <f t="shared" ref="K47:K48" si="21">K19/L19-1</f>
         <v>-0.12280701754385959</v>
       </c>
     </row>
     <row r="48" ht="16.5">
       <c r="B48" s="36" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="C48" s="24">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.17841378692698395</v>
       </c>
       <c r="D48" s="24">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.11653786266302868</v>
       </c>
       <c r="E48" s="24">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.039236935866983291</v>
       </c>
       <c r="F48" s="24">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.13703116032544482</v>
       </c>
       <c r="G48" s="24">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.14603524655175759</v>
       </c>
       <c r="H48" s="24">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.033302016910867982</v>
       </c>
       <c r="I48" s="24">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>-0.036459938366718125</v>
       </c>
       <c r="J48" s="24">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-0.43630165244392327</v>
       </c>
       <c r="K48" s="34">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-0.06542056074766367</v>
       </c>
     </row>
     <row r="49" s="22" customFormat="1" ht="16.5">
       <c r="A49" s="22"/>
       <c r="B49" s="22" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="C49" s="70">
         <f>C17/C15</f>
@@ -16164,14 +16186,14 @@
         <v>0.076985077861587883</v>
       </c>
       <c r="K49" s="72">
-        <f t="shared" ref="K49:K50" si="20">C49</f>
+        <f t="shared" ref="K49:K50" si="22">C49</f>
         <v>0.079548794001937151</v>
       </c>
     </row>
     <row r="50" s="22" customFormat="1" ht="16.5">
       <c r="A50" s="22"/>
       <c r="B50" s="22" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="C50" s="70">
         <f>C5/C15</f>
@@ -16200,14 +16222,14 @@
       <c r="I50" s="70"/>
       <c r="J50" s="70"/>
       <c r="K50" s="72">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.21308956749106944</v>
       </c>
     </row>
     <row r="51" s="22" customFormat="1" ht="16.5">
       <c r="A51" s="22"/>
       <c r="B51" s="22" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C51" s="70">
         <f>C24/C23*-1</f>
@@ -16259,7 +16281,7 @@
     </row>
     <row r="53" ht="16.5">
       <c r="A53" s="48" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="B53" s="21"/>
       <c r="C53" s="21"/>
@@ -16273,7 +16295,7 @@
     </row>
     <row r="54" ht="16.5">
       <c r="A54" s="22" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="B54" s="21"/>
       <c r="C54" s="21"/>
@@ -16288,7 +16310,7 @@
     <row r="55" ht="16.5">
       <c r="A55" s="21"/>
       <c r="B55" s="21" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="C55" s="25">
         <v>4014.6199999999999</v>
@@ -16318,7 +16340,7 @@
     </row>
     <row r="56" ht="16.5">
       <c r="B56" s="21" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="C56" s="25">
         <v>247057.45000000001</v>
@@ -16348,7 +16370,7 @@
     </row>
     <row r="57" ht="16.5">
       <c r="B57" s="21" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="C57" s="25">
         <f>C56+C55</f>
@@ -16385,7 +16407,7 @@
     </row>
     <row r="58" ht="16.5">
       <c r="A58" s="22" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="B58" s="21"/>
       <c r="C58" s="21"/>
@@ -16399,7 +16421,7 @@
     </row>
     <row r="59" ht="16.5">
       <c r="B59" s="21" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="C59" s="25">
         <v>174762.20000000001</v>
@@ -16428,7 +16450,7 @@
     </row>
     <row r="60" ht="16.5">
       <c r="B60" s="21" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="C60" s="25">
         <v>500519.53000000003</v>
@@ -16457,7 +16479,7 @@
     </row>
     <row r="61" ht="16.5">
       <c r="B61" s="21" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="C61" s="25">
         <v>4018.2600000000002</v>
@@ -16486,7 +16508,7 @@
     </row>
     <row r="62" ht="16.5">
       <c r="B62" s="21" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="C62" s="25">
         <v>3309.73</v>
@@ -16507,7 +16529,7 @@
     </row>
     <row r="63" ht="16.5">
       <c r="B63" s="21" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="C63" s="25">
         <f>SUM(C59:C62)</f>
@@ -16545,7 +16567,7 @@
     <row r="64" s="22" customFormat="1" ht="16.5">
       <c r="A64" s="22"/>
       <c r="B64" s="22" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="C64" s="55">
         <f>C63+C57</f>
@@ -16593,21 +16615,21 @@
     </row>
     <row r="66" ht="16.5">
       <c r="A66" s="48" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="C66" s="21"/>
       <c r="D66" s="21"/>
     </row>
     <row r="67" ht="16.5">
       <c r="A67" s="22" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="C67" s="21"/>
       <c r="D67" s="21"/>
     </row>
     <row r="68" ht="16.5">
       <c r="B68" s="21" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="C68" s="62">
         <f>C23</f>
@@ -16620,10 +16642,10 @@
     </row>
     <row r="69" ht="16.5">
       <c r="A69" s="21" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="B69" s="21" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="C69" s="62">
         <f>C20</f>
@@ -16632,10 +16654,10 @@
     </row>
     <row r="70" ht="16.5">
       <c r="A70" s="21" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="B70" s="21" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="C70" s="62">
         <f>C18</f>
@@ -16644,10 +16666,10 @@
     </row>
     <row r="71" ht="16.5">
       <c r="A71" s="21" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="B71" s="21" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="C71" s="62">
         <f>C17</f>
@@ -16656,10 +16678,10 @@
     </row>
     <row r="72" ht="16.5">
       <c r="A72" s="21" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="B72" s="21" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="C72" s="21">
         <v>-6.3899999999999997</v>
@@ -16667,7 +16689,7 @@
     </row>
     <row r="73" ht="16.5">
       <c r="B73" s="21" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="C73" s="21">
         <v>161.02000000000001</v>
@@ -16675,10 +16697,10 @@
     </row>
     <row r="74" ht="16.5">
       <c r="A74" s="21" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="B74" s="21" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C74" s="21">
         <v>-13.550000000000001</v>
@@ -16686,10 +16708,10 @@
     </row>
     <row r="75" ht="16.5">
       <c r="A75" s="21" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="B75" s="21" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="C75" s="21">
         <v>-3369.0799999999999</v>
@@ -16697,10 +16719,10 @@
     </row>
     <row r="76" ht="16.5">
       <c r="A76" s="21" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="B76" s="21" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="C76" s="21">
         <v>-48.100000000000001</v>
@@ -16708,7 +16730,7 @@
     </row>
     <row r="77" ht="16.5">
       <c r="B77" s="21" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="C77" s="21">
         <v>-1022.58</v>
@@ -16716,7 +16738,7 @@
     </row>
     <row r="78" ht="16.5">
       <c r="B78" s="21" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="C78" s="21">
         <v>388.77999999999997</v>
@@ -16725,7 +16747,7 @@
     <row r="79" s="22" customFormat="1" ht="16.5">
       <c r="A79" s="22"/>
       <c r="B79" s="22" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="C79" s="59">
         <f>SUM(C68:C78)</f>
@@ -16742,16 +16764,16 @@
     <row r="81" ht="14.25">
       <c r="A81" s="21"/>
       <c r="B81" s="21" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="C81" s="21"/>
     </row>
     <row r="82" ht="14.25">
       <c r="A82" s="21" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="B82" s="21" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="C82" s="21">
         <v>-79.409999999999997</v>
@@ -16759,10 +16781,10 @@
     </row>
     <row r="83" ht="14.25">
       <c r="A83" s="21" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="B83" s="21" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="C83" s="21">
         <v>307.81</v>
@@ -16770,7 +16792,7 @@
     </row>
     <row r="84" ht="14.25">
       <c r="B84" s="21" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="C84" s="21">
         <v>-179256.51000000001</v>
@@ -16778,27 +16800,27 @@
     </row>
     <row r="85" ht="14.25">
       <c r="B85" s="21" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
     </row>
     <row r="86" ht="14.25">
       <c r="B86" s="21" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
     </row>
     <row r="87" ht="14.25">
       <c r="B87" s="21" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
     </row>
     <row r="88" ht="14.25">
       <c r="B88" s="21" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
     </row>
     <row r="89" ht="14.25">
       <c r="B89" s="21" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
     </row>
     <row r="90" ht="14.25">
@@ -16810,15 +16832,15 @@
     </row>
     <row r="92" ht="14.25">
       <c r="A92" s="21" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="B92" s="21" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="96" ht="14.25">
       <c r="A96" s="22" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="97" ht="14.25">
@@ -16826,7 +16848,7 @@
     </row>
     <row r="102" ht="14.25">
       <c r="A102" s="22" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
     </row>
   </sheetData>
